--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2430,6 +2430,7188 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132821661</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>696690</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6643717</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132825468</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>696704</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6643630</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132830947</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>696785</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6643731</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132830977</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>696664</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6643658</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132830954</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>696732</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6643642</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132821435</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>696687</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6643684</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132821594</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>696683</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6643725</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132830932</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>696970</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6643862</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132830940</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>696814</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6643811</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132830980</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>696668</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6643646</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132830962</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>696727</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6643708</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132830942</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>696776</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6643778</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132830941</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>696790</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6643780</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132822772</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>696813</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6643818</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132823051</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>696853</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6643821</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132830937</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>696837</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6643803</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132830929</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>697012</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6643911</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132830957</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>696757</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6643672</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132826336</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>696492</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6643764</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132830923</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>697051</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6643938</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132830961</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>696729</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6643708</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132823255</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>696904</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6643781</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132822951</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>696846</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6643821</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132830925</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>697028</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6643921</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132830915</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>696686</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6643680</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132822662</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>696811</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6643816</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132823172</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>696885</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6643816</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132821927</v>
+      </c>
+      <c r="B44" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>696722</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6643677</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132830956</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>696730</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6643665</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132830963</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>696701</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6643708</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132830936</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>696871</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6643836</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132830934</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>696926</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6643877</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132821365</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>696684</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6643670</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132830943</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>696778</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6643770</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132830979</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>696663</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6643658</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132822683</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>696803</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6643814</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132830927</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>696972</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6643904</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132830930</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>697027</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6643874</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132830911</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>696479</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6643760</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132830931</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91929</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>697026</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6643874</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132830935</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>696897</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6643810</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132821892</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>696722</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6643684</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132822271</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>696774</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6643715</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132821521</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>696690</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6643690</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132821719</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>696709</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6643709</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132830970</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>696614</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6643745</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132830971</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>696622</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6643679</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132830933</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>696939</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6643882</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132826107</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>696530</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6643699</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132830913</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>696702</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6643704</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132830985</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>696679</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6643623</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132825569</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>696671</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6643630</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132830978</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>696664</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6643658</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132830964</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>696700</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6643694</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132830946</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>696782</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6643729</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132822866</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>696815</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6643822</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132830976</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>696677</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6643661</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132830974</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>696678</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6643668</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132830949</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>696758</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6643677</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132821474</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>696684</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6643683</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132830928</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91929</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>696996</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6643908</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132830960</v>
+      </c>
+      <c r="B78" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>696741</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6643703</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132830945</v>
+      </c>
+      <c r="B79" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>696784</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6643729</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132823493</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>696964</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6643823</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,7 +2432,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132821661</v>
+        <v>132825468</v>
       </c>
       <c r="B17" t="n">
         <v>99118</v>
@@ -2460,7 +2460,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2472,10 +2476,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696690</v>
+        <v>696704</v>
       </c>
       <c r="R17" t="n">
-        <v>6643717</v>
+        <v>6643630</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,7 +2511,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2517,7 +2521,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,54 +2548,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132825468</v>
+        <v>132830947</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696704</v>
+        <v>696785</v>
       </c>
       <c r="R18" t="n">
-        <v>6643630</v>
+        <v>6643731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2648,62 +2648,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132830947</v>
+        <v>132830954</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>101326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696785</v>
+        <v>696732</v>
       </c>
       <c r="R19" t="n">
-        <v>6643731</v>
+        <v>6643642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2735,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2740,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,53 +2767,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132830977</v>
+        <v>132821661</v>
       </c>
       <c r="B20" t="n">
-        <v>58327</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696664</v>
+        <v>696690</v>
       </c>
       <c r="R20" t="n">
-        <v>6643658</v>
+        <v>6643717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,7 +2842,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2852,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2875,22 +2867,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830954</v>
+        <v>132830977</v>
       </c>
       <c r="B21" t="n">
-        <v>101326</v>
+        <v>58327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,34 +2890,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696732</v>
+        <v>696664</v>
       </c>
       <c r="R21" t="n">
-        <v>6643642</v>
+        <v>6643658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3226,7 +3226,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132830932</v>
+        <v>132830962</v>
       </c>
       <c r="B24" t="n">
         <v>101326</v>
@@ -3257,14 +3257,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696970</v>
+        <v>696727</v>
       </c>
       <c r="R24" t="n">
-        <v>6643862</v>
+        <v>6643708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,45 +3333,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830940</v>
+        <v>132830942</v>
       </c>
       <c r="B25" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696814</v>
+        <v>696776</v>
       </c>
       <c r="R25" t="n">
-        <v>6643811</v>
+        <v>6643778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3413,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3440,45 +3449,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830980</v>
+        <v>132830932</v>
       </c>
       <c r="B26" t="n">
-        <v>91909</v>
+        <v>101326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696668</v>
+        <v>696970</v>
       </c>
       <c r="R26" t="n">
-        <v>6643646</v>
+        <v>6643862</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3510,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3520,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,7 +3556,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830962</v>
+        <v>132830940</v>
       </c>
       <c r="B27" t="n">
         <v>101326</v>
@@ -3582,10 +3591,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696727</v>
+        <v>696814</v>
       </c>
       <c r="R27" t="n">
-        <v>6643708</v>
+        <v>6643811</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3617,7 +3626,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3627,7 +3636,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3654,54 +3663,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830942</v>
+        <v>132830980</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696776</v>
+        <v>696668</v>
       </c>
       <c r="R28" t="n">
-        <v>6643778</v>
+        <v>6643646</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5443,45 +5443,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132821927</v>
+        <v>132830956</v>
       </c>
       <c r="B44" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696722</v>
+        <v>696730</v>
       </c>
       <c r="R44" t="n">
-        <v>6643677</v>
+        <v>6643665</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5538,54 +5547,50 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830956</v>
+        <v>132830963</v>
       </c>
       <c r="B45" t="n">
-        <v>99118</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5594,10 +5599,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696730</v>
+        <v>696701</v>
       </c>
       <c r="R45" t="n">
-        <v>6643665</v>
+        <v>6643708</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5629,7 +5634,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5639,7 +5644,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5666,50 +5671,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830963</v>
+        <v>132830934</v>
       </c>
       <c r="B46" t="n">
-        <v>57950</v>
+        <v>101326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696701</v>
+        <v>696926</v>
       </c>
       <c r="R46" t="n">
-        <v>6643708</v>
+        <v>6643877</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,45 +5778,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830936</v>
+        <v>132821365</v>
       </c>
       <c r="B47" t="n">
-        <v>91930</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696871</v>
+        <v>696684</v>
       </c>
       <c r="R47" t="n">
-        <v>6643836</v>
+        <v>6643670</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5848,7 +5857,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5858,7 +5867,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5873,22 +5882,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830934</v>
+        <v>132821927</v>
       </c>
       <c r="B48" t="n">
-        <v>101326</v>
+        <v>106244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,34 +5905,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696926</v>
+        <v>696722</v>
       </c>
       <c r="R48" t="n">
-        <v>6643877</v>
+        <v>6643677</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5955,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5965,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,66 +5989,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132821365</v>
+        <v>132830936</v>
       </c>
       <c r="B49" t="n">
-        <v>99118</v>
+        <v>91930</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696684</v>
+        <v>696871</v>
       </c>
       <c r="R49" t="n">
-        <v>6643670</v>
+        <v>6643836</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,12 +6096,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -7340,54 +7340,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132821719</v>
+        <v>132830970</v>
       </c>
       <c r="B61" t="n">
-        <v>99118</v>
+        <v>101326</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696709</v>
+        <v>696614</v>
       </c>
       <c r="R61" t="n">
-        <v>6643709</v>
+        <v>6643745</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7419,7 +7410,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7429,7 +7420,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7444,57 +7435,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830970</v>
+        <v>132830971</v>
       </c>
       <c r="B62" t="n">
-        <v>101326</v>
+        <v>57950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696614</v>
+        <v>696622</v>
       </c>
       <c r="R62" t="n">
-        <v>6643745</v>
+        <v>6643679</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7526,7 +7522,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7536,7 +7532,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7563,50 +7559,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830971</v>
+        <v>132821719</v>
       </c>
       <c r="B63" t="n">
-        <v>57950</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696622</v>
+        <v>696709</v>
       </c>
       <c r="R63" t="n">
-        <v>6643679</v>
+        <v>6643709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132826107</v>
+        <v>132830913</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696530</v>
+        <v>696702</v>
       </c>
       <c r="R65" t="n">
-        <v>6643699</v>
+        <v>6643704</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7895,19 +7895,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132830913</v>
+        <v>132830985</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696702</v>
+        <v>696679</v>
       </c>
       <c r="R66" t="n">
-        <v>6643704</v>
+        <v>6643623</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7996,7 +7996,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8023,7 +8028,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132830985</v>
+        <v>132826107</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -8053,7 +8058,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8063,14 +8068,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696679</v>
+        <v>696530</v>
       </c>
       <c r="R67" t="n">
-        <v>6643623</v>
+        <v>6643699</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8102,7 +8107,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8112,12 +8117,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,12 +8132,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,54 +2432,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132825468</v>
+        <v>132830977</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>58328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696704</v>
+        <v>696664</v>
       </c>
       <c r="R17" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2521,7 +2520,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,12 +2535,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2551,7 +2550,7 @@
         <v>132830947</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,45 +2659,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132830954</v>
+        <v>132825468</v>
       </c>
       <c r="B19" t="n">
-        <v>101326</v>
+        <v>99119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696732</v>
+        <v>696704</v>
       </c>
       <c r="R19" t="n">
-        <v>6643642</v>
+        <v>6643630</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2740,7 +2748,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,12 +2763,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2770,7 +2778,7 @@
         <v>132821661</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,53 +2887,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830977</v>
+        <v>132821435</v>
       </c>
       <c r="B21" t="n">
-        <v>58327</v>
+        <v>99119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696664</v>
+        <v>696687</v>
       </c>
       <c r="R21" t="n">
-        <v>6643658</v>
+        <v>6643684</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,7 +2966,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,7 +2976,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,66 +2991,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132821435</v>
+        <v>132830954</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>101327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696687</v>
+        <v>696732</v>
       </c>
       <c r="R22" t="n">
-        <v>6643684</v>
+        <v>6643642</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,66 +3098,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132821594</v>
+        <v>132830980</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>91910</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696683</v>
+        <v>696668</v>
       </c>
       <c r="R23" t="n">
-        <v>6643725</v>
+        <v>6643646</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3189,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3199,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,12 +3205,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3229,7 +3220,7 @@
         <v>132830962</v>
       </c>
       <c r="B24" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3333,54 +3324,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830942</v>
+        <v>132830932</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>101327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696776</v>
+        <v>696970</v>
       </c>
       <c r="R25" t="n">
-        <v>6643778</v>
+        <v>6643862</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,10 +3431,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830932</v>
+        <v>132830940</v>
       </c>
       <c r="B26" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3480,14 +3462,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696970</v>
+        <v>696814</v>
       </c>
       <c r="R26" t="n">
-        <v>6643862</v>
+        <v>6643811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,10 +3538,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830940</v>
+        <v>132830941</v>
       </c>
       <c r="B27" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,10 +3573,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696814</v>
+        <v>696790</v>
       </c>
       <c r="R27" t="n">
-        <v>6643811</v>
+        <v>6643780</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3626,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3636,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3663,45 +3645,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830980</v>
+        <v>132822772</v>
       </c>
       <c r="B28" t="n">
-        <v>91909</v>
+        <v>99119</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696668</v>
+        <v>696813</v>
       </c>
       <c r="R28" t="n">
-        <v>6643646</v>
+        <v>6643818</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3733,7 +3724,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3743,7 +3734,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,57 +3749,66 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830941</v>
+        <v>132830942</v>
       </c>
       <c r="B29" t="n">
-        <v>101326</v>
+        <v>99119</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696790</v>
+        <v>696776</v>
       </c>
       <c r="R29" t="n">
-        <v>6643780</v>
+        <v>6643778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132822772</v>
+        <v>132823051</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696813</v>
+        <v>696853</v>
       </c>
       <c r="R30" t="n">
-        <v>6643818</v>
+        <v>6643821</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132823051</v>
+        <v>132821594</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696853</v>
+        <v>696683</v>
       </c>
       <c r="R31" t="n">
-        <v>6643821</v>
+        <v>6643725</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,45 +4109,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132830937</v>
+        <v>132826336</v>
       </c>
       <c r="B32" t="n">
-        <v>101326</v>
+        <v>57951</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696837</v>
+        <v>696492</v>
       </c>
       <c r="R32" t="n">
-        <v>6643803</v>
+        <v>6643764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,22 +4209,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830929</v>
+        <v>132830937</v>
       </c>
       <c r="B33" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4247,14 +4252,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697012</v>
+        <v>696837</v>
       </c>
       <c r="R33" t="n">
-        <v>6643911</v>
+        <v>6643803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,7 +4291,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4301,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,10 +4328,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830957</v>
+        <v>132830929</v>
       </c>
       <c r="B34" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,14 +4359,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696757</v>
+        <v>697012</v>
       </c>
       <c r="R34" t="n">
-        <v>6643672</v>
+        <v>6643911</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,50 +4435,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132826336</v>
+        <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>57950</v>
+        <v>101327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696492</v>
+        <v>696757</v>
       </c>
       <c r="R35" t="n">
-        <v>6643764</v>
+        <v>6643672</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,22 +4530,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132830923</v>
+        <v>132830961</v>
       </c>
       <c r="B36" t="n">
-        <v>101326</v>
+        <v>99154</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,34 +4553,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697051</v>
+        <v>696729</v>
       </c>
       <c r="R36" t="n">
-        <v>6643938</v>
+        <v>6643708</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132830961</v>
+        <v>132830923</v>
       </c>
       <c r="B37" t="n">
-        <v>99153</v>
+        <v>101327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,34 +4660,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696729</v>
+        <v>697051</v>
       </c>
       <c r="R37" t="n">
-        <v>6643708</v>
+        <v>6643938</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4759,7 +4759,7 @@
         <v>132823255</v>
       </c>
       <c r="B38" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>132822951</v>
       </c>
       <c r="B39" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,45 +4988,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132830925</v>
+        <v>132823172</v>
       </c>
       <c r="B40" t="n">
-        <v>101326</v>
+        <v>99119</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697028</v>
+        <v>696885</v>
       </c>
       <c r="R40" t="n">
-        <v>6643921</v>
+        <v>6643816</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5058,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5068,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,12 +5092,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5098,7 +5107,7 @@
         <v>132830915</v>
       </c>
       <c r="B41" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5214,7 +5223,7 @@
         <v>132822662</v>
       </c>
       <c r="B42" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,54 +5336,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132823172</v>
+        <v>132830925</v>
       </c>
       <c r="B43" t="n">
-        <v>99118</v>
+        <v>101327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696885</v>
+        <v>697028</v>
       </c>
       <c r="R43" t="n">
-        <v>6643816</v>
+        <v>6643921</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5431,66 +5431,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830956</v>
+        <v>132830936</v>
       </c>
       <c r="B44" t="n">
-        <v>99118</v>
+        <v>91931</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696730</v>
+        <v>696871</v>
       </c>
       <c r="R44" t="n">
-        <v>6643665</v>
+        <v>6643836</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5522,7 +5513,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5532,7 +5523,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5562,7 +5553,7 @@
         <v>132830963</v>
       </c>
       <c r="B45" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5671,45 +5662,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830934</v>
+        <v>132830956</v>
       </c>
       <c r="B46" t="n">
-        <v>101326</v>
+        <v>99119</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696926</v>
+        <v>696730</v>
       </c>
       <c r="R46" t="n">
-        <v>6643877</v>
+        <v>6643665</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5781,7 +5781,7 @@
         <v>132821365</v>
       </c>
       <c r="B47" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>132821927</v>
       </c>
       <c r="B48" t="n">
-        <v>106244</v>
+        <v>106245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6001,32 +6001,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830936</v>
+        <v>132830934</v>
       </c>
       <c r="B49" t="n">
-        <v>91930</v>
+        <v>101327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696871</v>
+        <v>696926</v>
       </c>
       <c r="R49" t="n">
-        <v>6643836</v>
+        <v>6643877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6108,45 +6108,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132830943</v>
+        <v>132830979</v>
       </c>
       <c r="B50" t="n">
-        <v>101326</v>
+        <v>99119</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696778</v>
+        <v>696663</v>
       </c>
       <c r="R50" t="n">
-        <v>6643770</v>
+        <v>6643658</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,7 +6187,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6188,7 +6197,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,54 +6224,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132830979</v>
+        <v>132830943</v>
       </c>
       <c r="B51" t="n">
-        <v>99118</v>
+        <v>101327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696663</v>
+        <v>696778</v>
       </c>
       <c r="R51" t="n">
-        <v>6643658</v>
+        <v>6643770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6331,54 +6331,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132822683</v>
+        <v>132830911</v>
       </c>
       <c r="B52" t="n">
-        <v>99118</v>
+        <v>57951</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696803</v>
+        <v>696479</v>
       </c>
       <c r="R52" t="n">
-        <v>6643814</v>
+        <v>6643760</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6410,7 +6406,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6420,7 +6416,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6435,66 +6431,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830927</v>
+        <v>132830930</v>
       </c>
       <c r="B53" t="n">
-        <v>99118</v>
+        <v>101327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696972</v>
+        <v>697027</v>
       </c>
       <c r="R53" t="n">
-        <v>6643904</v>
+        <v>6643874</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6526,7 +6513,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6523,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6563,45 +6550,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830930</v>
+        <v>132830927</v>
       </c>
       <c r="B54" t="n">
-        <v>101326</v>
+        <v>99119</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697027</v>
+        <v>696972</v>
       </c>
       <c r="R54" t="n">
-        <v>6643874</v>
+        <v>6643904</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6633,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6643,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,50 +6666,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830911</v>
+        <v>132822683</v>
       </c>
       <c r="B55" t="n">
-        <v>57950</v>
+        <v>99119</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696479</v>
+        <v>696803</v>
       </c>
       <c r="R55" t="n">
-        <v>6643760</v>
+        <v>6643814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,53 +6770,66 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132830931</v>
+        <v>132821892</v>
       </c>
       <c r="B56" t="n">
-        <v>91929</v>
+        <v>99119</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697026</v>
+        <v>696722</v>
       </c>
       <c r="R56" t="n">
-        <v>6643874</v>
+        <v>6643684</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6848,7 +6861,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6858,7 +6871,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6873,12 +6886,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6888,7 +6901,7 @@
         <v>132830935</v>
       </c>
       <c r="B57" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6992,54 +7005,41 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132821892</v>
+        <v>132830931</v>
       </c>
       <c r="B58" t="n">
-        <v>99118</v>
+        <v>91930</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696722</v>
+        <v>697026</v>
       </c>
       <c r="R58" t="n">
-        <v>6643684</v>
+        <v>6643874</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7111,7 +7111,7 @@
         <v>132822271</v>
       </c>
       <c r="B59" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7227,7 +7227,7 @@
         <v>132821521</v>
       </c>
       <c r="B60" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>132830970</v>
       </c>
       <c r="B61" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>132830971</v>
       </c>
       <c r="B62" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>132821719</v>
       </c>
       <c r="B63" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>132830933</v>
       </c>
       <c r="B64" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132830913</v>
+        <v>132830985</v>
       </c>
       <c r="B65" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7835,10 +7835,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696702</v>
+        <v>696679</v>
       </c>
       <c r="R65" t="n">
-        <v>6643704</v>
+        <v>6643623</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7880,7 +7880,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7907,10 +7912,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132830985</v>
+        <v>132826107</v>
       </c>
       <c r="B66" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7937,7 +7942,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7947,14 +7952,14 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696679</v>
+        <v>696530</v>
       </c>
       <c r="R66" t="n">
-        <v>6643623</v>
+        <v>6643699</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7986,7 +7991,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7996,12 +8001,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8016,22 +8016,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132826107</v>
+        <v>132830913</v>
       </c>
       <c r="B67" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8068,14 +8068,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696530</v>
+        <v>696702</v>
       </c>
       <c r="R67" t="n">
-        <v>6643699</v>
+        <v>6643704</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,66 +8132,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132825569</v>
+        <v>132830978</v>
       </c>
       <c r="B68" t="n">
-        <v>99118</v>
+        <v>58498</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696671</v>
+        <v>696664</v>
       </c>
       <c r="R68" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8223,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8248,22 +8247,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B69" t="n">
-        <v>58497</v>
+        <v>58637</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8271,16 +8270,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8303,10 +8302,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R69" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8375,53 +8374,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>58636</v>
+        <v>99119</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R70" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8493,7 +8493,7 @@
         <v>132830946</v>
       </c>
       <c r="B71" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>132822866</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>132830976</v>
       </c>
       <c r="B73" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,54 +8829,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830974</v>
+        <v>132830949</v>
       </c>
       <c r="B74" t="n">
-        <v>99118</v>
+        <v>101327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696678</v>
+        <v>696758</v>
       </c>
       <c r="R74" t="n">
-        <v>6643668</v>
+        <v>6643677</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8908,7 +8899,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8918,12 +8909,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8950,45 +8936,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132830949</v>
+        <v>132821474</v>
       </c>
       <c r="B75" t="n">
-        <v>101326</v>
+        <v>99119</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696758</v>
+        <v>696684</v>
       </c>
       <c r="R75" t="n">
-        <v>6643677</v>
+        <v>6643683</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9020,7 +9015,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9030,7 +9025,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9045,22 +9040,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132821474</v>
+        <v>132830974</v>
       </c>
       <c r="B76" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9087,7 +9082,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9097,14 +9092,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696684</v>
+        <v>696678</v>
       </c>
       <c r="R76" t="n">
-        <v>6643683</v>
+        <v>6643668</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9149,6 +9144,11 @@
           <t>08:54</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9161,12 +9161,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9176,7 +9176,7 @@
         <v>132830928</v>
       </c>
       <c r="B77" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9276,10 +9276,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132830960</v>
+        <v>132830945</v>
       </c>
       <c r="B78" t="n">
-        <v>101326</v>
+        <v>58328</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9287,34 +9287,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696741</v>
+        <v>696784</v>
       </c>
       <c r="R78" t="n">
-        <v>6643703</v>
+        <v>6643729</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9346,7 +9354,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9356,7 +9364,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9383,53 +9391,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132830945</v>
+        <v>132823493</v>
       </c>
       <c r="B79" t="n">
-        <v>58327</v>
+        <v>99119</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696784</v>
+        <v>696964</v>
       </c>
       <c r="R79" t="n">
-        <v>6643729</v>
+        <v>6643823</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9461,7 +9470,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9471,7 +9480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9486,66 +9495,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B80" t="n">
-        <v>99118</v>
+        <v>101327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R80" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,27 +2432,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830977</v>
+        <v>132830947</v>
       </c>
       <c r="B17" t="n">
-        <v>58328</v>
+        <v>57951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2461,24 +2461,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696664</v>
+        <v>696785</v>
       </c>
       <c r="R17" t="n">
-        <v>6643658</v>
+        <v>6643731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2507,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,7 +2517,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,27 +2544,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830947</v>
+        <v>132830977</v>
       </c>
       <c r="B18" t="n">
-        <v>57951</v>
+        <v>58328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2576,21 +2573,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696785</v>
+        <v>696664</v>
       </c>
       <c r="R18" t="n">
-        <v>6643731</v>
+        <v>6643658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,7 +2662,7 @@
         <v>132825468</v>
       </c>
       <c r="B19" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821661</v>
+        <v>132821435</v>
       </c>
       <c r="B20" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2815,10 +2819,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696690</v>
+        <v>696687</v>
       </c>
       <c r="R20" t="n">
-        <v>6643717</v>
+        <v>6643684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,7 +2854,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2864,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,10 +2891,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132821435</v>
+        <v>132821661</v>
       </c>
       <c r="B21" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,11 +2919,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696687</v>
+        <v>696690</v>
       </c>
       <c r="R21" t="n">
-        <v>6643684</v>
+        <v>6643717</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3006,7 +3006,7 @@
         <v>132830954</v>
       </c>
       <c r="B22" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>132830980</v>
       </c>
       <c r="B23" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3217,45 +3217,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132830962</v>
+        <v>132821594</v>
       </c>
       <c r="B24" t="n">
-        <v>101327</v>
+        <v>99121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696727</v>
+        <v>696683</v>
       </c>
       <c r="R24" t="n">
-        <v>6643708</v>
+        <v>6643725</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3297,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,57 +3321,66 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830932</v>
+        <v>132822772</v>
       </c>
       <c r="B25" t="n">
-        <v>101327</v>
+        <v>99121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696970</v>
+        <v>696813</v>
       </c>
       <c r="R25" t="n">
-        <v>6643862</v>
+        <v>6643818</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,57 +3437,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830940</v>
+        <v>132830942</v>
       </c>
       <c r="B26" t="n">
-        <v>101327</v>
+        <v>99121</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696814</v>
+        <v>696776</v>
       </c>
       <c r="R26" t="n">
-        <v>6643811</v>
+        <v>6643778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,45 +3565,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830941</v>
+        <v>132823051</v>
       </c>
       <c r="B27" t="n">
-        <v>101327</v>
+        <v>99121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696790</v>
+        <v>696853</v>
       </c>
       <c r="R27" t="n">
-        <v>6643780</v>
+        <v>6643821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3608,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3633,66 +3669,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132822772</v>
+        <v>132830962</v>
       </c>
       <c r="B28" t="n">
-        <v>99119</v>
+        <v>101329</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696813</v>
+        <v>696727</v>
       </c>
       <c r="R28" t="n">
-        <v>6643818</v>
+        <v>6643708</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3734,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,66 +3776,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830942</v>
+        <v>132830932</v>
       </c>
       <c r="B29" t="n">
-        <v>99119</v>
+        <v>101329</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696776</v>
+        <v>696970</v>
       </c>
       <c r="R29" t="n">
-        <v>6643778</v>
+        <v>6643862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3840,7 +3858,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3868,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,54 +3895,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132823051</v>
+        <v>132830940</v>
       </c>
       <c r="B30" t="n">
-        <v>99119</v>
+        <v>101329</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696853</v>
+        <v>696814</v>
       </c>
       <c r="R30" t="n">
-        <v>6643821</v>
+        <v>6643811</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3966,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3981,66 +3990,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132821594</v>
+        <v>132830941</v>
       </c>
       <c r="B31" t="n">
-        <v>99119</v>
+        <v>101329</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696683</v>
+        <v>696790</v>
       </c>
       <c r="R31" t="n">
-        <v>6643725</v>
+        <v>6643780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,12 +4097,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4224,7 +4224,7 @@
         <v>132830937</v>
       </c>
       <c r="B33" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>132830929</v>
       </c>
       <c r="B34" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132830961</v>
+        <v>132830923</v>
       </c>
       <c r="B36" t="n">
-        <v>99154</v>
+        <v>101329</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,34 +4553,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696729</v>
+        <v>697051</v>
       </c>
       <c r="R36" t="n">
-        <v>6643708</v>
+        <v>6643938</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132830923</v>
+        <v>132830961</v>
       </c>
       <c r="B37" t="n">
-        <v>101327</v>
+        <v>99156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,34 +4660,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697051</v>
+        <v>696729</v>
       </c>
       <c r="R37" t="n">
-        <v>6643938</v>
+        <v>6643708</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4759,7 +4759,7 @@
         <v>132823255</v>
       </c>
       <c r="B38" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>132822951</v>
       </c>
       <c r="B39" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132823172</v>
+        <v>132822662</v>
       </c>
       <c r="B40" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696885</v>
+        <v>696811</v>
       </c>
       <c r="R40" t="n">
         <v>6643816</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5104,10 +5104,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132830915</v>
+        <v>132823172</v>
       </c>
       <c r="B41" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5144,14 +5144,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696686</v>
+        <v>696885</v>
       </c>
       <c r="R41" t="n">
-        <v>6643680</v>
+        <v>6643816</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5208,22 +5208,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132822662</v>
+        <v>132830915</v>
       </c>
       <c r="B42" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5260,14 +5260,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696811</v>
+        <v>696686</v>
       </c>
       <c r="R42" t="n">
-        <v>6643816</v>
+        <v>6643680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5324,12 +5324,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5339,7 +5339,7 @@
         <v>132830925</v>
       </c>
       <c r="B43" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5443,45 +5443,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830936</v>
+        <v>132830956</v>
       </c>
       <c r="B44" t="n">
-        <v>91931</v>
+        <v>99121</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696871</v>
+        <v>696730</v>
       </c>
       <c r="R44" t="n">
-        <v>6643836</v>
+        <v>6643665</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5513,7 +5522,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5523,7 +5532,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5550,50 +5559,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830963</v>
+        <v>132821927</v>
       </c>
       <c r="B45" t="n">
-        <v>57951</v>
+        <v>106247</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696701</v>
+        <v>696722</v>
       </c>
       <c r="R45" t="n">
-        <v>6643708</v>
+        <v>6643677</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,7 +5629,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5635,7 +5639,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5650,22 +5654,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830956</v>
+        <v>132821365</v>
       </c>
       <c r="B46" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5692,7 +5696,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5702,14 +5706,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696730</v>
+        <v>696684</v>
       </c>
       <c r="R46" t="n">
-        <v>6643665</v>
+        <v>6643670</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5741,7 +5745,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5751,7 +5755,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5766,66 +5770,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821365</v>
+        <v>132830934</v>
       </c>
       <c r="B47" t="n">
-        <v>99119</v>
+        <v>101329</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696684</v>
+        <v>696926</v>
       </c>
       <c r="R47" t="n">
-        <v>6643670</v>
+        <v>6643877</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5857,7 +5852,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5867,7 +5862,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5882,57 +5877,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821927</v>
+        <v>132830936</v>
       </c>
       <c r="B48" t="n">
-        <v>106245</v>
+        <v>91933</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696722</v>
+        <v>696871</v>
       </c>
       <c r="R48" t="n">
-        <v>6643677</v>
+        <v>6643836</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5959,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5969,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5989,57 +5984,62 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830934</v>
+        <v>132830963</v>
       </c>
       <c r="B49" t="n">
-        <v>101327</v>
+        <v>57951</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696926</v>
+        <v>696701</v>
       </c>
       <c r="R49" t="n">
-        <v>6643877</v>
+        <v>6643708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6111,7 +6111,7 @@
         <v>132830979</v>
       </c>
       <c r="B50" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>132830943</v>
       </c>
       <c r="B51" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6331,50 +6331,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830911</v>
+        <v>132830927</v>
       </c>
       <c r="B52" t="n">
-        <v>57951</v>
+        <v>99121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696479</v>
+        <v>696972</v>
       </c>
       <c r="R52" t="n">
-        <v>6643760</v>
+        <v>6643904</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6406,7 +6410,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6416,7 +6420,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6443,45 +6447,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830930</v>
+        <v>132822683</v>
       </c>
       <c r="B53" t="n">
-        <v>101327</v>
+        <v>99121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697027</v>
+        <v>696803</v>
       </c>
       <c r="R53" t="n">
-        <v>6643874</v>
+        <v>6643814</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6523,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6538,66 +6551,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830927</v>
+        <v>132830930</v>
       </c>
       <c r="B54" t="n">
-        <v>99119</v>
+        <v>101329</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696972</v>
+        <v>697027</v>
       </c>
       <c r="R54" t="n">
-        <v>6643904</v>
+        <v>6643874</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6633,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6643,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,54 +6670,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132822683</v>
+        <v>132830911</v>
       </c>
       <c r="B55" t="n">
-        <v>99119</v>
+        <v>57951</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696803</v>
+        <v>696479</v>
       </c>
       <c r="R55" t="n">
-        <v>6643814</v>
+        <v>6643760</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,66 +6770,53 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132821892</v>
+        <v>132830931</v>
       </c>
       <c r="B56" t="n">
-        <v>99119</v>
+        <v>91932</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696722</v>
+        <v>697026</v>
       </c>
       <c r="R56" t="n">
-        <v>6643684</v>
+        <v>6643874</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6861,7 +6848,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6871,7 +6858,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6886,12 +6873,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6901,7 +6888,7 @@
         <v>132830935</v>
       </c>
       <c r="B57" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7005,41 +6992,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830931</v>
+        <v>132821892</v>
       </c>
       <c r="B58" t="n">
-        <v>91930</v>
+        <v>99121</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>697026</v>
+        <v>696722</v>
       </c>
       <c r="R58" t="n">
-        <v>6643874</v>
+        <v>6643684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7111,7 +7111,7 @@
         <v>132822271</v>
       </c>
       <c r="B59" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7227,7 +7227,7 @@
         <v>132821521</v>
       </c>
       <c r="B60" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,45 +7340,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132830970</v>
+        <v>132830971</v>
       </c>
       <c r="B61" t="n">
-        <v>101327</v>
+        <v>57951</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696614</v>
+        <v>696622</v>
       </c>
       <c r="R61" t="n">
-        <v>6643745</v>
+        <v>6643679</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7410,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7420,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7447,50 +7452,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830971</v>
+        <v>132830970</v>
       </c>
       <c r="B62" t="n">
-        <v>57951</v>
+        <v>101329</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696622</v>
+        <v>696614</v>
       </c>
       <c r="R62" t="n">
-        <v>6643679</v>
+        <v>6643745</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7562,7 +7562,7 @@
         <v>132821719</v>
       </c>
       <c r="B63" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>132830933</v>
       </c>
       <c r="B64" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132830985</v>
+        <v>132826107</v>
       </c>
       <c r="B65" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696679</v>
+        <v>696530</v>
       </c>
       <c r="R65" t="n">
-        <v>6643623</v>
+        <v>6643699</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7880,12 +7880,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7900,22 +7895,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132826107</v>
+        <v>132830913</v>
       </c>
       <c r="B66" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7942,7 +7937,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7952,14 +7947,14 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696530</v>
+        <v>696702</v>
       </c>
       <c r="R66" t="n">
-        <v>6643699</v>
+        <v>6643704</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7991,7 +7986,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8001,7 +7996,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8016,22 +8011,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132830913</v>
+        <v>132830985</v>
       </c>
       <c r="B67" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8058,7 +8053,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8072,10 +8067,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696702</v>
+        <v>696679</v>
       </c>
       <c r="R67" t="n">
-        <v>6643704</v>
+        <v>6643623</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8107,7 +8102,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8117,7 +8112,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8259,53 +8259,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B69" t="n">
-        <v>58637</v>
+        <v>99121</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R69" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8338,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8348,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8362,66 +8363,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132825569</v>
+        <v>132830964</v>
       </c>
       <c r="B70" t="n">
-        <v>99119</v>
+        <v>58637</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696671</v>
+        <v>696700</v>
       </c>
       <c r="R70" t="n">
-        <v>6643630</v>
+        <v>6643694</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8493,7 +8493,7 @@
         <v>132830946</v>
       </c>
       <c r="B71" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>132822866</v>
       </c>
       <c r="B72" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8722,45 +8722,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132830976</v>
+        <v>132821474</v>
       </c>
       <c r="B73" t="n">
-        <v>101327</v>
+        <v>99121</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696677</v>
+        <v>696684</v>
       </c>
       <c r="R73" t="n">
-        <v>6643661</v>
+        <v>6643683</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8817,57 +8826,66 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830949</v>
+        <v>132830974</v>
       </c>
       <c r="B74" t="n">
-        <v>101327</v>
+        <v>99121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696758</v>
+        <v>696678</v>
       </c>
       <c r="R74" t="n">
-        <v>6643677</v>
+        <v>6643668</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8899,7 +8917,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8909,7 +8927,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8936,54 +8959,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132821474</v>
+        <v>132830976</v>
       </c>
       <c r="B75" t="n">
-        <v>99119</v>
+        <v>101329</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696684</v>
+        <v>696677</v>
       </c>
       <c r="R75" t="n">
-        <v>6643683</v>
+        <v>6643661</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9040,66 +9054,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830974</v>
+        <v>132830949</v>
       </c>
       <c r="B76" t="n">
-        <v>99119</v>
+        <v>101329</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696678</v>
+        <v>696758</v>
       </c>
       <c r="R76" t="n">
-        <v>6643668</v>
+        <v>6643677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9131,7 +9136,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9141,12 +9146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9176,7 +9176,7 @@
         <v>132830928</v>
       </c>
       <c r="B77" t="n">
-        <v>91930</v>
+        <v>91932</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9276,53 +9276,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132830945</v>
+        <v>132823493</v>
       </c>
       <c r="B78" t="n">
-        <v>58328</v>
+        <v>99121</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696784</v>
+        <v>696964</v>
       </c>
       <c r="R78" t="n">
-        <v>6643729</v>
+        <v>6643823</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9354,7 +9355,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9364,7 +9365,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9379,66 +9380,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B79" t="n">
-        <v>99119</v>
+        <v>101329</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R79" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9470,7 +9462,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9480,7 +9472,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9495,22 +9487,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132830960</v>
+        <v>132830945</v>
       </c>
       <c r="B80" t="n">
-        <v>101327</v>
+        <v>58328</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9518,34 +9510,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696741</v>
+        <v>696784</v>
       </c>
       <c r="R80" t="n">
-        <v>6643703</v>
+        <v>6643729</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2662,7 +2662,7 @@
         <v>132825468</v>
       </c>
       <c r="B19" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>132821435</v>
       </c>
       <c r="B20" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>132821661</v>
       </c>
       <c r="B21" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>132830954</v>
       </c>
       <c r="B22" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,45 +3110,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132830980</v>
+        <v>132822772</v>
       </c>
       <c r="B23" t="n">
-        <v>91912</v>
+        <v>99122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696668</v>
+        <v>696813</v>
       </c>
       <c r="R23" t="n">
-        <v>6643646</v>
+        <v>6643818</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3180,7 +3189,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3199,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,22 +3214,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132821594</v>
+        <v>132830942</v>
       </c>
       <c r="B24" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3247,7 +3256,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,14 +3266,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696683</v>
+        <v>696776</v>
       </c>
       <c r="R24" t="n">
-        <v>6643725</v>
+        <v>6643778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3305,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3315,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,22 +3330,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132822772</v>
+        <v>132821594</v>
       </c>
       <c r="B25" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3363,7 +3372,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696813</v>
+        <v>696683</v>
       </c>
       <c r="R25" t="n">
-        <v>6643818</v>
+        <v>6643725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3421,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3431,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3442,17 +3451,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830942</v>
+        <v>132823051</v>
       </c>
       <c r="B26" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,7 +3488,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3489,14 +3498,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696776</v>
+        <v>696853</v>
       </c>
       <c r="R26" t="n">
-        <v>6643778</v>
+        <v>6643821</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3528,7 +3537,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3538,7 +3547,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,66 +3562,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132823051</v>
+        <v>132830962</v>
       </c>
       <c r="B27" t="n">
-        <v>99121</v>
+        <v>101330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696853</v>
+        <v>696727</v>
       </c>
       <c r="R27" t="n">
-        <v>6643821</v>
+        <v>6643708</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,22 +3669,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830962</v>
+        <v>132830932</v>
       </c>
       <c r="B28" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,14 +3712,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696727</v>
+        <v>696970</v>
       </c>
       <c r="R28" t="n">
-        <v>6643708</v>
+        <v>6643862</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,10 +3788,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830932</v>
+        <v>132830940</v>
       </c>
       <c r="B29" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,14 +3819,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696970</v>
+        <v>696814</v>
       </c>
       <c r="R29" t="n">
-        <v>6643862</v>
+        <v>6643811</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132830940</v>
+        <v>132830941</v>
       </c>
       <c r="B30" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696814</v>
+        <v>696790</v>
       </c>
       <c r="R30" t="n">
-        <v>6643811</v>
+        <v>6643780</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4002,32 +4002,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132830941</v>
+        <v>132830980</v>
       </c>
       <c r="B31" t="n">
-        <v>101329</v>
+        <v>91913</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696790</v>
+        <v>696668</v>
       </c>
       <c r="R31" t="n">
-        <v>6643780</v>
+        <v>6643646</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4224,7 +4224,7 @@
         <v>132830937</v>
       </c>
       <c r="B33" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>132830929</v>
       </c>
       <c r="B34" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132830923</v>
+        <v>132830961</v>
       </c>
       <c r="B36" t="n">
-        <v>101329</v>
+        <v>99157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,34 +4553,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697051</v>
+        <v>696729</v>
       </c>
       <c r="R36" t="n">
-        <v>6643938</v>
+        <v>6643708</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132830961</v>
+        <v>132830923</v>
       </c>
       <c r="B37" t="n">
-        <v>99156</v>
+        <v>101330</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,34 +4660,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696729</v>
+        <v>697051</v>
       </c>
       <c r="R37" t="n">
-        <v>6643708</v>
+        <v>6643938</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4759,7 +4759,7 @@
         <v>132823255</v>
       </c>
       <c r="B38" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>132822951</v>
       </c>
       <c r="B39" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>132822662</v>
       </c>
       <c r="B40" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>132823172</v>
       </c>
       <c r="B41" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>132830915</v>
       </c>
       <c r="B42" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>132830925</v>
       </c>
       <c r="B43" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5443,54 +5443,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830956</v>
+        <v>132830936</v>
       </c>
       <c r="B44" t="n">
-        <v>99121</v>
+        <v>91934</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696730</v>
+        <v>696871</v>
       </c>
       <c r="R44" t="n">
-        <v>6643665</v>
+        <v>6643836</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5522,7 +5513,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5532,7 +5523,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5559,45 +5550,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132821927</v>
+        <v>132830956</v>
       </c>
       <c r="B45" t="n">
-        <v>106247</v>
+        <v>99122</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696722</v>
+        <v>696730</v>
       </c>
       <c r="R45" t="n">
-        <v>6643677</v>
+        <v>6643665</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5654,12 +5654,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5669,7 +5669,7 @@
         <v>132821365</v>
       </c>
       <c r="B46" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>132830934</v>
       </c>
       <c r="B47" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5889,10 +5889,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830936</v>
+        <v>132830963</v>
       </c>
       <c r="B48" t="n">
-        <v>91933</v>
+        <v>57951</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,34 +5900,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696871</v>
+        <v>696701</v>
       </c>
       <c r="R48" t="n">
-        <v>6643836</v>
+        <v>6643708</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5959,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5969,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5996,50 +6001,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830963</v>
+        <v>132821927</v>
       </c>
       <c r="B49" t="n">
-        <v>57951</v>
+        <v>106248</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696701</v>
+        <v>696722</v>
       </c>
       <c r="R49" t="n">
-        <v>6643708</v>
+        <v>6643677</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,12 +6096,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6111,7 +6111,7 @@
         <v>132830979</v>
       </c>
       <c r="B50" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>132830943</v>
       </c>
       <c r="B51" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6331,54 +6331,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830927</v>
+        <v>132830911</v>
       </c>
       <c r="B52" t="n">
-        <v>99121</v>
+        <v>57951</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696972</v>
+        <v>696479</v>
       </c>
       <c r="R52" t="n">
-        <v>6643904</v>
+        <v>6643760</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6410,7 +6406,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6420,7 +6416,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6447,10 +6443,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132822683</v>
+        <v>132830927</v>
       </c>
       <c r="B53" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6477,7 +6473,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6487,14 +6483,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696803</v>
+        <v>696972</v>
       </c>
       <c r="R53" t="n">
-        <v>6643814</v>
+        <v>6643904</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6526,7 +6522,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6532,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6551,57 +6547,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830930</v>
+        <v>132822683</v>
       </c>
       <c r="B54" t="n">
-        <v>101329</v>
+        <v>99122</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697027</v>
+        <v>696803</v>
       </c>
       <c r="R54" t="n">
-        <v>6643874</v>
+        <v>6643814</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6633,7 +6638,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6643,7 +6648,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6658,62 +6663,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830911</v>
+        <v>132830930</v>
       </c>
       <c r="B55" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696479</v>
+        <v>697027</v>
       </c>
       <c r="R55" t="n">
-        <v>6643760</v>
+        <v>6643874</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6785,7 +6785,7 @@
         <v>132830931</v>
       </c>
       <c r="B56" t="n">
-        <v>91932</v>
+        <v>91933</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>132830935</v>
       </c>
       <c r="B57" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>132821892</v>
       </c>
       <c r="B58" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>132822271</v>
       </c>
       <c r="B59" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>132821521</v>
       </c>
       <c r="B60" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>132830970</v>
       </c>
       <c r="B62" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>132821719</v>
       </c>
       <c r="B63" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7678,7 +7678,7 @@
         <v>132830933</v>
       </c>
       <c r="B64" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>132826107</v>
       </c>
       <c r="B65" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>132830913</v>
       </c>
       <c r="B66" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>132830985</v>
       </c>
       <c r="B67" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B68" t="n">
-        <v>58498</v>
+        <v>58637</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R68" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8262,7 +8262,7 @@
         <v>132825569</v>
       </c>
       <c r="B69" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8368,17 +8368,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830964</v>
+        <v>132830978</v>
       </c>
       <c r="B70" t="n">
-        <v>58637</v>
+        <v>58498</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8386,16 +8386,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696700</v>
+        <v>696664</v>
       </c>
       <c r="R70" t="n">
-        <v>6643694</v>
+        <v>6643658</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8493,7 +8493,7 @@
         <v>132830946</v>
       </c>
       <c r="B71" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>132822866</v>
       </c>
       <c r="B72" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>132821474</v>
       </c>
       <c r="B73" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>132830974</v>
       </c>
       <c r="B74" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>132830976</v>
       </c>
       <c r="B75" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>132830949</v>
       </c>
       <c r="B76" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>132830928</v>
       </c>
       <c r="B77" t="n">
-        <v>91932</v>
+        <v>91933</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>132823493</v>
       </c>
       <c r="B78" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9392,10 +9392,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132830960</v>
+        <v>132830945</v>
       </c>
       <c r="B79" t="n">
-        <v>101329</v>
+        <v>58328</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9403,34 +9403,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696741</v>
+        <v>696784</v>
       </c>
       <c r="R79" t="n">
-        <v>6643703</v>
+        <v>6643729</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9462,7 +9470,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9472,7 +9480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9499,10 +9507,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132830945</v>
+        <v>132830960</v>
       </c>
       <c r="B80" t="n">
-        <v>58328</v>
+        <v>101330</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9510,42 +9518,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696784</v>
+        <v>696741</v>
       </c>
       <c r="R80" t="n">
-        <v>6643729</v>
+        <v>6643703</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2544,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830977</v>
+        <v>132830954</v>
       </c>
       <c r="B18" t="n">
-        <v>58328</v>
+        <v>101330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,42 +2555,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696664</v>
+        <v>696732</v>
       </c>
       <c r="R18" t="n">
-        <v>6643658</v>
+        <v>6643642</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3003,10 +2995,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830954</v>
+        <v>132830977</v>
       </c>
       <c r="B22" t="n">
-        <v>101330</v>
+        <v>58328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,34 +3006,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696732</v>
+        <v>696664</v>
       </c>
       <c r="R22" t="n">
-        <v>6643642</v>
+        <v>6643658</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830936</v>
+        <v>132830963</v>
       </c>
       <c r="B44" t="n">
-        <v>91934</v>
+        <v>57951</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5454,34 +5454,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696871</v>
+        <v>696701</v>
       </c>
       <c r="R44" t="n">
-        <v>6643836</v>
+        <v>6643708</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5513,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5523,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5782,10 +5787,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830934</v>
+        <v>132821927</v>
       </c>
       <c r="B47" t="n">
-        <v>101330</v>
+        <v>106248</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5793,34 +5798,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696926</v>
+        <v>696722</v>
       </c>
       <c r="R47" t="n">
-        <v>6643877</v>
+        <v>6643677</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5852,7 +5857,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5862,7 +5867,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,62 +5882,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830963</v>
+        <v>132830934</v>
       </c>
       <c r="B48" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696701</v>
+        <v>696926</v>
       </c>
       <c r="R48" t="n">
-        <v>6643708</v>
+        <v>6643877</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,45 +6001,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132821927</v>
+        <v>132830936</v>
       </c>
       <c r="B49" t="n">
-        <v>106248</v>
+        <v>91934</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696722</v>
+        <v>696871</v>
       </c>
       <c r="R49" t="n">
-        <v>6643677</v>
+        <v>6643836</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,12 +6096,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6331,50 +6331,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830911</v>
+        <v>132830927</v>
       </c>
       <c r="B52" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696479</v>
+        <v>696972</v>
       </c>
       <c r="R52" t="n">
-        <v>6643760</v>
+        <v>6643904</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6406,7 +6410,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6416,7 +6420,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6443,7 +6447,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830927</v>
+        <v>132822683</v>
       </c>
       <c r="B53" t="n">
         <v>99122</v>
@@ -6473,7 +6477,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6483,14 +6487,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696972</v>
+        <v>696803</v>
       </c>
       <c r="R53" t="n">
-        <v>6643904</v>
+        <v>6643814</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6522,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6532,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6547,66 +6551,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132822683</v>
+        <v>132830930</v>
       </c>
       <c r="B54" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696803</v>
+        <v>697027</v>
       </c>
       <c r="R54" t="n">
-        <v>6643814</v>
+        <v>6643874</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6638,7 +6633,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6648,7 +6643,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6663,57 +6658,62 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830930</v>
+        <v>132830911</v>
       </c>
       <c r="B55" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697027</v>
+        <v>696479</v>
       </c>
       <c r="R55" t="n">
-        <v>6643874</v>
+        <v>6643760</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6885,45 +6885,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B57" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R57" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6955,7 +6964,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6965,7 +6974,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6980,66 +6989,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132821892</v>
+        <v>132830935</v>
       </c>
       <c r="B58" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696722</v>
+        <v>696897</v>
       </c>
       <c r="R58" t="n">
-        <v>6643684</v>
+        <v>6643810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7452,45 +7452,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B62" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R62" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7522,7 +7531,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7532,7 +7541,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7547,66 +7556,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132821719</v>
+        <v>132830970</v>
       </c>
       <c r="B63" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696709</v>
+        <v>696614</v>
       </c>
       <c r="R63" t="n">
-        <v>6643709</v>
+        <v>6643745</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8259,54 +8259,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132825569</v>
+        <v>132830978</v>
       </c>
       <c r="B69" t="n">
-        <v>99122</v>
+        <v>58498</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696671</v>
+        <v>696664</v>
       </c>
       <c r="R69" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8363,65 +8362,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830978</v>
+        <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>58498</v>
+        <v>99122</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696664</v>
+        <v>696671</v>
       </c>
       <c r="R70" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2544,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830954</v>
+        <v>132830977</v>
       </c>
       <c r="B18" t="n">
-        <v>101330</v>
+        <v>58328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,34 +2555,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696732</v>
+        <v>696664</v>
       </c>
       <c r="R18" t="n">
-        <v>6643642</v>
+        <v>6643658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2995,10 +3003,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830977</v>
+        <v>132830954</v>
       </c>
       <c r="B22" t="n">
-        <v>58328</v>
+        <v>101330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,42 +3014,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696664</v>
+        <v>696732</v>
       </c>
       <c r="R22" t="n">
-        <v>6643658</v>
+        <v>6643642</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,54 +3110,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132822772</v>
+        <v>132830980</v>
       </c>
       <c r="B23" t="n">
-        <v>99122</v>
+        <v>91913</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696813</v>
+        <v>696668</v>
       </c>
       <c r="R23" t="n">
-        <v>6643818</v>
+        <v>6643646</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3189,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3199,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,66 +3205,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132830942</v>
+        <v>132830941</v>
       </c>
       <c r="B24" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696776</v>
+        <v>696790</v>
       </c>
       <c r="R24" t="n">
-        <v>6643778</v>
+        <v>6643780</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,7 +3287,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3315,7 +3297,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3342,54 +3324,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132821594</v>
+        <v>132830932</v>
       </c>
       <c r="B25" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696683</v>
+        <v>696970</v>
       </c>
       <c r="R25" t="n">
-        <v>6643725</v>
+        <v>6643862</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3421,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3431,7 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3446,66 +3419,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132823051</v>
+        <v>132830940</v>
       </c>
       <c r="B26" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696853</v>
+        <v>696814</v>
       </c>
       <c r="R26" t="n">
-        <v>6643821</v>
+        <v>6643811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3547,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3562,12 +3526,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3681,45 +3645,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830932</v>
+        <v>132822772</v>
       </c>
       <c r="B28" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696970</v>
+        <v>696813</v>
       </c>
       <c r="R28" t="n">
-        <v>6643862</v>
+        <v>6643818</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,7 +3724,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3734,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3776,57 +3749,66 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830940</v>
+        <v>132830942</v>
       </c>
       <c r="B29" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696814</v>
+        <v>696776</v>
       </c>
       <c r="R29" t="n">
-        <v>6643811</v>
+        <v>6643778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,7 +3840,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3868,7 +3850,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,45 +3877,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132830941</v>
+        <v>132821594</v>
       </c>
       <c r="B30" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696790</v>
+        <v>696683</v>
       </c>
       <c r="R30" t="n">
-        <v>6643780</v>
+        <v>6643725</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,7 +3956,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3966,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,57 +3981,66 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132830980</v>
+        <v>132823051</v>
       </c>
       <c r="B31" t="n">
-        <v>91913</v>
+        <v>99122</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696668</v>
+        <v>696853</v>
       </c>
       <c r="R31" t="n">
-        <v>6643646</v>
+        <v>6643821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,62 +4097,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132826336</v>
+        <v>132830937</v>
       </c>
       <c r="B32" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696492</v>
+        <v>696837</v>
       </c>
       <c r="R32" t="n">
-        <v>6643764</v>
+        <v>6643803</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4184,7 +4179,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4194,7 +4189,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,19 +4204,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830937</v>
+        <v>132830929</v>
       </c>
       <c r="B33" t="n">
         <v>101330</v>
@@ -4252,14 +4247,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696837</v>
+        <v>697012</v>
       </c>
       <c r="R33" t="n">
-        <v>6643803</v>
+        <v>6643911</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4301,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,7 +4323,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830929</v>
+        <v>132830957</v>
       </c>
       <c r="B34" t="n">
         <v>101330</v>
@@ -4359,14 +4354,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697012</v>
+        <v>696757</v>
       </c>
       <c r="R34" t="n">
-        <v>6643911</v>
+        <v>6643672</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4398,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,45 +4430,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132830957</v>
+        <v>132826336</v>
       </c>
       <c r="B35" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696757</v>
+        <v>696492</v>
       </c>
       <c r="R35" t="n">
-        <v>6643672</v>
+        <v>6643764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4981,61 +4981,52 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132822662</v>
+        <v>132830925</v>
       </c>
       <c r="B40" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696811</v>
+        <v>697028</v>
       </c>
       <c r="R40" t="n">
-        <v>6643816</v>
+        <v>6643921</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5067,7 +5058,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5077,7 +5068,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,19 +5083,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132823172</v>
+        <v>132822662</v>
       </c>
       <c r="B41" t="n">
         <v>99122</v>
@@ -5134,7 +5125,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5148,7 +5139,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696885</v>
+        <v>696811</v>
       </c>
       <c r="R41" t="n">
         <v>6643816</v>
@@ -5183,7 +5174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5193,7 +5184,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5220,7 +5211,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132830915</v>
+        <v>132823172</v>
       </c>
       <c r="B42" t="n">
         <v>99122</v>
@@ -5250,7 +5241,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5260,14 +5251,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696686</v>
+        <v>696885</v>
       </c>
       <c r="R42" t="n">
-        <v>6643680</v>
+        <v>6643816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5299,7 +5290,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5309,7 +5300,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5324,57 +5315,66 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132830925</v>
+        <v>132830915</v>
       </c>
       <c r="B43" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697028</v>
+        <v>696686</v>
       </c>
       <c r="R43" t="n">
-        <v>6643921</v>
+        <v>6643680</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5555,54 +5555,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830956</v>
+        <v>132830936</v>
       </c>
       <c r="B45" t="n">
-        <v>99122</v>
+        <v>91934</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696730</v>
+        <v>696871</v>
       </c>
       <c r="R45" t="n">
-        <v>6643665</v>
+        <v>6643836</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5634,7 +5625,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5644,7 +5635,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5671,7 +5662,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132821365</v>
+        <v>132830956</v>
       </c>
       <c r="B46" t="n">
         <v>99122</v>
@@ -5701,7 +5692,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5711,14 +5702,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696684</v>
+        <v>696730</v>
       </c>
       <c r="R46" t="n">
-        <v>6643670</v>
+        <v>6643665</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5750,7 +5741,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5760,7 +5751,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5775,12 +5766,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5894,45 +5885,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830934</v>
+        <v>132821365</v>
       </c>
       <c r="B48" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696926</v>
+        <v>696684</v>
       </c>
       <c r="R48" t="n">
-        <v>6643877</v>
+        <v>6643670</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5989,44 +5989,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830936</v>
+        <v>132830934</v>
       </c>
       <c r="B49" t="n">
-        <v>91934</v>
+        <v>101330</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696871</v>
+        <v>696926</v>
       </c>
       <c r="R49" t="n">
-        <v>6643836</v>
+        <v>6643877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6331,7 +6331,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830927</v>
+        <v>132822683</v>
       </c>
       <c r="B52" t="n">
         <v>99122</v>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6371,14 +6371,14 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696972</v>
+        <v>696803</v>
       </c>
       <c r="R52" t="n">
-        <v>6643904</v>
+        <v>6643814</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6435,19 +6435,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132822683</v>
+        <v>132830927</v>
       </c>
       <c r="B53" t="n">
         <v>99122</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6487,14 +6487,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696803</v>
+        <v>696972</v>
       </c>
       <c r="R53" t="n">
-        <v>6643814</v>
+        <v>6643904</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6551,12 +6551,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -8259,53 +8259,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830978</v>
+        <v>132825569</v>
       </c>
       <c r="B69" t="n">
-        <v>58498</v>
+        <v>99122</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696664</v>
+        <v>696671</v>
       </c>
       <c r="R69" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8338,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8348,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8362,66 +8363,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132825569</v>
+        <v>132830978</v>
       </c>
       <c r="B70" t="n">
-        <v>99122</v>
+        <v>58498</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696671</v>
+        <v>696664</v>
       </c>
       <c r="R70" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8959,7 +8959,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132830976</v>
+        <v>132830949</v>
       </c>
       <c r="B75" t="n">
         <v>101330</v>
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696677</v>
+        <v>696758</v>
       </c>
       <c r="R75" t="n">
-        <v>6643661</v>
+        <v>6643677</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9066,7 +9066,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830949</v>
+        <v>132830976</v>
       </c>
       <c r="B76" t="n">
         <v>101330</v>
@@ -9101,10 +9101,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696758</v>
+        <v>696677</v>
       </c>
       <c r="R76" t="n">
-        <v>6643677</v>
+        <v>6643661</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5443,38 +5443,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830963</v>
+        <v>132830956</v>
       </c>
       <c r="B44" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5483,10 +5487,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696701</v>
+        <v>696730</v>
       </c>
       <c r="R44" t="n">
-        <v>6643708</v>
+        <v>6643665</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5518,7 +5522,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,7 +5532,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5555,45 +5559,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830936</v>
+        <v>132821927</v>
       </c>
       <c r="B45" t="n">
-        <v>91934</v>
+        <v>106248</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696871</v>
+        <v>696722</v>
       </c>
       <c r="R45" t="n">
-        <v>6643836</v>
+        <v>6643677</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,7 +5629,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5635,7 +5639,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5650,19 +5654,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830956</v>
+        <v>132821365</v>
       </c>
       <c r="B46" t="n">
         <v>99122</v>
@@ -5692,7 +5696,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5702,14 +5706,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696730</v>
+        <v>696684</v>
       </c>
       <c r="R46" t="n">
-        <v>6643665</v>
+        <v>6643670</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5741,7 +5745,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5751,7 +5755,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5766,22 +5770,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821927</v>
+        <v>132830934</v>
       </c>
       <c r="B47" t="n">
-        <v>106248</v>
+        <v>101330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,34 +5793,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696722</v>
+        <v>696926</v>
       </c>
       <c r="R47" t="n">
-        <v>6643677</v>
+        <v>6643877</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5848,7 +5852,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5858,7 +5862,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5873,66 +5877,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821365</v>
+        <v>132830936</v>
       </c>
       <c r="B48" t="n">
-        <v>99122</v>
+        <v>91934</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696684</v>
+        <v>696871</v>
       </c>
       <c r="R48" t="n">
-        <v>6643670</v>
+        <v>6643836</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5959,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5969,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5989,57 +5984,62 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830934</v>
+        <v>132830963</v>
       </c>
       <c r="B49" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696926</v>
+        <v>696701</v>
       </c>
       <c r="R49" t="n">
-        <v>6643877</v>
+        <v>6643708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6331,54 +6331,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132822683</v>
+        <v>132830930</v>
       </c>
       <c r="B52" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696803</v>
+        <v>697027</v>
       </c>
       <c r="R52" t="n">
-        <v>6643814</v>
+        <v>6643874</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6410,7 +6401,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6420,7 +6411,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6435,66 +6426,62 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830927</v>
+        <v>132830911</v>
       </c>
       <c r="B53" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696972</v>
+        <v>696479</v>
       </c>
       <c r="R53" t="n">
-        <v>6643904</v>
+        <v>6643760</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6526,7 +6513,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6523,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6563,45 +6550,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830930</v>
+        <v>132830927</v>
       </c>
       <c r="B54" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697027</v>
+        <v>696972</v>
       </c>
       <c r="R54" t="n">
-        <v>6643874</v>
+        <v>6643904</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6633,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6643,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,50 +6666,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830911</v>
+        <v>132822683</v>
       </c>
       <c r="B55" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696479</v>
+        <v>696803</v>
       </c>
       <c r="R55" t="n">
-        <v>6643760</v>
+        <v>6643814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,12 +6770,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7340,50 +7340,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132830971</v>
+        <v>132821719</v>
       </c>
       <c r="B61" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696622</v>
+        <v>696709</v>
       </c>
       <c r="R61" t="n">
-        <v>6643679</v>
+        <v>6643709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7415,7 +7419,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7429,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7440,66 +7444,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132821719</v>
+        <v>132830971</v>
       </c>
       <c r="B62" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696709</v>
+        <v>696622</v>
       </c>
       <c r="R62" t="n">
-        <v>6643709</v>
+        <v>6643679</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7556,12 +7556,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -9612,6 +9612,129 @@
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>133089120</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99122</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Eklund V om 2 (*knärot* /stjälk/), Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>696529</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6643700</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>AB-Nor-1962</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2544,53 +2544,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830977</v>
+        <v>132825468</v>
       </c>
       <c r="B18" t="n">
-        <v>58328</v>
+        <v>99122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696664</v>
+        <v>696704</v>
       </c>
       <c r="R18" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2623,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2633,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2647,19 +2648,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132825468</v>
+        <v>132821435</v>
       </c>
       <c r="B19" t="n">
         <v>99122</v>
@@ -2689,7 +2690,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2703,10 +2704,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696704</v>
+        <v>696687</v>
       </c>
       <c r="R19" t="n">
-        <v>6643630</v>
+        <v>6643684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,7 +2739,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2748,7 +2749,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2775,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821435</v>
+        <v>132821661</v>
       </c>
       <c r="B20" t="n">
         <v>99122</v>
@@ -2803,11 +2804,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2819,10 +2816,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696687</v>
+        <v>696690</v>
       </c>
       <c r="R20" t="n">
-        <v>6643684</v>
+        <v>6643717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2854,7 +2851,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2864,7 +2861,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,50 +2888,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132821661</v>
+        <v>132830977</v>
       </c>
       <c r="B21" t="n">
-        <v>99122</v>
+        <v>58328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696690</v>
+        <v>696664</v>
       </c>
       <c r="R21" t="n">
-        <v>6643717</v>
+        <v>6643658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,12 +2991,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4988,45 +4988,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132830925</v>
+        <v>132822662</v>
       </c>
       <c r="B40" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697028</v>
+        <v>696811</v>
       </c>
       <c r="R40" t="n">
-        <v>6643921</v>
+        <v>6643816</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5058,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5068,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,19 +5092,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132822662</v>
+        <v>132823172</v>
       </c>
       <c r="B41" t="n">
         <v>99122</v>
@@ -5125,7 +5134,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5139,7 +5148,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696811</v>
+        <v>696885</v>
       </c>
       <c r="R41" t="n">
         <v>6643816</v>
@@ -5174,7 +5183,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5184,7 +5193,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5204,14 +5213,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132823172</v>
+        <v>132830915</v>
       </c>
       <c r="B42" t="n">
         <v>99122</v>
@@ -5241,7 +5250,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5251,14 +5260,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696885</v>
+        <v>696686</v>
       </c>
       <c r="R42" t="n">
-        <v>6643816</v>
+        <v>6643680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5290,7 +5299,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5300,7 +5309,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,66 +5324,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132830915</v>
+        <v>132830925</v>
       </c>
       <c r="B43" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696686</v>
+        <v>697028</v>
       </c>
       <c r="R43" t="n">
-        <v>6643680</v>
+        <v>6643921</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,50 +2432,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830947</v>
+        <v>132825468</v>
       </c>
       <c r="B17" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696785</v>
+        <v>696704</v>
       </c>
       <c r="R17" t="n">
-        <v>6643731</v>
+        <v>6643630</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,7 +2511,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2517,7 +2521,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,19 +2536,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132825468</v>
+        <v>132821435</v>
       </c>
       <c r="B18" t="n">
         <v>99122</v>
@@ -2574,7 +2578,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2588,10 +2592,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696704</v>
+        <v>696687</v>
       </c>
       <c r="R18" t="n">
-        <v>6643630</v>
+        <v>6643684</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,7 +2627,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2633,7 +2637,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,7 +2664,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821435</v>
+        <v>132821661</v>
       </c>
       <c r="B19" t="n">
         <v>99122</v>
@@ -2688,11 +2692,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696687</v>
+        <v>696690</v>
       </c>
       <c r="R19" t="n">
-        <v>6643684</v>
+        <v>6643717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,50 +2776,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821661</v>
+        <v>132830947</v>
       </c>
       <c r="B20" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696690</v>
+        <v>696785</v>
       </c>
       <c r="R20" t="n">
-        <v>6643717</v>
+        <v>6643731</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,12 +2876,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3217,45 +3217,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132830941</v>
+        <v>132822772</v>
       </c>
       <c r="B24" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696790</v>
+        <v>696813</v>
       </c>
       <c r="R24" t="n">
-        <v>6643780</v>
+        <v>6643818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3297,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,57 +3321,66 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830932</v>
+        <v>132823051</v>
       </c>
       <c r="B25" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696970</v>
+        <v>696853</v>
       </c>
       <c r="R25" t="n">
-        <v>6643862</v>
+        <v>6643821</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,19 +3437,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830940</v>
+        <v>132830962</v>
       </c>
       <c r="B26" t="n">
         <v>101330</v>
@@ -3466,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696814</v>
+        <v>696727</v>
       </c>
       <c r="R26" t="n">
-        <v>6643811</v>
+        <v>6643708</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,7 +3556,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830962</v>
+        <v>132830932</v>
       </c>
       <c r="B27" t="n">
         <v>101330</v>
@@ -3569,14 +3587,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696727</v>
+        <v>696970</v>
       </c>
       <c r="R27" t="n">
-        <v>6643708</v>
+        <v>6643862</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3608,7 +3626,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,7 +3636,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,54 +3663,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132822772</v>
+        <v>132830940</v>
       </c>
       <c r="B28" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696813</v>
+        <v>696814</v>
       </c>
       <c r="R28" t="n">
-        <v>6643818</v>
+        <v>6643811</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,7 +3733,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3734,7 +3743,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,66 +3758,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830942</v>
+        <v>132830941</v>
       </c>
       <c r="B29" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696776</v>
+        <v>696790</v>
       </c>
       <c r="R29" t="n">
-        <v>6643778</v>
+        <v>6643780</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3993,7 +3993,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132823051</v>
+        <v>132830942</v>
       </c>
       <c r="B31" t="n">
         <v>99122</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4033,14 +4033,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696853</v>
+        <v>696776</v>
       </c>
       <c r="R31" t="n">
-        <v>6643821</v>
+        <v>6643778</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,57 +4097,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132830937</v>
+        <v>132826336</v>
       </c>
       <c r="B32" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696837</v>
+        <v>696492</v>
       </c>
       <c r="R32" t="n">
-        <v>6643803</v>
+        <v>6643764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,19 +4209,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830929</v>
+        <v>132830937</v>
       </c>
       <c r="B33" t="n">
         <v>101330</v>
@@ -4247,14 +4252,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697012</v>
+        <v>696837</v>
       </c>
       <c r="R33" t="n">
-        <v>6643911</v>
+        <v>6643803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,7 +4291,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4301,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,7 +4328,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830957</v>
+        <v>132830929</v>
       </c>
       <c r="B34" t="n">
         <v>101330</v>
@@ -4354,14 +4359,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696757</v>
+        <v>697012</v>
       </c>
       <c r="R34" t="n">
-        <v>6643672</v>
+        <v>6643911</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,50 +4435,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132826336</v>
+        <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696492</v>
+        <v>696757</v>
       </c>
       <c r="R35" t="n">
-        <v>6643764</v>
+        <v>6643672</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132823255</v>
+        <v>132822951</v>
       </c>
       <c r="B38" t="n">
         <v>99122</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696904</v>
+        <v>696846</v>
       </c>
       <c r="R38" t="n">
-        <v>6643781</v>
+        <v>6643821</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4865,14 +4865,14 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132822951</v>
+        <v>132823255</v>
       </c>
       <c r="B39" t="n">
         <v>99122</v>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696846</v>
+        <v>696904</v>
       </c>
       <c r="R39" t="n">
-        <v>6643821</v>
+        <v>6643781</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4981,14 +4981,14 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132822662</v>
+        <v>132830915</v>
       </c>
       <c r="B40" t="n">
         <v>99122</v>
@@ -5028,14 +5028,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696811</v>
+        <v>696686</v>
       </c>
       <c r="R40" t="n">
-        <v>6643816</v>
+        <v>6643680</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,19 +5092,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132823172</v>
+        <v>132822662</v>
       </c>
       <c r="B41" t="n">
         <v>99122</v>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696885</v>
+        <v>696811</v>
       </c>
       <c r="R41" t="n">
         <v>6643816</v>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132830915</v>
+        <v>132823172</v>
       </c>
       <c r="B42" t="n">
         <v>99122</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5260,14 +5260,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696686</v>
+        <v>696885</v>
       </c>
       <c r="R42" t="n">
-        <v>6643680</v>
+        <v>6643816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5324,12 +5324,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5443,42 +5443,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830956</v>
+        <v>132830963</v>
       </c>
       <c r="B44" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5487,10 +5483,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696730</v>
+        <v>696701</v>
       </c>
       <c r="R44" t="n">
-        <v>6643665</v>
+        <v>6643708</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5522,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5532,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5666,54 +5662,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132821365</v>
+        <v>132830934</v>
       </c>
       <c r="B46" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696684</v>
+        <v>696926</v>
       </c>
       <c r="R46" t="n">
-        <v>6643670</v>
+        <v>6643877</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5745,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5755,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5770,57 +5757,66 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830934</v>
+        <v>132830956</v>
       </c>
       <c r="B47" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696926</v>
+        <v>696730</v>
       </c>
       <c r="R47" t="n">
-        <v>6643877</v>
+        <v>6643665</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5852,7 +5848,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5862,7 +5858,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5889,45 +5885,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830936</v>
+        <v>132821365</v>
       </c>
       <c r="B48" t="n">
-        <v>91934</v>
+        <v>99122</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696871</v>
+        <v>696684</v>
       </c>
       <c r="R48" t="n">
-        <v>6643836</v>
+        <v>6643670</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5959,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5969,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5984,22 +5989,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830963</v>
+        <v>132830936</v>
       </c>
       <c r="B49" t="n">
-        <v>57951</v>
+        <v>91934</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6007,39 +6012,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696701</v>
+        <v>696871</v>
       </c>
       <c r="R49" t="n">
-        <v>6643708</v>
+        <v>6643836</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6108,54 +6108,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132830979</v>
+        <v>132830943</v>
       </c>
       <c r="B50" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696663</v>
+        <v>696778</v>
       </c>
       <c r="R50" t="n">
-        <v>6643658</v>
+        <v>6643770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6187,7 +6178,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6197,7 +6188,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6224,45 +6215,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132830943</v>
+        <v>132830979</v>
       </c>
       <c r="B51" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696778</v>
+        <v>696663</v>
       </c>
       <c r="R51" t="n">
-        <v>6643770</v>
+        <v>6643658</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6331,45 +6331,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830930</v>
+        <v>132830911</v>
       </c>
       <c r="B52" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697027</v>
+        <v>696479</v>
       </c>
       <c r="R52" t="n">
-        <v>6643874</v>
+        <v>6643760</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6401,7 +6406,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6411,7 +6416,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6438,50 +6443,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830911</v>
+        <v>132830930</v>
       </c>
       <c r="B53" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696479</v>
+        <v>697027</v>
       </c>
       <c r="R53" t="n">
-        <v>6643760</v>
+        <v>6643874</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6885,54 +6885,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132821892</v>
+        <v>132830935</v>
       </c>
       <c r="B57" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696722</v>
+        <v>696897</v>
       </c>
       <c r="R57" t="n">
-        <v>6643684</v>
+        <v>6643810</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6964,7 +6955,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6974,7 +6965,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6989,57 +6980,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B58" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R58" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7340,54 +7340,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132821719</v>
+        <v>132830971</v>
       </c>
       <c r="B61" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696709</v>
+        <v>696622</v>
       </c>
       <c r="R61" t="n">
-        <v>6643709</v>
+        <v>6643679</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7419,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7429,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7444,62 +7440,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830971</v>
+        <v>132830970</v>
       </c>
       <c r="B62" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696622</v>
+        <v>696614</v>
       </c>
       <c r="R62" t="n">
-        <v>6643679</v>
+        <v>6643745</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7531,7 +7522,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7541,7 +7532,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7568,45 +7559,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B63" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R63" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132826107</v>
+        <v>132830985</v>
       </c>
       <c r="B65" t="n">
         <v>99122</v>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696530</v>
+        <v>696679</v>
       </c>
       <c r="R65" t="n">
-        <v>6643699</v>
+        <v>6643623</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7880,7 +7880,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7895,12 +7900,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8023,7 +8028,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132830985</v>
+        <v>132826107</v>
       </c>
       <c r="B67" t="n">
         <v>99122</v>
@@ -8053,7 +8058,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8063,14 +8068,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696679</v>
+        <v>696530</v>
       </c>
       <c r="R67" t="n">
-        <v>6643623</v>
+        <v>6643699</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8102,7 +8107,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8112,12 +8117,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,22 +8132,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830964</v>
+        <v>132830978</v>
       </c>
       <c r="B68" t="n">
-        <v>58637</v>
+        <v>58498</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696700</v>
+        <v>696664</v>
       </c>
       <c r="R68" t="n">
-        <v>6643694</v>
+        <v>6643658</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8375,10 +8375,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B70" t="n">
-        <v>58498</v>
+        <v>58637</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8386,16 +8386,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R70" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8722,54 +8722,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132821474</v>
+        <v>132830976</v>
       </c>
       <c r="B73" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696684</v>
+        <v>696677</v>
       </c>
       <c r="R73" t="n">
-        <v>6643683</v>
+        <v>6643661</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8826,12 +8817,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8959,45 +8950,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132830949</v>
+        <v>132821474</v>
       </c>
       <c r="B75" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696758</v>
+        <v>696684</v>
       </c>
       <c r="R75" t="n">
-        <v>6643677</v>
+        <v>6643683</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9054,19 +9054,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830976</v>
+        <v>132830949</v>
       </c>
       <c r="B76" t="n">
         <v>101330</v>
@@ -9101,10 +9101,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696677</v>
+        <v>696758</v>
       </c>
       <c r="R76" t="n">
-        <v>6643661</v>
+        <v>6643677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9276,54 +9276,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B78" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R78" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9355,7 +9346,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9365,7 +9356,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9380,12 +9371,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9507,45 +9498,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132830960</v>
+        <v>132823493</v>
       </c>
       <c r="B80" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696741</v>
+        <v>696964</v>
       </c>
       <c r="R80" t="n">
-        <v>6643703</v>
+        <v>6643823</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,54 +2432,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132825468</v>
+        <v>132830947</v>
       </c>
       <c r="B17" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696704</v>
+        <v>696785</v>
       </c>
       <c r="R17" t="n">
-        <v>6643630</v>
+        <v>6643731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,7 +2507,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2521,7 +2517,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,66 +2532,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132821435</v>
+        <v>132830954</v>
       </c>
       <c r="B18" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696687</v>
+        <v>696732</v>
       </c>
       <c r="R18" t="n">
-        <v>6643684</v>
+        <v>6643642</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2627,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2637,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,19 +2639,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821661</v>
+        <v>132825468</v>
       </c>
       <c r="B19" t="n">
         <v>99122</v>
@@ -2692,7 +2679,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2704,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696690</v>
+        <v>696704</v>
       </c>
       <c r="R19" t="n">
-        <v>6643717</v>
+        <v>6643630</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,7 +2740,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,50 +2767,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132830947</v>
+        <v>132821435</v>
       </c>
       <c r="B20" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696785</v>
+        <v>696687</v>
       </c>
       <c r="R20" t="n">
-        <v>6643731</v>
+        <v>6643684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2851,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2861,7 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,65 +2871,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830977</v>
+        <v>132821661</v>
       </c>
       <c r="B21" t="n">
-        <v>58328</v>
+        <v>99122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696664</v>
+        <v>696690</v>
       </c>
       <c r="R21" t="n">
-        <v>6643658</v>
+        <v>6643717</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,7 +2958,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2976,7 +2968,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,22 +2983,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830954</v>
+        <v>132830977</v>
       </c>
       <c r="B22" t="n">
-        <v>101330</v>
+        <v>58328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,34 +3006,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696732</v>
+        <v>696664</v>
       </c>
       <c r="R22" t="n">
-        <v>6643642</v>
+        <v>6643658</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,32 +3110,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132830980</v>
+        <v>132830962</v>
       </c>
       <c r="B23" t="n">
-        <v>91913</v>
+        <v>101330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696668</v>
+        <v>696727</v>
       </c>
       <c r="R23" t="n">
-        <v>6643646</v>
+        <v>6643708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3217,54 +3217,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132822772</v>
+        <v>132830932</v>
       </c>
       <c r="B24" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696813</v>
+        <v>696970</v>
       </c>
       <c r="R24" t="n">
-        <v>6643818</v>
+        <v>6643862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3287,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3297,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,66 +3312,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132823051</v>
+        <v>132830940</v>
       </c>
       <c r="B25" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696853</v>
+        <v>696814</v>
       </c>
       <c r="R25" t="n">
-        <v>6643821</v>
+        <v>6643811</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3437,19 +3419,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830962</v>
+        <v>132830941</v>
       </c>
       <c r="B26" t="n">
         <v>101330</v>
@@ -3484,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696727</v>
+        <v>696790</v>
       </c>
       <c r="R26" t="n">
-        <v>6643708</v>
+        <v>6643780</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,45 +3538,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830932</v>
+        <v>132822772</v>
       </c>
       <c r="B27" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696970</v>
+        <v>696813</v>
       </c>
       <c r="R27" t="n">
-        <v>6643862</v>
+        <v>6643818</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3626,7 +3617,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3636,7 +3627,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,57 +3642,66 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830940</v>
+        <v>132830942</v>
       </c>
       <c r="B28" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696814</v>
+        <v>696776</v>
       </c>
       <c r="R28" t="n">
-        <v>6643811</v>
+        <v>6643778</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3770,45 +3770,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830941</v>
+        <v>132821594</v>
       </c>
       <c r="B29" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696790</v>
+        <v>696683</v>
       </c>
       <c r="R29" t="n">
-        <v>6643780</v>
+        <v>6643725</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3840,7 +3849,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3859,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3865,19 +3874,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132821594</v>
+        <v>132823051</v>
       </c>
       <c r="B30" t="n">
         <v>99122</v>
@@ -3907,7 +3916,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3921,10 +3930,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696683</v>
+        <v>696853</v>
       </c>
       <c r="R30" t="n">
-        <v>6643725</v>
+        <v>6643821</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3966,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3993,54 +4002,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132830942</v>
+        <v>132830980</v>
       </c>
       <c r="B31" t="n">
-        <v>99122</v>
+        <v>91913</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696776</v>
+        <v>696668</v>
       </c>
       <c r="R31" t="n">
-        <v>6643778</v>
+        <v>6643646</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4756,7 +4756,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132822951</v>
+        <v>132823255</v>
       </c>
       <c r="B38" t="n">
         <v>99122</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696846</v>
+        <v>696904</v>
       </c>
       <c r="R38" t="n">
-        <v>6643821</v>
+        <v>6643781</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4872,7 +4872,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132823255</v>
+        <v>132822951</v>
       </c>
       <c r="B39" t="n">
         <v>99122</v>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696904</v>
+        <v>696846</v>
       </c>
       <c r="R39" t="n">
-        <v>6643781</v>
+        <v>6643821</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4988,7 +4988,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132830915</v>
+        <v>132822662</v>
       </c>
       <c r="B40" t="n">
         <v>99122</v>
@@ -5028,14 +5028,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696686</v>
+        <v>696811</v>
       </c>
       <c r="R40" t="n">
-        <v>6643680</v>
+        <v>6643816</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,19 +5092,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132822662</v>
+        <v>132823172</v>
       </c>
       <c r="B41" t="n">
         <v>99122</v>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696811</v>
+        <v>696885</v>
       </c>
       <c r="R41" t="n">
         <v>6643816</v>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5220,7 +5220,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132823172</v>
+        <v>132830915</v>
       </c>
       <c r="B42" t="n">
         <v>99122</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5260,14 +5260,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696885</v>
+        <v>696686</v>
       </c>
       <c r="R42" t="n">
-        <v>6643816</v>
+        <v>6643680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5324,12 +5324,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5555,45 +5555,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132821927</v>
+        <v>132830936</v>
       </c>
       <c r="B45" t="n">
-        <v>106248</v>
+        <v>91934</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696722</v>
+        <v>696871</v>
       </c>
       <c r="R45" t="n">
-        <v>6643677</v>
+        <v>6643836</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5650,12 +5650,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5885,54 +5885,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821365</v>
+        <v>132821927</v>
       </c>
       <c r="B48" t="n">
-        <v>99122</v>
+        <v>106250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696684</v>
+        <v>696722</v>
       </c>
       <c r="R48" t="n">
-        <v>6643670</v>
+        <v>6643677</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5955,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5965,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,45 +5992,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830936</v>
+        <v>132821365</v>
       </c>
       <c r="B49" t="n">
-        <v>91934</v>
+        <v>99122</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696871</v>
+        <v>696684</v>
       </c>
       <c r="R49" t="n">
-        <v>6643836</v>
+        <v>6643670</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,12 +6096,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6331,50 +6331,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830911</v>
+        <v>132830927</v>
       </c>
       <c r="B52" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696479</v>
+        <v>696972</v>
       </c>
       <c r="R52" t="n">
-        <v>6643760</v>
+        <v>6643904</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6406,7 +6410,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6416,7 +6420,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6443,45 +6447,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830930</v>
+        <v>132822683</v>
       </c>
       <c r="B53" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697027</v>
+        <v>696803</v>
       </c>
       <c r="R53" t="n">
-        <v>6643874</v>
+        <v>6643814</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6523,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6538,66 +6551,62 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830927</v>
+        <v>132830911</v>
       </c>
       <c r="B54" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696972</v>
+        <v>696479</v>
       </c>
       <c r="R54" t="n">
-        <v>6643904</v>
+        <v>6643760</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6638,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6648,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,54 +6675,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132822683</v>
+        <v>132830930</v>
       </c>
       <c r="B55" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696803</v>
+        <v>697027</v>
       </c>
       <c r="R55" t="n">
-        <v>6643814</v>
+        <v>6643874</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,53 +6770,66 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132830931</v>
+        <v>132821892</v>
       </c>
       <c r="B56" t="n">
-        <v>91933</v>
+        <v>99122</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697026</v>
+        <v>696722</v>
       </c>
       <c r="R56" t="n">
-        <v>6643874</v>
+        <v>6643684</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6848,7 +6861,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6858,7 +6871,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6873,46 +6886,42 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830935</v>
+        <v>132830931</v>
       </c>
       <c r="B57" t="n">
-        <v>101330</v>
+        <v>91933</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6920,10 +6929,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696897</v>
+        <v>697026</v>
       </c>
       <c r="R57" t="n">
-        <v>6643810</v>
+        <v>6643874</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6955,7 +6964,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6965,7 +6974,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6992,54 +7001,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132821892</v>
+        <v>132830935</v>
       </c>
       <c r="B58" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696722</v>
+        <v>696897</v>
       </c>
       <c r="R58" t="n">
-        <v>6643684</v>
+        <v>6643810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7340,50 +7340,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132830971</v>
+        <v>132830970</v>
       </c>
       <c r="B61" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696622</v>
+        <v>696614</v>
       </c>
       <c r="R61" t="n">
-        <v>6643679</v>
+        <v>6643745</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7415,7 +7410,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7420,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7452,45 +7447,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B62" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R62" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7522,7 +7526,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7532,7 +7536,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7547,66 +7551,62 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132821719</v>
+        <v>132830971</v>
       </c>
       <c r="B63" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696709</v>
+        <v>696622</v>
       </c>
       <c r="R63" t="n">
-        <v>6643709</v>
+        <v>6643679</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132830985</v>
+        <v>132826107</v>
       </c>
       <c r="B65" t="n">
         <v>99122</v>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696679</v>
+        <v>696530</v>
       </c>
       <c r="R65" t="n">
-        <v>6643623</v>
+        <v>6643699</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7880,12 +7880,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7900,12 +7895,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8028,7 +8023,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132826107</v>
+        <v>132830985</v>
       </c>
       <c r="B67" t="n">
         <v>99122</v>
@@ -8058,7 +8053,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8068,14 +8063,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696530</v>
+        <v>696679</v>
       </c>
       <c r="R67" t="n">
-        <v>6643699</v>
+        <v>6643623</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8107,7 +8102,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8117,7 +8112,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,12 +8132,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8259,54 +8259,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132825569</v>
+        <v>132830964</v>
       </c>
       <c r="B69" t="n">
-        <v>99122</v>
+        <v>58637</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696671</v>
+        <v>696700</v>
       </c>
       <c r="R69" t="n">
-        <v>6643630</v>
+        <v>6643694</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8363,65 +8362,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>58637</v>
+        <v>99122</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R70" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8829,54 +8829,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830974</v>
+        <v>132830949</v>
       </c>
       <c r="B74" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696678</v>
+        <v>696758</v>
       </c>
       <c r="R74" t="n">
-        <v>6643668</v>
+        <v>6643677</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8908,7 +8899,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8918,12 +8909,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9066,45 +9052,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830949</v>
+        <v>132830974</v>
       </c>
       <c r="B76" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696758</v>
+        <v>696678</v>
       </c>
       <c r="R76" t="n">
-        <v>6643677</v>
+        <v>6643668</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9136,7 +9131,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9146,7 +9141,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9276,10 +9276,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132830960</v>
+        <v>132830945</v>
       </c>
       <c r="B78" t="n">
-        <v>101330</v>
+        <v>58328</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9287,34 +9287,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696741</v>
+        <v>696784</v>
       </c>
       <c r="R78" t="n">
-        <v>6643703</v>
+        <v>6643729</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9346,7 +9354,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9356,7 +9364,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9383,53 +9391,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132830945</v>
+        <v>132823493</v>
       </c>
       <c r="B79" t="n">
-        <v>58328</v>
+        <v>99122</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696784</v>
+        <v>696964</v>
       </c>
       <c r="R79" t="n">
-        <v>6643729</v>
+        <v>6643823</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9461,7 +9470,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9471,7 +9480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9486,66 +9495,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B80" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R80" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2544,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830954</v>
+        <v>132830977</v>
       </c>
       <c r="B18" t="n">
-        <v>101330</v>
+        <v>58328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,34 +2555,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696732</v>
+        <v>696664</v>
       </c>
       <c r="R18" t="n">
-        <v>6643642</v>
+        <v>6643658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,54 +2659,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132825468</v>
+        <v>132830954</v>
       </c>
       <c r="B19" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696704</v>
+        <v>696732</v>
       </c>
       <c r="R19" t="n">
-        <v>6643630</v>
+        <v>6643642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2740,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,19 +2754,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821435</v>
+        <v>132825468</v>
       </c>
       <c r="B20" t="n">
         <v>99122</v>
@@ -2797,7 +2796,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2811,10 +2810,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696687</v>
+        <v>696704</v>
       </c>
       <c r="R20" t="n">
-        <v>6643684</v>
+        <v>6643630</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,7 +2855,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,7 +2882,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132821661</v>
+        <v>132821435</v>
       </c>
       <c r="B21" t="n">
         <v>99122</v>
@@ -2911,7 +2910,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2923,10 +2926,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696690</v>
+        <v>696687</v>
       </c>
       <c r="R21" t="n">
-        <v>6643717</v>
+        <v>6643684</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2968,7 +2971,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,53 +2998,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830977</v>
+        <v>132821661</v>
       </c>
       <c r="B22" t="n">
-        <v>58328</v>
+        <v>99122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696664</v>
+        <v>696690</v>
       </c>
       <c r="R22" t="n">
-        <v>6643658</v>
+        <v>6643717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,12 +3098,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4109,50 +4109,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132826336</v>
+        <v>132830937</v>
       </c>
       <c r="B32" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696492</v>
+        <v>696837</v>
       </c>
       <c r="R32" t="n">
-        <v>6643764</v>
+        <v>6643803</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4184,7 +4179,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4194,7 +4189,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,19 +4204,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830937</v>
+        <v>132830929</v>
       </c>
       <c r="B33" t="n">
         <v>101330</v>
@@ -4252,14 +4247,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696837</v>
+        <v>697012</v>
       </c>
       <c r="R33" t="n">
-        <v>6643803</v>
+        <v>6643911</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4301,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,7 +4323,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830929</v>
+        <v>132830957</v>
       </c>
       <c r="B34" t="n">
         <v>101330</v>
@@ -4359,14 +4354,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697012</v>
+        <v>696757</v>
       </c>
       <c r="R34" t="n">
-        <v>6643911</v>
+        <v>6643672</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4398,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,45 +4430,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132830957</v>
+        <v>132826336</v>
       </c>
       <c r="B35" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696757</v>
+        <v>696492</v>
       </c>
       <c r="R35" t="n">
-        <v>6643672</v>
+        <v>6643764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4988,54 +4988,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132822662</v>
+        <v>132830925</v>
       </c>
       <c r="B40" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696811</v>
+        <v>697028</v>
       </c>
       <c r="R40" t="n">
-        <v>6643816</v>
+        <v>6643921</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5067,7 +5058,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5077,7 +5068,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,19 +5083,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132823172</v>
+        <v>132822662</v>
       </c>
       <c r="B41" t="n">
         <v>99122</v>
@@ -5134,7 +5125,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5148,7 +5139,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696885</v>
+        <v>696811</v>
       </c>
       <c r="R41" t="n">
         <v>6643816</v>
@@ -5183,7 +5174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5193,7 +5184,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5220,7 +5211,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132830915</v>
+        <v>132823172</v>
       </c>
       <c r="B42" t="n">
         <v>99122</v>
@@ -5250,7 +5241,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5260,14 +5251,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696686</v>
+        <v>696885</v>
       </c>
       <c r="R42" t="n">
-        <v>6643680</v>
+        <v>6643816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5299,7 +5290,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5309,7 +5300,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5324,57 +5315,66 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132830925</v>
+        <v>132830915</v>
       </c>
       <c r="B43" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697028</v>
+        <v>696686</v>
       </c>
       <c r="R43" t="n">
-        <v>6643921</v>
+        <v>6643680</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5443,50 +5443,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830963</v>
+        <v>132830934</v>
       </c>
       <c r="B44" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696701</v>
+        <v>696926</v>
       </c>
       <c r="R44" t="n">
-        <v>6643708</v>
+        <v>6643877</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5518,7 +5513,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,7 +5523,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5662,45 +5657,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830934</v>
+        <v>132830963</v>
       </c>
       <c r="B46" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696926</v>
+        <v>696701</v>
       </c>
       <c r="R46" t="n">
-        <v>6643877</v>
+        <v>6643708</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6331,54 +6331,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830927</v>
+        <v>132830911</v>
       </c>
       <c r="B52" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696972</v>
+        <v>696479</v>
       </c>
       <c r="R52" t="n">
-        <v>6643904</v>
+        <v>6643760</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6410,7 +6406,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6420,7 +6416,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6447,54 +6443,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132822683</v>
+        <v>132830930</v>
       </c>
       <c r="B53" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696803</v>
+        <v>697027</v>
       </c>
       <c r="R53" t="n">
-        <v>6643814</v>
+        <v>6643874</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6526,7 +6513,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6523,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6551,62 +6538,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830911</v>
+        <v>132830927</v>
       </c>
       <c r="B54" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696479</v>
+        <v>696972</v>
       </c>
       <c r="R54" t="n">
-        <v>6643760</v>
+        <v>6643904</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6638,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6648,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6675,45 +6666,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830930</v>
+        <v>132822683</v>
       </c>
       <c r="B55" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697027</v>
+        <v>696803</v>
       </c>
       <c r="R55" t="n">
-        <v>6643874</v>
+        <v>6643814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,66 +6770,53 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132821892</v>
+        <v>132830931</v>
       </c>
       <c r="B56" t="n">
-        <v>99122</v>
+        <v>91933</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696722</v>
+        <v>697026</v>
       </c>
       <c r="R56" t="n">
-        <v>6643684</v>
+        <v>6643874</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6861,7 +6848,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6871,7 +6858,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6886,53 +6873,66 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830931</v>
+        <v>132821892</v>
       </c>
       <c r="B57" t="n">
-        <v>91933</v>
+        <v>99122</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697026</v>
+        <v>696722</v>
       </c>
       <c r="R57" t="n">
-        <v>6643874</v>
+        <v>6643684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6989,12 +6989,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7340,45 +7340,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B61" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R61" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7410,7 +7419,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7420,7 +7429,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7435,66 +7444,62 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132821719</v>
+        <v>132830971</v>
       </c>
       <c r="B62" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696709</v>
+        <v>696622</v>
       </c>
       <c r="R62" t="n">
-        <v>6643709</v>
+        <v>6643679</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7526,7 +7531,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7536,7 +7541,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7551,62 +7556,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830971</v>
+        <v>132830970</v>
       </c>
       <c r="B63" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696622</v>
+        <v>696614</v>
       </c>
       <c r="R63" t="n">
-        <v>6643679</v>
+        <v>6643745</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9391,54 +9391,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B79" t="n">
-        <v>99122</v>
+        <v>101330</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R79" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9470,7 +9461,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9480,7 +9471,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9495,57 +9486,66 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132830960</v>
+        <v>132823493</v>
       </c>
       <c r="B80" t="n">
-        <v>101330</v>
+        <v>99122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696741</v>
+        <v>696964</v>
       </c>
       <c r="R80" t="n">
-        <v>6643703</v>
+        <v>6643823</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9617,7 +9617,7 @@
         <v>133089120</v>
       </c>
       <c r="B81" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,50 +2432,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830947</v>
+        <v>132825468</v>
       </c>
       <c r="B17" t="n">
-        <v>57951</v>
+        <v>99125</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696785</v>
+        <v>696704</v>
       </c>
       <c r="R17" t="n">
-        <v>6643731</v>
+        <v>6643630</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,7 +2511,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2517,7 +2521,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,65 +2536,66 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830977</v>
+        <v>132821435</v>
       </c>
       <c r="B18" t="n">
-        <v>58328</v>
+        <v>99125</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696664</v>
+        <v>696687</v>
       </c>
       <c r="R18" t="n">
-        <v>6643658</v>
+        <v>6643684</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2627,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2637,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2647,57 +2652,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132830954</v>
+        <v>132821661</v>
       </c>
       <c r="B19" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696732</v>
+        <v>696690</v>
       </c>
       <c r="R19" t="n">
-        <v>6643642</v>
+        <v>6643717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2739,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2749,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,66 +2764,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132825468</v>
+        <v>132830954</v>
       </c>
       <c r="B20" t="n">
-        <v>99122</v>
+        <v>101333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696704</v>
+        <v>696732</v>
       </c>
       <c r="R20" t="n">
-        <v>6643630</v>
+        <v>6643642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,7 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,66 +2871,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132821435</v>
+        <v>132830947</v>
       </c>
       <c r="B21" t="n">
-        <v>99122</v>
+        <v>57954</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696687</v>
+        <v>696785</v>
       </c>
       <c r="R21" t="n">
-        <v>6643684</v>
+        <v>6643731</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,7 +2958,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2968,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,62 +2983,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132821661</v>
+        <v>132830977</v>
       </c>
       <c r="B22" t="n">
-        <v>99122</v>
+        <v>58331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696690</v>
+        <v>696664</v>
       </c>
       <c r="R22" t="n">
-        <v>6643717</v>
+        <v>6643658</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,57 +3098,66 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132830962</v>
+        <v>132822772</v>
       </c>
       <c r="B23" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696727</v>
+        <v>696813</v>
       </c>
       <c r="R23" t="n">
-        <v>6643708</v>
+        <v>6643818</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3180,7 +3189,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3199,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,57 +3214,66 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132830932</v>
+        <v>132830942</v>
       </c>
       <c r="B24" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696970</v>
+        <v>696776</v>
       </c>
       <c r="R24" t="n">
-        <v>6643862</v>
+        <v>6643778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,7 +3305,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3297,7 +3315,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3324,45 +3342,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830940</v>
+        <v>132821594</v>
       </c>
       <c r="B25" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696814</v>
+        <v>696683</v>
       </c>
       <c r="R25" t="n">
-        <v>6643811</v>
+        <v>6643725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3421,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3431,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,57 +3446,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830941</v>
+        <v>132823051</v>
       </c>
       <c r="B26" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696790</v>
+        <v>696853</v>
       </c>
       <c r="R26" t="n">
-        <v>6643780</v>
+        <v>6643821</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3537,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3547,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,66 +3562,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132822772</v>
+        <v>132830980</v>
       </c>
       <c r="B27" t="n">
-        <v>99122</v>
+        <v>91916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696813</v>
+        <v>696668</v>
       </c>
       <c r="R27" t="n">
-        <v>6643818</v>
+        <v>6643646</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3617,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3627,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3642,66 +3669,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830942</v>
+        <v>132830962</v>
       </c>
       <c r="B28" t="n">
-        <v>99122</v>
+        <v>101333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696776</v>
+        <v>696727</v>
       </c>
       <c r="R28" t="n">
-        <v>6643778</v>
+        <v>6643708</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3733,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3743,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3770,54 +3788,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132821594</v>
+        <v>132830932</v>
       </c>
       <c r="B29" t="n">
-        <v>99122</v>
+        <v>101333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696683</v>
+        <v>696970</v>
       </c>
       <c r="R29" t="n">
-        <v>6643725</v>
+        <v>6643862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3849,7 +3858,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3859,7 +3868,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3874,66 +3883,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132823051</v>
+        <v>132830940</v>
       </c>
       <c r="B30" t="n">
-        <v>99122</v>
+        <v>101333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696853</v>
+        <v>696814</v>
       </c>
       <c r="R30" t="n">
-        <v>6643821</v>
+        <v>6643811</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,44 +3990,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132830980</v>
+        <v>132830941</v>
       </c>
       <c r="B31" t="n">
-        <v>91913</v>
+        <v>101333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4037,10 +4037,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696668</v>
+        <v>696790</v>
       </c>
       <c r="R31" t="n">
-        <v>6643646</v>
+        <v>6643780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,45 +4109,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132830937</v>
+        <v>132826336</v>
       </c>
       <c r="B32" t="n">
-        <v>101330</v>
+        <v>57954</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696837</v>
+        <v>696492</v>
       </c>
       <c r="R32" t="n">
-        <v>6643803</v>
+        <v>6643764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,22 +4209,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830929</v>
+        <v>132830937</v>
       </c>
       <c r="B33" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4247,14 +4252,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697012</v>
+        <v>696837</v>
       </c>
       <c r="R33" t="n">
-        <v>6643911</v>
+        <v>6643803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,7 +4291,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4301,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,10 +4328,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830957</v>
+        <v>132830929</v>
       </c>
       <c r="B34" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,14 +4359,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696757</v>
+        <v>697012</v>
       </c>
       <c r="R34" t="n">
-        <v>6643672</v>
+        <v>6643911</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,50 +4435,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132826336</v>
+        <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>57951</v>
+        <v>101333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696492</v>
+        <v>696757</v>
       </c>
       <c r="R35" t="n">
-        <v>6643764</v>
+        <v>6643672</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
         <v>132830961</v>
       </c>
       <c r="B36" t="n">
-        <v>99157</v>
+        <v>99160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>132830923</v>
       </c>
       <c r="B37" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>132823255</v>
       </c>
       <c r="B38" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>132822951</v>
       </c>
       <c r="B39" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,45 +4988,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132830925</v>
+        <v>132822662</v>
       </c>
       <c r="B40" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697028</v>
+        <v>696811</v>
       </c>
       <c r="R40" t="n">
-        <v>6643921</v>
+        <v>6643816</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5058,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5068,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,22 +5092,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132822662</v>
+        <v>132823172</v>
       </c>
       <c r="B41" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5125,7 +5134,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5139,7 +5148,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696811</v>
+        <v>696885</v>
       </c>
       <c r="R41" t="n">
         <v>6643816</v>
@@ -5174,7 +5183,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5184,7 +5193,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5211,10 +5220,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132823172</v>
+        <v>132830915</v>
       </c>
       <c r="B42" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5241,7 +5250,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5251,14 +5260,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696885</v>
+        <v>696686</v>
       </c>
       <c r="R42" t="n">
-        <v>6643816</v>
+        <v>6643680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5290,7 +5299,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5300,7 +5309,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,66 +5324,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132830915</v>
+        <v>132830925</v>
       </c>
       <c r="B43" t="n">
-        <v>99122</v>
+        <v>101333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696686</v>
+        <v>697028</v>
       </c>
       <c r="R43" t="n">
-        <v>6643680</v>
+        <v>6643921</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5443,32 +5443,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830934</v>
+        <v>132830936</v>
       </c>
       <c r="B44" t="n">
-        <v>101330</v>
+        <v>91937</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696926</v>
+        <v>696871</v>
       </c>
       <c r="R44" t="n">
-        <v>6643877</v>
+        <v>6643836</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5550,45 +5550,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830936</v>
+        <v>132830956</v>
       </c>
       <c r="B45" t="n">
-        <v>91934</v>
+        <v>99125</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696871</v>
+        <v>696730</v>
       </c>
       <c r="R45" t="n">
-        <v>6643836</v>
+        <v>6643665</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5620,7 +5629,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5639,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5657,50 +5666,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830963</v>
+        <v>132821927</v>
       </c>
       <c r="B46" t="n">
-        <v>57951</v>
+        <v>106253</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696701</v>
+        <v>696722</v>
       </c>
       <c r="R46" t="n">
-        <v>6643708</v>
+        <v>6643677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,7 +5736,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5746,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5757,22 +5761,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830956</v>
+        <v>132821365</v>
       </c>
       <c r="B47" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5799,7 +5803,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5809,14 +5813,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696730</v>
+        <v>696684</v>
       </c>
       <c r="R47" t="n">
-        <v>6643665</v>
+        <v>6643670</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5848,7 +5852,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5858,7 +5862,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5873,22 +5877,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821927</v>
+        <v>132830934</v>
       </c>
       <c r="B48" t="n">
-        <v>106250</v>
+        <v>101333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,34 +5900,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696722</v>
+        <v>696926</v>
       </c>
       <c r="R48" t="n">
-        <v>6643677</v>
+        <v>6643877</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5955,7 +5959,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5965,7 +5969,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,66 +5984,62 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132821365</v>
+        <v>132830963</v>
       </c>
       <c r="B49" t="n">
-        <v>99122</v>
+        <v>57954</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696684</v>
+        <v>696701</v>
       </c>
       <c r="R49" t="n">
-        <v>6643670</v>
+        <v>6643708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,12 +6096,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6111,7 +6111,7 @@
         <v>132830943</v>
       </c>
       <c r="B50" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>132830979</v>
       </c>
       <c r="B51" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>132830911</v>
       </c>
       <c r="B52" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6443,45 +6443,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830930</v>
+        <v>132830927</v>
       </c>
       <c r="B53" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697027</v>
+        <v>696972</v>
       </c>
       <c r="R53" t="n">
-        <v>6643874</v>
+        <v>6643904</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,7 +6522,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6523,7 +6532,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6550,10 +6559,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830927</v>
+        <v>132822683</v>
       </c>
       <c r="B54" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6580,7 +6589,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6590,14 +6599,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696972</v>
+        <v>696803</v>
       </c>
       <c r="R54" t="n">
-        <v>6643904</v>
+        <v>6643814</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6638,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6648,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6654,66 +6663,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132822683</v>
+        <v>132830930</v>
       </c>
       <c r="B55" t="n">
-        <v>99122</v>
+        <v>101333</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696803</v>
+        <v>697027</v>
       </c>
       <c r="R55" t="n">
-        <v>6643814</v>
+        <v>6643874</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,12 +6770,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6785,7 +6785,7 @@
         <v>132830931</v>
       </c>
       <c r="B56" t="n">
-        <v>91933</v>
+        <v>91936</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>132821892</v>
       </c>
       <c r="B57" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>132830935</v>
       </c>
       <c r="B58" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>132822271</v>
       </c>
       <c r="B59" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>132821521</v>
       </c>
       <c r="B60" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>132821719</v>
       </c>
       <c r="B61" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7456,50 +7456,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830971</v>
+        <v>132830970</v>
       </c>
       <c r="B62" t="n">
-        <v>57951</v>
+        <v>101333</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696622</v>
+        <v>696614</v>
       </c>
       <c r="R62" t="n">
-        <v>6643679</v>
+        <v>6643745</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7531,7 +7526,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7541,7 +7536,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7568,45 +7563,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830970</v>
+        <v>132830971</v>
       </c>
       <c r="B63" t="n">
-        <v>101330</v>
+        <v>57954</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696614</v>
+        <v>696622</v>
       </c>
       <c r="R63" t="n">
-        <v>6643745</v>
+        <v>6643679</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7678,7 +7678,7 @@
         <v>132830933</v>
       </c>
       <c r="B64" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>132826107</v>
       </c>
       <c r="B65" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>132830913</v>
       </c>
       <c r="B66" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>132830985</v>
       </c>
       <c r="B67" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B68" t="n">
-        <v>58498</v>
+        <v>58640</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R68" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,53 +8259,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B69" t="n">
-        <v>58637</v>
+        <v>99125</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R69" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8338,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8348,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8362,66 +8363,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132825569</v>
+        <v>132830978</v>
       </c>
       <c r="B70" t="n">
-        <v>99122</v>
+        <v>58501</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696671</v>
+        <v>696664</v>
       </c>
       <c r="R70" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8493,7 +8493,7 @@
         <v>132830946</v>
       </c>
       <c r="B71" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>132822866</v>
       </c>
       <c r="B72" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8722,45 +8722,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132830976</v>
+        <v>132821474</v>
       </c>
       <c r="B73" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696677</v>
+        <v>696684</v>
       </c>
       <c r="R73" t="n">
-        <v>6643661</v>
+        <v>6643683</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8817,57 +8826,66 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830949</v>
+        <v>132830974</v>
       </c>
       <c r="B74" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696758</v>
+        <v>696678</v>
       </c>
       <c r="R74" t="n">
-        <v>6643677</v>
+        <v>6643668</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8899,7 +8917,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8909,7 +8927,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8936,54 +8959,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132821474</v>
+        <v>132830976</v>
       </c>
       <c r="B75" t="n">
-        <v>99122</v>
+        <v>101333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696684</v>
+        <v>696677</v>
       </c>
       <c r="R75" t="n">
-        <v>6643683</v>
+        <v>6643661</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9040,66 +9054,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830974</v>
+        <v>132830949</v>
       </c>
       <c r="B76" t="n">
-        <v>99122</v>
+        <v>101333</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696678</v>
+        <v>696758</v>
       </c>
       <c r="R76" t="n">
-        <v>6643668</v>
+        <v>6643677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9131,7 +9136,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9141,12 +9146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9176,7 +9176,7 @@
         <v>132830928</v>
       </c>
       <c r="B77" t="n">
-        <v>91933</v>
+        <v>91936</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>132830945</v>
       </c>
       <c r="B78" t="n">
-        <v>58328</v>
+        <v>58331</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9391,45 +9391,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132830960</v>
+        <v>132823493</v>
       </c>
       <c r="B79" t="n">
-        <v>101330</v>
+        <v>99125</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696741</v>
+        <v>696964</v>
       </c>
       <c r="R79" t="n">
-        <v>6643703</v>
+        <v>6643823</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9461,7 +9470,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9471,7 +9480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9486,66 +9495,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B80" t="n">
-        <v>99122</v>
+        <v>101333</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R80" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,54 +2432,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132825468</v>
+        <v>132830954</v>
       </c>
       <c r="B17" t="n">
-        <v>99125</v>
+        <v>101333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696704</v>
+        <v>696732</v>
       </c>
       <c r="R17" t="n">
-        <v>6643630</v>
+        <v>6643642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,7 +2502,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2521,7 +2512,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,19 +2527,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132821435</v>
+        <v>132825468</v>
       </c>
       <c r="B18" t="n">
         <v>99125</v>
@@ -2578,7 +2569,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2592,10 +2583,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696687</v>
+        <v>696704</v>
       </c>
       <c r="R18" t="n">
-        <v>6643684</v>
+        <v>6643630</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2627,7 +2618,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2637,7 +2628,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,7 +2655,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821661</v>
+        <v>132821435</v>
       </c>
       <c r="B19" t="n">
         <v>99125</v>
@@ -2692,7 +2683,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2704,10 +2699,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696690</v>
+        <v>696687</v>
       </c>
       <c r="R19" t="n">
-        <v>6643717</v>
+        <v>6643684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,7 +2734,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,7 +2744,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,45 +2771,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132830954</v>
+        <v>132821661</v>
       </c>
       <c r="B20" t="n">
-        <v>101333</v>
+        <v>99125</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696732</v>
+        <v>696690</v>
       </c>
       <c r="R20" t="n">
-        <v>6643642</v>
+        <v>6643717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2871,39 +2871,39 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830947</v>
+        <v>132830977</v>
       </c>
       <c r="B21" t="n">
-        <v>57954</v>
+        <v>58331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2912,21 +2912,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696785</v>
+        <v>696664</v>
       </c>
       <c r="R21" t="n">
-        <v>6643731</v>
+        <v>6643658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2968,7 +2971,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,27 +2998,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830977</v>
+        <v>132830947</v>
       </c>
       <c r="B22" t="n">
-        <v>58331</v>
+        <v>57954</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3024,24 +3027,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696664</v>
+        <v>696785</v>
       </c>
       <c r="R22" t="n">
-        <v>6643658</v>
+        <v>6643731</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,54 +3110,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132822772</v>
+        <v>132830980</v>
       </c>
       <c r="B23" t="n">
-        <v>99125</v>
+        <v>91916</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696813</v>
+        <v>696668</v>
       </c>
       <c r="R23" t="n">
-        <v>6643818</v>
+        <v>6643646</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3189,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3199,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,19 +3205,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132830942</v>
+        <v>132822772</v>
       </c>
       <c r="B24" t="n">
         <v>99125</v>
@@ -3256,7 +3247,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3266,14 +3257,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696776</v>
+        <v>696813</v>
       </c>
       <c r="R24" t="n">
-        <v>6643778</v>
+        <v>6643818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3315,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,19 +3321,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132821594</v>
+        <v>132830942</v>
       </c>
       <c r="B25" t="n">
         <v>99125</v>
@@ -3372,7 +3363,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3382,14 +3373,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696683</v>
+        <v>696776</v>
       </c>
       <c r="R25" t="n">
-        <v>6643725</v>
+        <v>6643778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3421,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3431,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3446,19 +3437,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132823051</v>
+        <v>132821594</v>
       </c>
       <c r="B26" t="n">
         <v>99125</v>
@@ -3488,7 +3479,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3502,10 +3493,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696853</v>
+        <v>696683</v>
       </c>
       <c r="R26" t="n">
-        <v>6643821</v>
+        <v>6643725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3547,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3574,45 +3565,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830980</v>
+        <v>132823051</v>
       </c>
       <c r="B27" t="n">
-        <v>91916</v>
+        <v>99125</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696668</v>
+        <v>696853</v>
       </c>
       <c r="R27" t="n">
-        <v>6643646</v>
+        <v>6643821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,12 +3669,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132830961</v>
+        <v>132830923</v>
       </c>
       <c r="B36" t="n">
-        <v>99160</v>
+        <v>101333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,34 +4553,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696729</v>
+        <v>697051</v>
       </c>
       <c r="R36" t="n">
-        <v>6643708</v>
+        <v>6643938</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132830923</v>
+        <v>132830961</v>
       </c>
       <c r="B37" t="n">
-        <v>101333</v>
+        <v>99160</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,34 +4660,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697051</v>
+        <v>696729</v>
       </c>
       <c r="R37" t="n">
-        <v>6643938</v>
+        <v>6643708</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830936</v>
+        <v>132830963</v>
       </c>
       <c r="B44" t="n">
-        <v>91937</v>
+        <v>57954</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5454,34 +5454,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696871</v>
+        <v>696701</v>
       </c>
       <c r="R44" t="n">
-        <v>6643836</v>
+        <v>6643708</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5513,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5523,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5550,54 +5555,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830956</v>
+        <v>132830934</v>
       </c>
       <c r="B45" t="n">
-        <v>99125</v>
+        <v>101333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696730</v>
+        <v>696926</v>
       </c>
       <c r="R45" t="n">
-        <v>6643665</v>
+        <v>6643877</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5629,7 +5625,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5639,7 +5635,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5666,45 +5662,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132821927</v>
+        <v>132830936</v>
       </c>
       <c r="B46" t="n">
-        <v>106253</v>
+        <v>91937</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696722</v>
+        <v>696871</v>
       </c>
       <c r="R46" t="n">
-        <v>6643677</v>
+        <v>6643836</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5736,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5746,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5761,19 +5757,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821365</v>
+        <v>132830956</v>
       </c>
       <c r="B47" t="n">
         <v>99125</v>
@@ -5803,7 +5799,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5813,14 +5809,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696684</v>
+        <v>696730</v>
       </c>
       <c r="R47" t="n">
-        <v>6643670</v>
+        <v>6643665</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5852,7 +5848,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5862,7 +5858,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,57 +5873,66 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830934</v>
+        <v>132821365</v>
       </c>
       <c r="B48" t="n">
-        <v>101333</v>
+        <v>99125</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696926</v>
+        <v>696684</v>
       </c>
       <c r="R48" t="n">
-        <v>6643877</v>
+        <v>6643670</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5959,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5969,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5984,62 +5989,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830963</v>
+        <v>132821927</v>
       </c>
       <c r="B49" t="n">
-        <v>57954</v>
+        <v>106253</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696701</v>
+        <v>696722</v>
       </c>
       <c r="R49" t="n">
-        <v>6643708</v>
+        <v>6643677</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,12 +6096,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6331,50 +6331,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830911</v>
+        <v>132830930</v>
       </c>
       <c r="B52" t="n">
-        <v>57954</v>
+        <v>101333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696479</v>
+        <v>697027</v>
       </c>
       <c r="R52" t="n">
-        <v>6643760</v>
+        <v>6643874</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6406,7 +6401,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6416,7 +6411,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6443,54 +6438,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830927</v>
+        <v>132830911</v>
       </c>
       <c r="B53" t="n">
-        <v>99125</v>
+        <v>57954</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696972</v>
+        <v>696479</v>
       </c>
       <c r="R53" t="n">
-        <v>6643904</v>
+        <v>6643760</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6522,7 +6513,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6532,7 +6523,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6559,7 +6550,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132822683</v>
+        <v>132830927</v>
       </c>
       <c r="B54" t="n">
         <v>99125</v>
@@ -6589,7 +6580,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6599,14 +6590,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696803</v>
+        <v>696972</v>
       </c>
       <c r="R54" t="n">
-        <v>6643814</v>
+        <v>6643904</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6638,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6648,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6663,57 +6654,66 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830930</v>
+        <v>132822683</v>
       </c>
       <c r="B55" t="n">
-        <v>101333</v>
+        <v>99125</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697027</v>
+        <v>696803</v>
       </c>
       <c r="R55" t="n">
-        <v>6643874</v>
+        <v>6643814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,42 +6770,46 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132830931</v>
+        <v>132830935</v>
       </c>
       <c r="B56" t="n">
-        <v>91936</v>
+        <v>101333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6813,10 +6817,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697026</v>
+        <v>696897</v>
       </c>
       <c r="R56" t="n">
-        <v>6643874</v>
+        <v>6643810</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6848,7 +6852,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6858,7 +6862,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6885,54 +6889,41 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132821892</v>
+        <v>132830931</v>
       </c>
       <c r="B57" t="n">
-        <v>99125</v>
+        <v>91936</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696722</v>
+        <v>697026</v>
       </c>
       <c r="R57" t="n">
-        <v>6643684</v>
+        <v>6643874</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6964,7 +6955,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6974,7 +6965,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6989,57 +6980,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B58" t="n">
-        <v>101333</v>
+        <v>99125</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R58" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7340,54 +7340,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132821719</v>
+        <v>132830971</v>
       </c>
       <c r="B61" t="n">
-        <v>99125</v>
+        <v>57954</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696709</v>
+        <v>696622</v>
       </c>
       <c r="R61" t="n">
-        <v>6643709</v>
+        <v>6643679</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7419,7 +7415,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7429,7 +7425,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7444,57 +7440,66 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B62" t="n">
-        <v>101333</v>
+        <v>99125</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R62" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7526,7 +7531,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7536,7 +7541,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7551,62 +7556,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830971</v>
+        <v>132830970</v>
       </c>
       <c r="B63" t="n">
-        <v>57954</v>
+        <v>101333</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696622</v>
+        <v>696614</v>
       </c>
       <c r="R63" t="n">
-        <v>6643679</v>
+        <v>6643745</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830964</v>
+        <v>132830978</v>
       </c>
       <c r="B68" t="n">
-        <v>58640</v>
+        <v>58501</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696700</v>
+        <v>696664</v>
       </c>
       <c r="R68" t="n">
-        <v>6643694</v>
+        <v>6643658</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8375,10 +8375,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B70" t="n">
-        <v>58501</v>
+        <v>58640</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8386,16 +8386,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R70" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9276,53 +9276,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132830945</v>
+        <v>132823493</v>
       </c>
       <c r="B78" t="n">
-        <v>58331</v>
+        <v>99125</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696784</v>
+        <v>696964</v>
       </c>
       <c r="R78" t="n">
-        <v>6643729</v>
+        <v>6643823</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9354,7 +9355,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9364,7 +9365,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9379,66 +9380,65 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132823493</v>
+        <v>132830945</v>
       </c>
       <c r="B79" t="n">
-        <v>99125</v>
+        <v>58331</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696964</v>
+        <v>696784</v>
       </c>
       <c r="R79" t="n">
-        <v>6643823</v>
+        <v>6643729</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9495,12 +9495,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,10 +2432,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830954</v>
+        <v>132830977</v>
       </c>
       <c r="B17" t="n">
-        <v>101333</v>
+        <v>58331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,34 +2443,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696732</v>
+        <v>696664</v>
       </c>
       <c r="R17" t="n">
-        <v>6643642</v>
+        <v>6643658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2502,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2512,7 +2520,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2764,7 +2772,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2876,34 +2884,34 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830977</v>
+        <v>132830947</v>
       </c>
       <c r="B21" t="n">
-        <v>58331</v>
+        <v>57954</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2912,24 +2920,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696664</v>
+        <v>696785</v>
       </c>
       <c r="R21" t="n">
-        <v>6643658</v>
+        <v>6643731</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,7 +2966,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2976,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2998,50 +3003,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830947</v>
+        <v>132830954</v>
       </c>
       <c r="B22" t="n">
-        <v>57954</v>
+        <v>101333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696785</v>
+        <v>696732</v>
       </c>
       <c r="R22" t="n">
-        <v>6643731</v>
+        <v>6643642</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4109,50 +4109,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132826336</v>
+        <v>132830937</v>
       </c>
       <c r="B32" t="n">
-        <v>57954</v>
+        <v>101333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696492</v>
+        <v>696837</v>
       </c>
       <c r="R32" t="n">
-        <v>6643764</v>
+        <v>6643803</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4184,7 +4179,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4194,7 +4189,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,19 +4204,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830937</v>
+        <v>132830929</v>
       </c>
       <c r="B33" t="n">
         <v>101333</v>
@@ -4252,14 +4247,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696837</v>
+        <v>697012</v>
       </c>
       <c r="R33" t="n">
-        <v>6643803</v>
+        <v>6643911</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4301,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,7 +4323,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830929</v>
+        <v>132830957</v>
       </c>
       <c r="B34" t="n">
         <v>101333</v>
@@ -4359,14 +4354,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697012</v>
+        <v>696757</v>
       </c>
       <c r="R34" t="n">
-        <v>6643911</v>
+        <v>6643672</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4398,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,45 +4430,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132830957</v>
+        <v>132826336</v>
       </c>
       <c r="B35" t="n">
-        <v>101333</v>
+        <v>57954</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696757</v>
+        <v>696492</v>
       </c>
       <c r="R35" t="n">
-        <v>6643672</v>
+        <v>6643764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,22 +4530,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132830923</v>
+        <v>132830961</v>
       </c>
       <c r="B36" t="n">
-        <v>101333</v>
+        <v>99160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,34 +4553,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697051</v>
+        <v>696729</v>
       </c>
       <c r="R36" t="n">
-        <v>6643938</v>
+        <v>6643708</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132830961</v>
+        <v>132830923</v>
       </c>
       <c r="B37" t="n">
-        <v>99160</v>
+        <v>101333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,34 +4660,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696729</v>
+        <v>697051</v>
       </c>
       <c r="R37" t="n">
-        <v>6643708</v>
+        <v>6643938</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5104,7 +5104,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132823172</v>
+        <v>132830915</v>
       </c>
       <c r="B41" t="n">
         <v>99125</v>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5144,14 +5144,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696885</v>
+        <v>696686</v>
       </c>
       <c r="R41" t="n">
-        <v>6643816</v>
+        <v>6643680</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5208,66 +5208,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132830915</v>
+        <v>132830925</v>
       </c>
       <c r="B42" t="n">
-        <v>99125</v>
+        <v>101333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696686</v>
+        <v>697028</v>
       </c>
       <c r="R42" t="n">
-        <v>6643680</v>
+        <v>6643921</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5299,7 +5290,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5309,7 +5300,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5336,45 +5327,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132830925</v>
+        <v>132823172</v>
       </c>
       <c r="B43" t="n">
-        <v>101333</v>
+        <v>99125</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697028</v>
+        <v>696885</v>
       </c>
       <c r="R43" t="n">
-        <v>6643921</v>
+        <v>6643816</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5431,12 +5431,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5555,32 +5555,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830934</v>
+        <v>132830936</v>
       </c>
       <c r="B45" t="n">
-        <v>101333</v>
+        <v>91937</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696926</v>
+        <v>696871</v>
       </c>
       <c r="R45" t="n">
-        <v>6643877</v>
+        <v>6643836</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5662,45 +5662,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830936</v>
+        <v>132830956</v>
       </c>
       <c r="B46" t="n">
-        <v>91937</v>
+        <v>99125</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696871</v>
+        <v>696730</v>
       </c>
       <c r="R46" t="n">
-        <v>6643836</v>
+        <v>6643665</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,7 +5741,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5751,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5769,54 +5778,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830956</v>
+        <v>132821927</v>
       </c>
       <c r="B47" t="n">
-        <v>99125</v>
+        <v>106253</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696730</v>
+        <v>696722</v>
       </c>
       <c r="R47" t="n">
-        <v>6643665</v>
+        <v>6643677</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5873,12 +5873,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132821927</v>
+        <v>132830934</v>
       </c>
       <c r="B49" t="n">
-        <v>106253</v>
+        <v>101333</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6012,34 +6012,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696722</v>
+        <v>696926</v>
       </c>
       <c r="R49" t="n">
-        <v>6643677</v>
+        <v>6643877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,57 +6096,66 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132830943</v>
+        <v>132830979</v>
       </c>
       <c r="B50" t="n">
-        <v>101333</v>
+        <v>99125</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696778</v>
+        <v>696663</v>
       </c>
       <c r="R50" t="n">
-        <v>6643770</v>
+        <v>6643658</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,7 +6187,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6188,7 +6197,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,54 +6224,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132830979</v>
+        <v>132830943</v>
       </c>
       <c r="B51" t="n">
-        <v>99125</v>
+        <v>101333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696663</v>
+        <v>696778</v>
       </c>
       <c r="R51" t="n">
-        <v>6643658</v>
+        <v>6643770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6438,50 +6438,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830911</v>
+        <v>132830927</v>
       </c>
       <c r="B53" t="n">
-        <v>57954</v>
+        <v>99125</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696479</v>
+        <v>696972</v>
       </c>
       <c r="R53" t="n">
-        <v>6643760</v>
+        <v>6643904</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,7 +6517,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6523,7 +6527,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6550,7 +6554,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830927</v>
+        <v>132822683</v>
       </c>
       <c r="B54" t="n">
         <v>99125</v>
@@ -6580,7 +6584,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6590,14 +6594,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696972</v>
+        <v>696803</v>
       </c>
       <c r="R54" t="n">
-        <v>6643904</v>
+        <v>6643814</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6633,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6643,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6654,66 +6658,62 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132822683</v>
+        <v>132830911</v>
       </c>
       <c r="B55" t="n">
-        <v>99125</v>
+        <v>57954</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696803</v>
+        <v>696479</v>
       </c>
       <c r="R55" t="n">
-        <v>6643814</v>
+        <v>6643760</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,57 +6770,66 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B56" t="n">
-        <v>101333</v>
+        <v>99125</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R56" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6852,7 +6861,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6862,7 +6871,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6877,42 +6886,46 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830931</v>
+        <v>132830935</v>
       </c>
       <c r="B57" t="n">
-        <v>91936</v>
+        <v>101333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6920,10 +6933,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697026</v>
+        <v>696897</v>
       </c>
       <c r="R57" t="n">
-        <v>6643874</v>
+        <v>6643810</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6955,7 +6968,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6965,7 +6978,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6992,54 +7005,41 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132821892</v>
+        <v>132830931</v>
       </c>
       <c r="B58" t="n">
-        <v>99125</v>
+        <v>91936</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696722</v>
+        <v>697026</v>
       </c>
       <c r="R58" t="n">
-        <v>6643684</v>
+        <v>6643874</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132826107</v>
+        <v>132830913</v>
       </c>
       <c r="B65" t="n">
         <v>99125</v>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696530</v>
+        <v>696702</v>
       </c>
       <c r="R65" t="n">
-        <v>6643699</v>
+        <v>6643704</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7895,19 +7895,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132830913</v>
+        <v>132830985</v>
       </c>
       <c r="B66" t="n">
         <v>99125</v>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696702</v>
+        <v>696679</v>
       </c>
       <c r="R66" t="n">
-        <v>6643704</v>
+        <v>6643623</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7996,7 +7996,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8023,7 +8028,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132830985</v>
+        <v>132826107</v>
       </c>
       <c r="B67" t="n">
         <v>99125</v>
@@ -8053,7 +8058,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8063,14 +8068,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696679</v>
+        <v>696530</v>
       </c>
       <c r="R67" t="n">
-        <v>6643623</v>
+        <v>6643699</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8102,7 +8107,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8112,12 +8117,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,12 +8132,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8259,54 +8259,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132825569</v>
+        <v>132830964</v>
       </c>
       <c r="B69" t="n">
-        <v>99125</v>
+        <v>58640</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696671</v>
+        <v>696700</v>
       </c>
       <c r="R69" t="n">
-        <v>6643630</v>
+        <v>6643694</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8363,65 +8362,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>58640</v>
+        <v>99125</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R70" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9276,54 +9276,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132823493</v>
+        <v>132830945</v>
       </c>
       <c r="B78" t="n">
-        <v>99125</v>
+        <v>58331</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696964</v>
+        <v>696784</v>
       </c>
       <c r="R78" t="n">
-        <v>6643823</v>
+        <v>6643729</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9355,7 +9354,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9365,7 +9364,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9380,65 +9379,66 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132830945</v>
+        <v>132823493</v>
       </c>
       <c r="B79" t="n">
-        <v>58331</v>
+        <v>99125</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696784</v>
+        <v>696964</v>
       </c>
       <c r="R79" t="n">
-        <v>6643729</v>
+        <v>6643823</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9495,12 +9495,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,27 +2432,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830977</v>
+        <v>132830947</v>
       </c>
       <c r="B17" t="n">
-        <v>58331</v>
+        <v>57954</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2461,24 +2461,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696664</v>
+        <v>696785</v>
       </c>
       <c r="R17" t="n">
-        <v>6643658</v>
+        <v>6643731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2507,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,7 +2517,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,54 +2544,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132825468</v>
+        <v>132830954</v>
       </c>
       <c r="B18" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696704</v>
+        <v>696732</v>
       </c>
       <c r="R18" t="n">
-        <v>6643630</v>
+        <v>6643642</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2636,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,66 +2639,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821435</v>
+        <v>132830977</v>
       </c>
       <c r="B19" t="n">
-        <v>99125</v>
+        <v>58331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696687</v>
+        <v>696664</v>
       </c>
       <c r="R19" t="n">
-        <v>6643684</v>
+        <v>6643658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2752,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2767,22 +2754,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821661</v>
+        <v>132825468</v>
       </c>
       <c r="B20" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2807,7 +2794,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2819,10 +2810,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696690</v>
+        <v>696704</v>
       </c>
       <c r="R20" t="n">
-        <v>6643717</v>
+        <v>6643630</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2854,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2864,7 +2855,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,57 +2875,61 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830947</v>
+        <v>132821435</v>
       </c>
       <c r="B21" t="n">
-        <v>57954</v>
+        <v>99126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696785</v>
+        <v>696687</v>
       </c>
       <c r="R21" t="n">
-        <v>6643731</v>
+        <v>6643684</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2976,7 +2971,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,57 +2986,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830954</v>
+        <v>132821661</v>
       </c>
       <c r="B22" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696732</v>
+        <v>696690</v>
       </c>
       <c r="R22" t="n">
-        <v>6643642</v>
+        <v>6643717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,12 +3098,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
         <v>132830980</v>
       </c>
       <c r="B23" t="n">
-        <v>91916</v>
+        <v>91917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3217,54 +3217,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132822772</v>
+        <v>132830962</v>
       </c>
       <c r="B24" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696813</v>
+        <v>696727</v>
       </c>
       <c r="R24" t="n">
-        <v>6643818</v>
+        <v>6643708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3287,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3297,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,66 +3312,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830942</v>
+        <v>132830932</v>
       </c>
       <c r="B25" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696776</v>
+        <v>696970</v>
       </c>
       <c r="R25" t="n">
-        <v>6643778</v>
+        <v>6643862</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,54 +3431,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132821594</v>
+        <v>132830940</v>
       </c>
       <c r="B26" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696683</v>
+        <v>696814</v>
       </c>
       <c r="R26" t="n">
-        <v>6643725</v>
+        <v>6643811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3528,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3538,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,66 +3526,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132823051</v>
+        <v>132830941</v>
       </c>
       <c r="B27" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696853</v>
+        <v>696790</v>
       </c>
       <c r="R27" t="n">
-        <v>6643821</v>
+        <v>6643780</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,57 +3633,66 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830962</v>
+        <v>132822772</v>
       </c>
       <c r="B28" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696727</v>
+        <v>696813</v>
       </c>
       <c r="R28" t="n">
-        <v>6643708</v>
+        <v>6643818</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,7 +3724,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3734,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3776,57 +3749,66 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830932</v>
+        <v>132830942</v>
       </c>
       <c r="B29" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696970</v>
+        <v>696776</v>
       </c>
       <c r="R29" t="n">
-        <v>6643862</v>
+        <v>6643778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,7 +3840,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3868,7 +3850,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,45 +3877,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132830940</v>
+        <v>132821594</v>
       </c>
       <c r="B30" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696814</v>
+        <v>696683</v>
       </c>
       <c r="R30" t="n">
-        <v>6643811</v>
+        <v>6643725</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,7 +3956,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3966,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,57 +3981,66 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132830941</v>
+        <v>132823051</v>
       </c>
       <c r="B31" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696790</v>
+        <v>696853</v>
       </c>
       <c r="R31" t="n">
-        <v>6643780</v>
+        <v>6643821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,57 +4097,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132830937</v>
+        <v>132826336</v>
       </c>
       <c r="B32" t="n">
-        <v>101333</v>
+        <v>57954</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696837</v>
+        <v>696492</v>
       </c>
       <c r="R32" t="n">
-        <v>6643803</v>
+        <v>6643764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,22 +4209,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830929</v>
+        <v>132830937</v>
       </c>
       <c r="B33" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4247,14 +4252,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697012</v>
+        <v>696837</v>
       </c>
       <c r="R33" t="n">
-        <v>6643911</v>
+        <v>6643803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,7 +4291,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4301,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,10 +4328,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830957</v>
+        <v>132830929</v>
       </c>
       <c r="B34" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,14 +4359,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696757</v>
+        <v>697012</v>
       </c>
       <c r="R34" t="n">
-        <v>6643672</v>
+        <v>6643911</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,50 +4435,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132826336</v>
+        <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>57954</v>
+        <v>101334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696492</v>
+        <v>696757</v>
       </c>
       <c r="R35" t="n">
-        <v>6643764</v>
+        <v>6643672</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
         <v>132830961</v>
       </c>
       <c r="B36" t="n">
-        <v>99160</v>
+        <v>99161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>132830923</v>
       </c>
       <c r="B37" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>132823255</v>
       </c>
       <c r="B38" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>132822951</v>
       </c>
       <c r="B39" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,54 +4988,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132822662</v>
+        <v>132830925</v>
       </c>
       <c r="B40" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696811</v>
+        <v>697028</v>
       </c>
       <c r="R40" t="n">
-        <v>6643816</v>
+        <v>6643921</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5067,7 +5058,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5077,7 +5068,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,22 +5083,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132830915</v>
+        <v>132822662</v>
       </c>
       <c r="B41" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5144,14 +5135,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696686</v>
+        <v>696811</v>
       </c>
       <c r="R41" t="n">
-        <v>6643680</v>
+        <v>6643816</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5183,7 +5174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5193,7 +5184,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5208,57 +5199,66 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132830925</v>
+        <v>132823172</v>
       </c>
       <c r="B42" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>697028</v>
+        <v>696885</v>
       </c>
       <c r="R42" t="n">
-        <v>6643921</v>
+        <v>6643816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,22 +5315,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132823172</v>
+        <v>132830915</v>
       </c>
       <c r="B43" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5367,14 +5367,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696885</v>
+        <v>696686</v>
       </c>
       <c r="R43" t="n">
-        <v>6643816</v>
+        <v>6643680</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5431,12 +5431,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
         <v>132830936</v>
       </c>
       <c r="B45" t="n">
-        <v>91937</v>
+        <v>91938</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5662,54 +5662,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830956</v>
+        <v>132830934</v>
       </c>
       <c r="B46" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696730</v>
+        <v>696926</v>
       </c>
       <c r="R46" t="n">
-        <v>6643665</v>
+        <v>6643877</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5741,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5751,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,45 +5769,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821927</v>
+        <v>132830956</v>
       </c>
       <c r="B47" t="n">
-        <v>106253</v>
+        <v>99126</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696722</v>
+        <v>696730</v>
       </c>
       <c r="R47" t="n">
-        <v>6643677</v>
+        <v>6643665</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5873,66 +5873,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821365</v>
+        <v>132821927</v>
       </c>
       <c r="B48" t="n">
-        <v>99125</v>
+        <v>106254</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696684</v>
+        <v>696722</v>
       </c>
       <c r="R48" t="n">
-        <v>6643670</v>
+        <v>6643677</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5955,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5965,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,45 +5992,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830934</v>
+        <v>132821365</v>
       </c>
       <c r="B49" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696926</v>
+        <v>696684</v>
       </c>
       <c r="R49" t="n">
-        <v>6643877</v>
+        <v>6643670</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,66 +6096,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132830979</v>
+        <v>132830943</v>
       </c>
       <c r="B50" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696663</v>
+        <v>696778</v>
       </c>
       <c r="R50" t="n">
-        <v>6643658</v>
+        <v>6643770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6187,7 +6178,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6197,7 +6188,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6224,45 +6215,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132830943</v>
+        <v>132830979</v>
       </c>
       <c r="B51" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696778</v>
+        <v>696663</v>
       </c>
       <c r="R51" t="n">
-        <v>6643770</v>
+        <v>6643658</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6331,45 +6331,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830930</v>
+        <v>132830911</v>
       </c>
       <c r="B52" t="n">
-        <v>101333</v>
+        <v>57954</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697027</v>
+        <v>696479</v>
       </c>
       <c r="R52" t="n">
-        <v>6643874</v>
+        <v>6643760</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6401,7 +6406,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6411,7 +6416,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6438,54 +6443,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830927</v>
+        <v>132830930</v>
       </c>
       <c r="B53" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696972</v>
+        <v>697027</v>
       </c>
       <c r="R53" t="n">
-        <v>6643904</v>
+        <v>6643874</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6517,7 +6513,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6527,7 +6523,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6554,10 +6550,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132822683</v>
+        <v>132830927</v>
       </c>
       <c r="B54" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6584,7 +6580,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6594,14 +6590,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696803</v>
+        <v>696972</v>
       </c>
       <c r="R54" t="n">
-        <v>6643814</v>
+        <v>6643904</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6633,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6643,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6658,62 +6654,66 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830911</v>
+        <v>132822683</v>
       </c>
       <c r="B55" t="n">
-        <v>57954</v>
+        <v>99126</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696479</v>
+        <v>696803</v>
       </c>
       <c r="R55" t="n">
-        <v>6643760</v>
+        <v>6643814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,66 +6770,53 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132821892</v>
+        <v>132830931</v>
       </c>
       <c r="B56" t="n">
-        <v>99125</v>
+        <v>91937</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696722</v>
+        <v>697026</v>
       </c>
       <c r="R56" t="n">
-        <v>6643684</v>
+        <v>6643874</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6861,7 +6848,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6871,7 +6858,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6886,12 +6873,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6901,7 +6888,7 @@
         <v>132830935</v>
       </c>
       <c r="B57" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7005,41 +6992,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830931</v>
+        <v>132821892</v>
       </c>
       <c r="B58" t="n">
-        <v>91936</v>
+        <v>99126</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>697026</v>
+        <v>696722</v>
       </c>
       <c r="R58" t="n">
-        <v>6643874</v>
+        <v>6643684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7111,7 +7111,7 @@
         <v>132822271</v>
       </c>
       <c r="B59" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>132821521</v>
       </c>
       <c r="B60" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7452,54 +7452,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132821719</v>
+        <v>132830970</v>
       </c>
       <c r="B62" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696709</v>
+        <v>696614</v>
       </c>
       <c r="R62" t="n">
-        <v>6643709</v>
+        <v>6643745</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7531,7 +7522,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7541,7 +7532,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7556,57 +7547,66 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B63" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R63" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7678,7 +7678,7 @@
         <v>132830933</v>
       </c>
       <c r="B64" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132830913</v>
+        <v>132826107</v>
       </c>
       <c r="B65" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696702</v>
+        <v>696530</v>
       </c>
       <c r="R65" t="n">
-        <v>6643704</v>
+        <v>6643699</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7895,22 +7895,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132830985</v>
+        <v>132830913</v>
       </c>
       <c r="B66" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696679</v>
+        <v>696702</v>
       </c>
       <c r="R66" t="n">
-        <v>6643623</v>
+        <v>6643704</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7996,12 +7996,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8028,10 +8023,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132826107</v>
+        <v>132830985</v>
       </c>
       <c r="B67" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8058,7 +8053,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8068,14 +8063,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696530</v>
+        <v>696679</v>
       </c>
       <c r="R67" t="n">
-        <v>6643699</v>
+        <v>6643623</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8107,7 +8102,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8117,7 +8112,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,65 +8132,66 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830978</v>
+        <v>132825569</v>
       </c>
       <c r="B68" t="n">
-        <v>58501</v>
+        <v>99126</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696664</v>
+        <v>696671</v>
       </c>
       <c r="R68" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8233,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8247,22 +8248,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830964</v>
+        <v>132830978</v>
       </c>
       <c r="B69" t="n">
-        <v>58640</v>
+        <v>58501</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8270,16 +8271,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8302,10 +8303,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696700</v>
+        <v>696664</v>
       </c>
       <c r="R69" t="n">
-        <v>6643694</v>
+        <v>6643658</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8338,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8348,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8374,54 +8375,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132825569</v>
+        <v>132830964</v>
       </c>
       <c r="B70" t="n">
-        <v>99125</v>
+        <v>58640</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696671</v>
+        <v>696700</v>
       </c>
       <c r="R70" t="n">
-        <v>6643630</v>
+        <v>6643694</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8493,7 +8493,7 @@
         <v>132830946</v>
       </c>
       <c r="B71" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>132822866</v>
       </c>
       <c r="B72" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132821474</v>
+        <v>132830974</v>
       </c>
       <c r="B73" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8762,14 +8762,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696684</v>
+        <v>696678</v>
       </c>
       <c r="R73" t="n">
-        <v>6643683</v>
+        <v>6643668</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8814,6 +8814,11 @@
           <t>08:54</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8826,66 +8831,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830974</v>
+        <v>132830976</v>
       </c>
       <c r="B74" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696678</v>
+        <v>696677</v>
       </c>
       <c r="R74" t="n">
-        <v>6643668</v>
+        <v>6643661</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8928,11 +8924,6 @@
       <c r="AB74" t="inlineStr">
         <is>
           <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8959,10 +8950,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132830976</v>
+        <v>132830949</v>
       </c>
       <c r="B75" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8994,10 +8985,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696677</v>
+        <v>696758</v>
       </c>
       <c r="R75" t="n">
-        <v>6643661</v>
+        <v>6643677</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9029,7 +9020,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9039,7 +9030,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9066,45 +9057,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830949</v>
+        <v>132821474</v>
       </c>
       <c r="B76" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696758</v>
+        <v>696684</v>
       </c>
       <c r="R76" t="n">
-        <v>6643677</v>
+        <v>6643683</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9161,12 +9161,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9176,7 +9176,7 @@
         <v>132830928</v>
       </c>
       <c r="B77" t="n">
-        <v>91936</v>
+        <v>91937</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9391,54 +9391,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B79" t="n">
-        <v>99125</v>
+        <v>101334</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R79" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9470,7 +9461,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9480,7 +9471,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9495,57 +9486,66 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132830960</v>
+        <v>132823493</v>
       </c>
       <c r="B80" t="n">
-        <v>101333</v>
+        <v>99126</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696741</v>
+        <v>696964</v>
       </c>
       <c r="R80" t="n">
-        <v>6643703</v>
+        <v>6643823</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9617,7 +9617,7 @@
         <v>133089120</v>
       </c>
       <c r="B81" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2435,7 +2435,7 @@
         <v>132830947</v>
       </c>
       <c r="B17" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,45 +2544,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830954</v>
+        <v>132825468</v>
       </c>
       <c r="B18" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696732</v>
+        <v>696704</v>
       </c>
       <c r="R18" t="n">
-        <v>6643642</v>
+        <v>6643630</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,7 +2623,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2633,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,65 +2648,66 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132830977</v>
+        <v>132821435</v>
       </c>
       <c r="B19" t="n">
-        <v>58331</v>
+        <v>99130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696664</v>
+        <v>696687</v>
       </c>
       <c r="R19" t="n">
-        <v>6643658</v>
+        <v>6643684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2739,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2749,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,22 +2764,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132825468</v>
+        <v>132821661</v>
       </c>
       <c r="B20" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2794,11 +2804,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2810,10 +2816,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696704</v>
+        <v>696690</v>
       </c>
       <c r="R20" t="n">
-        <v>6643630</v>
+        <v>6643717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,7 +2851,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,7 +2861,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,54 +2888,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132821435</v>
+        <v>132830977</v>
       </c>
       <c r="B21" t="n">
-        <v>99126</v>
+        <v>58332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696687</v>
+        <v>696664</v>
       </c>
       <c r="R21" t="n">
-        <v>6643684</v>
+        <v>6643658</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,7 +2966,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2976,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,62 +2991,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132821661</v>
+        <v>132830954</v>
       </c>
       <c r="B22" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696690</v>
+        <v>696732</v>
       </c>
       <c r="R22" t="n">
-        <v>6643717</v>
+        <v>6643642</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,12 +3098,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
         <v>132830980</v>
       </c>
       <c r="B23" t="n">
-        <v>91917</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3217,45 +3217,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132830962</v>
+        <v>132822772</v>
       </c>
       <c r="B24" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696727</v>
+        <v>696813</v>
       </c>
       <c r="R24" t="n">
-        <v>6643708</v>
+        <v>6643818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3297,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,57 +3321,66 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830932</v>
+        <v>132830942</v>
       </c>
       <c r="B25" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696970</v>
+        <v>696776</v>
       </c>
       <c r="R25" t="n">
-        <v>6643862</v>
+        <v>6643778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,45 +3449,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830940</v>
+        <v>132821594</v>
       </c>
       <c r="B26" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696814</v>
+        <v>696683</v>
       </c>
       <c r="R26" t="n">
-        <v>6643811</v>
+        <v>6643725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,57 +3553,66 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830941</v>
+        <v>132823051</v>
       </c>
       <c r="B27" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696790</v>
+        <v>696853</v>
       </c>
       <c r="R27" t="n">
-        <v>6643780</v>
+        <v>6643821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3608,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3633,66 +3669,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132822772</v>
+        <v>132830962</v>
       </c>
       <c r="B28" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696813</v>
+        <v>696727</v>
       </c>
       <c r="R28" t="n">
-        <v>6643818</v>
+        <v>6643708</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3734,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,66 +3776,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830942</v>
+        <v>132830932</v>
       </c>
       <c r="B29" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696776</v>
+        <v>696970</v>
       </c>
       <c r="R29" t="n">
-        <v>6643778</v>
+        <v>6643862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3840,7 +3858,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3868,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,54 +3895,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132821594</v>
+        <v>132830940</v>
       </c>
       <c r="B30" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696683</v>
+        <v>696814</v>
       </c>
       <c r="R30" t="n">
-        <v>6643725</v>
+        <v>6643811</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3966,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3981,66 +3990,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132823051</v>
+        <v>132830941</v>
       </c>
       <c r="B31" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696853</v>
+        <v>696790</v>
       </c>
       <c r="R31" t="n">
-        <v>6643821</v>
+        <v>6643780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,12 +4097,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4112,7 +4112,7 @@
         <v>132826336</v>
       </c>
       <c r="B32" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>132830937</v>
       </c>
       <c r="B33" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>132830929</v>
       </c>
       <c r="B34" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>132830961</v>
       </c>
       <c r="B36" t="n">
-        <v>99161</v>
+        <v>99165</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>132830923</v>
       </c>
       <c r="B37" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>132823255</v>
       </c>
       <c r="B38" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>132822951</v>
       </c>
       <c r="B39" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>132830925</v>
       </c>
       <c r="B40" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>132822662</v>
       </c>
       <c r="B41" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>132823172</v>
       </c>
       <c r="B42" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>132830915</v>
       </c>
       <c r="B43" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>132830963</v>
       </c>
       <c r="B44" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5555,45 +5555,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830936</v>
+        <v>132830956</v>
       </c>
       <c r="B45" t="n">
-        <v>91938</v>
+        <v>99130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696871</v>
+        <v>696730</v>
       </c>
       <c r="R45" t="n">
-        <v>6643836</v>
+        <v>6643665</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,7 +5634,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5635,7 +5644,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5662,10 +5671,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830934</v>
+        <v>132821927</v>
       </c>
       <c r="B46" t="n">
-        <v>101334</v>
+        <v>106258</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5673,34 +5682,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696926</v>
+        <v>696722</v>
       </c>
       <c r="R46" t="n">
-        <v>6643877</v>
+        <v>6643677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,7 +5741,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5751,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5757,22 +5766,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830956</v>
+        <v>132821365</v>
       </c>
       <c r="B47" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5799,7 +5808,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5809,14 +5818,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696730</v>
+        <v>696684</v>
       </c>
       <c r="R47" t="n">
-        <v>6643665</v>
+        <v>6643670</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5848,7 +5857,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5858,7 +5867,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5873,22 +5882,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821927</v>
+        <v>132830934</v>
       </c>
       <c r="B48" t="n">
-        <v>106254</v>
+        <v>101338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,34 +5905,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696722</v>
+        <v>696926</v>
       </c>
       <c r="R48" t="n">
-        <v>6643677</v>
+        <v>6643877</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5955,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5965,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,66 +5989,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132821365</v>
+        <v>132830936</v>
       </c>
       <c r="B49" t="n">
-        <v>99126</v>
+        <v>91939</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696684</v>
+        <v>696871</v>
       </c>
       <c r="R49" t="n">
-        <v>6643670</v>
+        <v>6643836</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,57 +6096,66 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132830943</v>
+        <v>132830979</v>
       </c>
       <c r="B50" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696778</v>
+        <v>696663</v>
       </c>
       <c r="R50" t="n">
-        <v>6643770</v>
+        <v>6643658</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,7 +6187,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6188,7 +6197,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,54 +6224,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132830979</v>
+        <v>132830943</v>
       </c>
       <c r="B51" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696663</v>
+        <v>696778</v>
       </c>
       <c r="R51" t="n">
-        <v>6643658</v>
+        <v>6643770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6334,7 +6334,7 @@
         <v>132830911</v>
       </c>
       <c r="B52" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6443,45 +6443,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830930</v>
+        <v>132830927</v>
       </c>
       <c r="B53" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697027</v>
+        <v>696972</v>
       </c>
       <c r="R53" t="n">
-        <v>6643874</v>
+        <v>6643904</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,7 +6522,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6523,7 +6532,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6550,10 +6559,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830927</v>
+        <v>132822683</v>
       </c>
       <c r="B54" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6580,7 +6589,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6590,14 +6599,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696972</v>
+        <v>696803</v>
       </c>
       <c r="R54" t="n">
-        <v>6643904</v>
+        <v>6643814</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6638,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6648,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6654,66 +6663,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132822683</v>
+        <v>132830930</v>
       </c>
       <c r="B55" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696803</v>
+        <v>697027</v>
       </c>
       <c r="R55" t="n">
-        <v>6643814</v>
+        <v>6643874</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,12 +6770,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6785,7 +6785,7 @@
         <v>132830931</v>
       </c>
       <c r="B56" t="n">
-        <v>91937</v>
+        <v>91938</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6885,45 +6885,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B57" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R57" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6955,7 +6964,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6965,7 +6974,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6980,66 +6989,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132821892</v>
+        <v>132830935</v>
       </c>
       <c r="B58" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696722</v>
+        <v>696897</v>
       </c>
       <c r="R58" t="n">
-        <v>6643684</v>
+        <v>6643810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7111,7 +7111,7 @@
         <v>132822271</v>
       </c>
       <c r="B59" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>132821521</v>
       </c>
       <c r="B60" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>132830971</v>
       </c>
       <c r="B61" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7452,45 +7452,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B62" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R62" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7522,7 +7531,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7532,7 +7541,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7547,66 +7556,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132821719</v>
+        <v>132830970</v>
       </c>
       <c r="B63" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696709</v>
+        <v>696614</v>
       </c>
       <c r="R63" t="n">
-        <v>6643709</v>
+        <v>6643745</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7678,7 +7678,7 @@
         <v>132830933</v>
       </c>
       <c r="B64" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>132826107</v>
       </c>
       <c r="B65" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>132830913</v>
       </c>
       <c r="B66" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>132830985</v>
       </c>
       <c r="B67" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8144,54 +8144,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132825569</v>
+        <v>132830978</v>
       </c>
       <c r="B68" t="n">
-        <v>99126</v>
+        <v>58502</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696671</v>
+        <v>696664</v>
       </c>
       <c r="R68" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8223,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8248,22 +8247,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B69" t="n">
-        <v>58501</v>
+        <v>58641</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8271,16 +8270,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8303,10 +8302,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R69" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8375,53 +8374,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>58640</v>
+        <v>99130</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R70" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8493,7 +8493,7 @@
         <v>132830946</v>
       </c>
       <c r="B71" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>132822866</v>
       </c>
       <c r="B72" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132830974</v>
+        <v>132821474</v>
       </c>
       <c r="B73" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8762,14 +8762,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696678</v>
+        <v>696684</v>
       </c>
       <c r="R73" t="n">
-        <v>6643668</v>
+        <v>6643683</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8814,11 +8814,6 @@
           <t>08:54</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8831,57 +8826,66 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830976</v>
+        <v>132830974</v>
       </c>
       <c r="B74" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696677</v>
+        <v>696678</v>
       </c>
       <c r="R74" t="n">
-        <v>6643661</v>
+        <v>6643668</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8924,6 +8928,11 @@
       <c r="AB74" t="inlineStr">
         <is>
           <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8950,10 +8959,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132830949</v>
+        <v>132830976</v>
       </c>
       <c r="B75" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8985,10 +8994,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696758</v>
+        <v>696677</v>
       </c>
       <c r="R75" t="n">
-        <v>6643677</v>
+        <v>6643661</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9020,7 +9029,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9030,7 +9039,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9057,54 +9066,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132821474</v>
+        <v>132830949</v>
       </c>
       <c r="B76" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696684</v>
+        <v>696758</v>
       </c>
       <c r="R76" t="n">
-        <v>6643683</v>
+        <v>6643677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9161,12 +9161,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9176,7 +9176,7 @@
         <v>132830928</v>
       </c>
       <c r="B77" t="n">
-        <v>91937</v>
+        <v>91938</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>132830945</v>
       </c>
       <c r="B78" t="n">
-        <v>58331</v>
+        <v>58332</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9391,45 +9391,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132830960</v>
+        <v>132823493</v>
       </c>
       <c r="B79" t="n">
-        <v>101334</v>
+        <v>99130</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696741</v>
+        <v>696964</v>
       </c>
       <c r="R79" t="n">
-        <v>6643703</v>
+        <v>6643823</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9461,7 +9470,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9471,7 +9480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9486,66 +9495,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B80" t="n">
-        <v>99126</v>
+        <v>101338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R80" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9617,7 +9617,7 @@
         <v>133089120</v>
       </c>
       <c r="B81" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,50 +2432,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830947</v>
+        <v>132830954</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696785</v>
+        <v>696732</v>
       </c>
       <c r="R17" t="n">
-        <v>6643731</v>
+        <v>6643642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,7 +2502,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2517,7 +2512,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,54 +2539,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132825468</v>
+        <v>132830947</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696704</v>
+        <v>696785</v>
       </c>
       <c r="R18" t="n">
-        <v>6643630</v>
+        <v>6643731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2633,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2648,66 +2639,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821435</v>
+        <v>132830977</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>58332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696687</v>
+        <v>696664</v>
       </c>
       <c r="R19" t="n">
-        <v>6643684</v>
+        <v>6643658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2764,19 +2754,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821661</v>
+        <v>132825468</v>
       </c>
       <c r="B20" t="n">
         <v>99130</v>
@@ -2804,7 +2794,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2816,10 +2810,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696690</v>
+        <v>696704</v>
       </c>
       <c r="R20" t="n">
-        <v>6643717</v>
+        <v>6643630</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2851,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2861,7 +2855,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,53 +2882,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830977</v>
+        <v>132821435</v>
       </c>
       <c r="B21" t="n">
-        <v>58332</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696664</v>
+        <v>696687</v>
       </c>
       <c r="R21" t="n">
-        <v>6643658</v>
+        <v>6643684</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2976,7 +2971,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,57 +2986,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830954</v>
+        <v>132821661</v>
       </c>
       <c r="B22" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696732</v>
+        <v>696690</v>
       </c>
       <c r="R22" t="n">
-        <v>6643642</v>
+        <v>6643717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,57 +3098,66 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132830980</v>
+        <v>132822772</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696668</v>
+        <v>696813</v>
       </c>
       <c r="R23" t="n">
-        <v>6643646</v>
+        <v>6643818</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3180,7 +3189,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3199,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,19 +3214,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132822772</v>
+        <v>132830942</v>
       </c>
       <c r="B24" t="n">
         <v>99130</v>
@@ -3247,7 +3256,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3257,14 +3266,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696813</v>
+        <v>696776</v>
       </c>
       <c r="R24" t="n">
-        <v>6643818</v>
+        <v>6643778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3305,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3315,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,19 +3330,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830942</v>
+        <v>132821594</v>
       </c>
       <c r="B25" t="n">
         <v>99130</v>
@@ -3363,7 +3372,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3373,14 +3382,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696776</v>
+        <v>696683</v>
       </c>
       <c r="R25" t="n">
-        <v>6643778</v>
+        <v>6643725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3421,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3431,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3437,19 +3446,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132821594</v>
+        <v>132823051</v>
       </c>
       <c r="B26" t="n">
         <v>99130</v>
@@ -3479,7 +3488,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3493,10 +3502,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696683</v>
+        <v>696853</v>
       </c>
       <c r="R26" t="n">
-        <v>6643725</v>
+        <v>6643821</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3528,7 +3537,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3538,7 +3547,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3565,54 +3574,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132823051</v>
+        <v>132830980</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696853</v>
+        <v>696668</v>
       </c>
       <c r="R27" t="n">
-        <v>6643821</v>
+        <v>6643646</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,12 +3669,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4109,50 +4109,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132826336</v>
+        <v>132830937</v>
       </c>
       <c r="B32" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696492</v>
+        <v>696837</v>
       </c>
       <c r="R32" t="n">
-        <v>6643764</v>
+        <v>6643803</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4184,7 +4179,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4194,7 +4189,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,19 +4204,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830937</v>
+        <v>132830929</v>
       </c>
       <c r="B33" t="n">
         <v>101338</v>
@@ -4252,14 +4247,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696837</v>
+        <v>697012</v>
       </c>
       <c r="R33" t="n">
-        <v>6643803</v>
+        <v>6643911</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4301,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,7 +4323,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830929</v>
+        <v>132830957</v>
       </c>
       <c r="B34" t="n">
         <v>101338</v>
@@ -4359,14 +4354,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697012</v>
+        <v>696757</v>
       </c>
       <c r="R34" t="n">
-        <v>6643911</v>
+        <v>6643672</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4398,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,45 +4430,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132830957</v>
+        <v>132826336</v>
       </c>
       <c r="B35" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696757</v>
+        <v>696492</v>
       </c>
       <c r="R35" t="n">
-        <v>6643672</v>
+        <v>6643764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4988,45 +4988,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132830925</v>
+        <v>132822662</v>
       </c>
       <c r="B40" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697028</v>
+        <v>696811</v>
       </c>
       <c r="R40" t="n">
-        <v>6643921</v>
+        <v>6643816</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5058,7 +5067,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5068,7 +5077,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5083,19 +5092,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132822662</v>
+        <v>132823172</v>
       </c>
       <c r="B41" t="n">
         <v>99130</v>
@@ -5125,7 +5134,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5139,7 +5148,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696811</v>
+        <v>696885</v>
       </c>
       <c r="R41" t="n">
         <v>6643816</v>
@@ -5174,7 +5183,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5184,7 +5193,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5211,7 +5220,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132823172</v>
+        <v>132830915</v>
       </c>
       <c r="B42" t="n">
         <v>99130</v>
@@ -5241,7 +5250,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5251,14 +5260,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696885</v>
+        <v>696686</v>
       </c>
       <c r="R42" t="n">
-        <v>6643816</v>
+        <v>6643680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5290,7 +5299,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5300,7 +5309,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,66 +5324,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132830915</v>
+        <v>132830925</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696686</v>
+        <v>697028</v>
       </c>
       <c r="R43" t="n">
-        <v>6643680</v>
+        <v>6643921</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5555,54 +5555,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830956</v>
+        <v>132830936</v>
       </c>
       <c r="B45" t="n">
-        <v>99130</v>
+        <v>91939</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696730</v>
+        <v>696871</v>
       </c>
       <c r="R45" t="n">
-        <v>6643665</v>
+        <v>6643836</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5634,7 +5625,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5644,7 +5635,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5671,45 +5662,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132821927</v>
+        <v>132830956</v>
       </c>
       <c r="B46" t="n">
-        <v>106258</v>
+        <v>99130</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696722</v>
+        <v>696730</v>
       </c>
       <c r="R46" t="n">
-        <v>6643677</v>
+        <v>6643665</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5766,12 +5766,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5894,10 +5894,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830934</v>
+        <v>132821927</v>
       </c>
       <c r="B48" t="n">
-        <v>101338</v>
+        <v>106258</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5905,34 +5905,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696926</v>
+        <v>696722</v>
       </c>
       <c r="R48" t="n">
-        <v>6643877</v>
+        <v>6643677</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5989,44 +5989,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830936</v>
+        <v>132830934</v>
       </c>
       <c r="B49" t="n">
-        <v>91939</v>
+        <v>101338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696871</v>
+        <v>696926</v>
       </c>
       <c r="R49" t="n">
-        <v>6643836</v>
+        <v>6643877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6331,50 +6331,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830911</v>
+        <v>132830927</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696479</v>
+        <v>696972</v>
       </c>
       <c r="R52" t="n">
-        <v>6643760</v>
+        <v>6643904</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6406,7 +6410,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6416,7 +6420,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6443,7 +6447,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830927</v>
+        <v>132822683</v>
       </c>
       <c r="B53" t="n">
         <v>99130</v>
@@ -6473,7 +6477,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6483,14 +6487,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696972</v>
+        <v>696803</v>
       </c>
       <c r="R53" t="n">
-        <v>6643904</v>
+        <v>6643814</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6522,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6532,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6547,66 +6551,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132822683</v>
+        <v>132830930</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696803</v>
+        <v>697027</v>
       </c>
       <c r="R54" t="n">
-        <v>6643814</v>
+        <v>6643874</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6638,7 +6633,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6648,7 +6643,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6663,57 +6658,62 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830930</v>
+        <v>132830911</v>
       </c>
       <c r="B55" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697027</v>
+        <v>696479</v>
       </c>
       <c r="R55" t="n">
-        <v>6643874</v>
+        <v>6643760</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6885,54 +6885,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132821892</v>
+        <v>132830935</v>
       </c>
       <c r="B57" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696722</v>
+        <v>696897</v>
       </c>
       <c r="R57" t="n">
-        <v>6643684</v>
+        <v>6643810</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6964,7 +6955,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6974,7 +6965,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6989,57 +6980,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B58" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R58" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7452,54 +7452,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132821719</v>
+        <v>132830970</v>
       </c>
       <c r="B62" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696709</v>
+        <v>696614</v>
       </c>
       <c r="R62" t="n">
-        <v>6643709</v>
+        <v>6643745</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7531,7 +7522,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7541,7 +7532,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7556,57 +7547,66 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B63" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R63" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B68" t="n">
-        <v>58502</v>
+        <v>58641</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R68" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,10 +8259,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830964</v>
+        <v>132830978</v>
       </c>
       <c r="B69" t="n">
-        <v>58641</v>
+        <v>58502</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8270,16 +8270,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696700</v>
+        <v>696664</v>
       </c>
       <c r="R69" t="n">
-        <v>6643694</v>
+        <v>6643658</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9276,10 +9276,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132830945</v>
+        <v>132830960</v>
       </c>
       <c r="B78" t="n">
-        <v>58332</v>
+        <v>101338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9287,42 +9287,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696784</v>
+        <v>696741</v>
       </c>
       <c r="R78" t="n">
-        <v>6643729</v>
+        <v>6643703</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9354,7 +9346,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9364,7 +9356,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9391,54 +9383,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132823493</v>
+        <v>132830945</v>
       </c>
       <c r="B79" t="n">
-        <v>99130</v>
+        <v>58332</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696964</v>
+        <v>696784</v>
       </c>
       <c r="R79" t="n">
-        <v>6643823</v>
+        <v>6643729</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9470,7 +9461,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9480,7 +9471,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9495,57 +9486,66 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132830960</v>
+        <v>132823493</v>
       </c>
       <c r="B80" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696741</v>
+        <v>696964</v>
       </c>
       <c r="R80" t="n">
-        <v>6643703</v>
+        <v>6643823</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,45 +2432,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830954</v>
+        <v>132830947</v>
       </c>
       <c r="B17" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696732</v>
+        <v>696785</v>
       </c>
       <c r="R17" t="n">
-        <v>6643642</v>
+        <v>6643731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2502,7 +2507,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2512,7 +2517,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,50 +2544,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830947</v>
+        <v>132825468</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696785</v>
+        <v>696704</v>
       </c>
       <c r="R18" t="n">
-        <v>6643731</v>
+        <v>6643630</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,7 +2623,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2633,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,65 +2648,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132830977</v>
+        <v>132821661</v>
       </c>
       <c r="B19" t="n">
-        <v>58332</v>
+        <v>99130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696664</v>
+        <v>696690</v>
       </c>
       <c r="R19" t="n">
-        <v>6643658</v>
+        <v>6643717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,19 +2760,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132825468</v>
+        <v>132821435</v>
       </c>
       <c r="B20" t="n">
         <v>99130</v>
@@ -2796,7 +2802,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2810,10 +2816,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696704</v>
+        <v>696687</v>
       </c>
       <c r="R20" t="n">
-        <v>6643630</v>
+        <v>6643684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,7 +2851,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,7 +2861,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,54 +2888,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132821435</v>
+        <v>132830954</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696687</v>
+        <v>696732</v>
       </c>
       <c r="R21" t="n">
-        <v>6643684</v>
+        <v>6643642</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,7 +2958,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2968,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,62 +2983,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132821661</v>
+        <v>132830977</v>
       </c>
       <c r="B22" t="n">
-        <v>99130</v>
+        <v>58332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696690</v>
+        <v>696664</v>
       </c>
       <c r="R22" t="n">
-        <v>6643717</v>
+        <v>6643658</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,66 +3098,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132822772</v>
+        <v>132830980</v>
       </c>
       <c r="B23" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696813</v>
+        <v>696668</v>
       </c>
       <c r="R23" t="n">
-        <v>6643818</v>
+        <v>6643646</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3189,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3199,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,19 +3205,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132830942</v>
+        <v>132822772</v>
       </c>
       <c r="B24" t="n">
         <v>99130</v>
@@ -3256,7 +3247,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3266,14 +3257,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696776</v>
+        <v>696813</v>
       </c>
       <c r="R24" t="n">
-        <v>6643778</v>
+        <v>6643818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3315,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,19 +3321,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132821594</v>
+        <v>132830942</v>
       </c>
       <c r="B25" t="n">
         <v>99130</v>
@@ -3372,7 +3363,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3382,14 +3373,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696683</v>
+        <v>696776</v>
       </c>
       <c r="R25" t="n">
-        <v>6643725</v>
+        <v>6643778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3421,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3431,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3446,19 +3437,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132823051</v>
+        <v>132821594</v>
       </c>
       <c r="B26" t="n">
         <v>99130</v>
@@ -3488,7 +3479,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3502,10 +3493,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696853</v>
+        <v>696683</v>
       </c>
       <c r="R26" t="n">
-        <v>6643821</v>
+        <v>6643725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3547,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3574,45 +3565,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830980</v>
+        <v>132823051</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696668</v>
+        <v>696853</v>
       </c>
       <c r="R27" t="n">
-        <v>6643646</v>
+        <v>6643821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,12 +3669,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4109,45 +4109,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132830937</v>
+        <v>132826336</v>
       </c>
       <c r="B32" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696837</v>
+        <v>696492</v>
       </c>
       <c r="R32" t="n">
-        <v>6643803</v>
+        <v>6643764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,19 +4209,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830929</v>
+        <v>132830937</v>
       </c>
       <c r="B33" t="n">
         <v>101338</v>
@@ -4247,14 +4252,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697012</v>
+        <v>696837</v>
       </c>
       <c r="R33" t="n">
-        <v>6643911</v>
+        <v>6643803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,7 +4291,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4301,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,7 +4328,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830957</v>
+        <v>132830929</v>
       </c>
       <c r="B34" t="n">
         <v>101338</v>
@@ -4354,14 +4359,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696757</v>
+        <v>697012</v>
       </c>
       <c r="R34" t="n">
-        <v>6643672</v>
+        <v>6643911</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,50 +4435,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132826336</v>
+        <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696492</v>
+        <v>696757</v>
       </c>
       <c r="R35" t="n">
-        <v>6643764</v>
+        <v>6643672</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830963</v>
+        <v>132830936</v>
       </c>
       <c r="B44" t="n">
-        <v>57955</v>
+        <v>91939</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5454,39 +5454,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696701</v>
+        <v>696871</v>
       </c>
       <c r="R44" t="n">
-        <v>6643708</v>
+        <v>6643836</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5518,7 +5513,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,7 +5523,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5555,45 +5550,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830936</v>
+        <v>132830956</v>
       </c>
       <c r="B45" t="n">
-        <v>91939</v>
+        <v>99130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696871</v>
+        <v>696730</v>
       </c>
       <c r="R45" t="n">
-        <v>6643836</v>
+        <v>6643665</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,7 +5629,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5635,7 +5639,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5662,54 +5666,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830956</v>
+        <v>132821927</v>
       </c>
       <c r="B46" t="n">
-        <v>99130</v>
+        <v>106258</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696730</v>
+        <v>696722</v>
       </c>
       <c r="R46" t="n">
-        <v>6643665</v>
+        <v>6643677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5766,66 +5761,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821365</v>
+        <v>132830934</v>
       </c>
       <c r="B47" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696684</v>
+        <v>696926</v>
       </c>
       <c r="R47" t="n">
-        <v>6643670</v>
+        <v>6643877</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5857,7 +5843,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5867,7 +5853,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5882,57 +5868,66 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821927</v>
+        <v>132821365</v>
       </c>
       <c r="B48" t="n">
-        <v>106258</v>
+        <v>99130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696722</v>
+        <v>696684</v>
       </c>
       <c r="R48" t="n">
-        <v>6643677</v>
+        <v>6643670</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5959,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5969,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,45 +5996,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830934</v>
+        <v>132830963</v>
       </c>
       <c r="B49" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696926</v>
+        <v>696701</v>
       </c>
       <c r="R49" t="n">
-        <v>6643877</v>
+        <v>6643708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6331,54 +6331,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830927</v>
+        <v>132830911</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696972</v>
+        <v>696479</v>
       </c>
       <c r="R52" t="n">
-        <v>6643904</v>
+        <v>6643760</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6410,7 +6406,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6420,7 +6416,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6447,54 +6443,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132822683</v>
+        <v>132830930</v>
       </c>
       <c r="B53" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696803</v>
+        <v>697027</v>
       </c>
       <c r="R53" t="n">
-        <v>6643814</v>
+        <v>6643874</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6526,7 +6513,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6523,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6551,57 +6538,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830930</v>
+        <v>132830927</v>
       </c>
       <c r="B54" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697027</v>
+        <v>696972</v>
       </c>
       <c r="R54" t="n">
-        <v>6643874</v>
+        <v>6643904</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6633,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6643,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,50 +6666,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830911</v>
+        <v>132822683</v>
       </c>
       <c r="B55" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696479</v>
+        <v>696803</v>
       </c>
       <c r="R55" t="n">
-        <v>6643760</v>
+        <v>6643814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,12 +6770,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6885,45 +6885,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B57" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R57" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6955,7 +6964,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6965,7 +6974,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6980,66 +6989,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132821892</v>
+        <v>132830935</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696722</v>
+        <v>696897</v>
       </c>
       <c r="R58" t="n">
-        <v>6643684</v>
+        <v>6643810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7452,45 +7452,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B62" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R62" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7522,7 +7531,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7532,7 +7541,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7547,66 +7556,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132821719</v>
+        <v>132830970</v>
       </c>
       <c r="B63" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696709</v>
+        <v>696614</v>
       </c>
       <c r="R63" t="n">
-        <v>6643709</v>
+        <v>6643745</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8259,53 +8259,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830978</v>
+        <v>132825569</v>
       </c>
       <c r="B69" t="n">
-        <v>58502</v>
+        <v>99130</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696664</v>
+        <v>696671</v>
       </c>
       <c r="R69" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8338,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8348,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8362,66 +8363,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132825569</v>
+        <v>132830978</v>
       </c>
       <c r="B70" t="n">
-        <v>99130</v>
+        <v>58502</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696671</v>
+        <v>696664</v>
       </c>
       <c r="R70" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9276,10 +9276,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132830960</v>
+        <v>132830945</v>
       </c>
       <c r="B78" t="n">
-        <v>101338</v>
+        <v>58332</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9287,34 +9287,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696741</v>
+        <v>696784</v>
       </c>
       <c r="R78" t="n">
-        <v>6643703</v>
+        <v>6643729</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9346,7 +9354,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9356,7 +9364,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9383,53 +9391,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132830945</v>
+        <v>132823493</v>
       </c>
       <c r="B79" t="n">
-        <v>58332</v>
+        <v>99130</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696784</v>
+        <v>696964</v>
       </c>
       <c r="R79" t="n">
-        <v>6643729</v>
+        <v>6643823</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9461,7 +9470,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9471,7 +9480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9486,66 +9495,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B80" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R80" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,50 +2432,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830947</v>
+        <v>132830954</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696785</v>
+        <v>696732</v>
       </c>
       <c r="R17" t="n">
-        <v>6643731</v>
+        <v>6643642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,7 +2502,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2517,7 +2512,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2660,7 +2655,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821661</v>
+        <v>132821435</v>
       </c>
       <c r="B19" t="n">
         <v>99130</v>
@@ -2688,7 +2683,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2700,10 +2699,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696690</v>
+        <v>696687</v>
       </c>
       <c r="R19" t="n">
-        <v>6643717</v>
+        <v>6643684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2735,7 +2734,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2744,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,7 +2771,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821435</v>
+        <v>132821661</v>
       </c>
       <c r="B20" t="n">
         <v>99130</v>
@@ -2800,11 +2799,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2816,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696687</v>
+        <v>696690</v>
       </c>
       <c r="R20" t="n">
-        <v>6643684</v>
+        <v>6643717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2851,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2861,7 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,45 +2883,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830954</v>
+        <v>132830947</v>
       </c>
       <c r="B21" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696732</v>
+        <v>696785</v>
       </c>
       <c r="R21" t="n">
-        <v>6643642</v>
+        <v>6643731</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,45 +3110,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132830980</v>
+        <v>132830942</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696668</v>
+        <v>696776</v>
       </c>
       <c r="R23" t="n">
-        <v>6643646</v>
+        <v>6643778</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3180,7 +3189,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3199,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3217,7 +3226,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132822772</v>
+        <v>132823051</v>
       </c>
       <c r="B24" t="n">
         <v>99130</v>
@@ -3247,7 +3256,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3261,10 +3270,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696813</v>
+        <v>696853</v>
       </c>
       <c r="R24" t="n">
-        <v>6643818</v>
+        <v>6643821</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3305,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3315,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3326,61 +3335,52 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830942</v>
+        <v>132830980</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696776</v>
+        <v>696668</v>
       </c>
       <c r="R25" t="n">
-        <v>6643778</v>
+        <v>6643646</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,54 +3449,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132821594</v>
+        <v>132830962</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696683</v>
+        <v>696727</v>
       </c>
       <c r="R26" t="n">
-        <v>6643725</v>
+        <v>6643708</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3528,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3538,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,66 +3544,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132823051</v>
+        <v>132830932</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696853</v>
+        <v>696970</v>
       </c>
       <c r="R27" t="n">
-        <v>6643821</v>
+        <v>6643862</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3626,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3636,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,19 +3651,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830962</v>
+        <v>132830940</v>
       </c>
       <c r="B28" t="n">
         <v>101338</v>
@@ -3716,10 +3698,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696727</v>
+        <v>696814</v>
       </c>
       <c r="R28" t="n">
-        <v>6643708</v>
+        <v>6643811</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,7 +3733,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3743,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,7 +3770,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830932</v>
+        <v>132830941</v>
       </c>
       <c r="B29" t="n">
         <v>101338</v>
@@ -3819,14 +3801,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696970</v>
+        <v>696790</v>
       </c>
       <c r="R29" t="n">
-        <v>6643862</v>
+        <v>6643780</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,7 +3840,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3868,7 +3850,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,45 +3877,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132830940</v>
+        <v>132822772</v>
       </c>
       <c r="B30" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696814</v>
+        <v>696813</v>
       </c>
       <c r="R30" t="n">
-        <v>6643811</v>
+        <v>6643818</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,7 +3956,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3966,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,57 +3981,66 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132830941</v>
+        <v>132821594</v>
       </c>
       <c r="B31" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696790</v>
+        <v>696683</v>
       </c>
       <c r="R31" t="n">
-        <v>6643780</v>
+        <v>6643725</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,62 +4097,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132826336</v>
+        <v>132830937</v>
       </c>
       <c r="B32" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696492</v>
+        <v>696837</v>
       </c>
       <c r="R32" t="n">
-        <v>6643764</v>
+        <v>6643803</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4184,7 +4179,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4194,7 +4189,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,19 +4204,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830937</v>
+        <v>132830929</v>
       </c>
       <c r="B33" t="n">
         <v>101338</v>
@@ -4252,14 +4247,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696837</v>
+        <v>697012</v>
       </c>
       <c r="R33" t="n">
-        <v>6643803</v>
+        <v>6643911</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4301,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,7 +4323,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830929</v>
+        <v>132830957</v>
       </c>
       <c r="B34" t="n">
         <v>101338</v>
@@ -4359,14 +4354,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697012</v>
+        <v>696757</v>
       </c>
       <c r="R34" t="n">
-        <v>6643911</v>
+        <v>6643672</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4398,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,45 +4430,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132830957</v>
+        <v>132826336</v>
       </c>
       <c r="B35" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696757</v>
+        <v>696492</v>
       </c>
       <c r="R35" t="n">
-        <v>6643672</v>
+        <v>6643764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,22 +4530,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132830961</v>
+        <v>132830923</v>
       </c>
       <c r="B36" t="n">
-        <v>99165</v>
+        <v>101338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,34 +4553,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696729</v>
+        <v>697051</v>
       </c>
       <c r="R36" t="n">
-        <v>6643708</v>
+        <v>6643938</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132830923</v>
+        <v>132830961</v>
       </c>
       <c r="B37" t="n">
-        <v>101338</v>
+        <v>99165</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,34 +4660,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697051</v>
+        <v>696729</v>
       </c>
       <c r="R37" t="n">
-        <v>6643938</v>
+        <v>6643708</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5443,45 +5443,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830936</v>
+        <v>132821927</v>
       </c>
       <c r="B44" t="n">
-        <v>91939</v>
+        <v>106258</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696871</v>
+        <v>696722</v>
       </c>
       <c r="R44" t="n">
-        <v>6643836</v>
+        <v>6643677</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5538,66 +5538,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830956</v>
+        <v>132830934</v>
       </c>
       <c r="B45" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696730</v>
+        <v>696926</v>
       </c>
       <c r="R45" t="n">
-        <v>6643665</v>
+        <v>6643877</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5629,7 +5620,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5639,7 +5630,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5666,45 +5657,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132821927</v>
+        <v>132830956</v>
       </c>
       <c r="B46" t="n">
-        <v>106258</v>
+        <v>99130</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696722</v>
+        <v>696730</v>
       </c>
       <c r="R46" t="n">
-        <v>6643677</v>
+        <v>6643665</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5761,57 +5761,66 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830934</v>
+        <v>132821365</v>
       </c>
       <c r="B47" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696926</v>
+        <v>696684</v>
       </c>
       <c r="R47" t="n">
-        <v>6643877</v>
+        <v>6643670</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5843,7 +5852,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5853,7 +5862,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5868,66 +5877,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821365</v>
+        <v>132830936</v>
       </c>
       <c r="B48" t="n">
-        <v>99130</v>
+        <v>91939</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696684</v>
+        <v>696871</v>
       </c>
       <c r="R48" t="n">
-        <v>6643670</v>
+        <v>6643836</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5984,12 +5984,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6331,50 +6331,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830911</v>
+        <v>132830930</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696479</v>
+        <v>697027</v>
       </c>
       <c r="R52" t="n">
-        <v>6643760</v>
+        <v>6643874</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6406,7 +6401,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6416,7 +6411,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6443,45 +6438,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830930</v>
+        <v>132830911</v>
       </c>
       <c r="B53" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697027</v>
+        <v>696479</v>
       </c>
       <c r="R53" t="n">
-        <v>6643874</v>
+        <v>6643760</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6782,30 +6782,34 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132830931</v>
+        <v>132830935</v>
       </c>
       <c r="B56" t="n">
-        <v>91938</v>
+        <v>101338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6813,10 +6817,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697026</v>
+        <v>696897</v>
       </c>
       <c r="R56" t="n">
-        <v>6643874</v>
+        <v>6643810</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6848,7 +6852,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6858,7 +6862,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6885,54 +6889,41 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132821892</v>
+        <v>132830931</v>
       </c>
       <c r="B57" t="n">
-        <v>99130</v>
+        <v>91938</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696722</v>
+        <v>697026</v>
       </c>
       <c r="R57" t="n">
-        <v>6643684</v>
+        <v>6643874</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6964,7 +6955,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6974,7 +6965,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6989,57 +6980,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B58" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R58" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7452,54 +7452,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132821719</v>
+        <v>132830970</v>
       </c>
       <c r="B62" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696709</v>
+        <v>696614</v>
       </c>
       <c r="R62" t="n">
-        <v>6643709</v>
+        <v>6643745</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7531,7 +7522,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7541,7 +7532,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7556,57 +7547,66 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B63" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R63" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830964</v>
+        <v>132830978</v>
       </c>
       <c r="B68" t="n">
-        <v>58641</v>
+        <v>58502</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696700</v>
+        <v>696664</v>
       </c>
       <c r="R68" t="n">
-        <v>6643694</v>
+        <v>6643658</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,54 +8259,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132825569</v>
+        <v>132830964</v>
       </c>
       <c r="B69" t="n">
-        <v>99130</v>
+        <v>58641</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696671</v>
+        <v>696700</v>
       </c>
       <c r="R69" t="n">
-        <v>6643630</v>
+        <v>6643694</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8363,65 +8362,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830978</v>
+        <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>58502</v>
+        <v>99130</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696664</v>
+        <v>696671</v>
       </c>
       <c r="R70" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8722,54 +8722,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132821474</v>
+        <v>132830976</v>
       </c>
       <c r="B73" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696684</v>
+        <v>696677</v>
       </c>
       <c r="R73" t="n">
-        <v>6643683</v>
+        <v>6643661</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8826,66 +8817,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830974</v>
+        <v>132830949</v>
       </c>
       <c r="B74" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696678</v>
+        <v>696758</v>
       </c>
       <c r="R74" t="n">
-        <v>6643668</v>
+        <v>6643677</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8917,7 +8899,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8927,12 +8909,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8959,45 +8936,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132830976</v>
+        <v>132821474</v>
       </c>
       <c r="B75" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696677</v>
+        <v>696684</v>
       </c>
       <c r="R75" t="n">
-        <v>6643661</v>
+        <v>6643683</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9054,57 +9040,66 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830949</v>
+        <v>132830974</v>
       </c>
       <c r="B76" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696758</v>
+        <v>696678</v>
       </c>
       <c r="R76" t="n">
-        <v>6643677</v>
+        <v>6643668</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9136,7 +9131,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9146,7 +9141,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9391,54 +9391,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B79" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R79" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9470,7 +9461,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9480,7 +9471,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9495,57 +9486,66 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132830960</v>
+        <v>132823493</v>
       </c>
       <c r="B80" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696741</v>
+        <v>696964</v>
       </c>
       <c r="R80" t="n">
-        <v>6643703</v>
+        <v>6643823</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2539,54 +2539,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132825468</v>
+        <v>132830947</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696704</v>
+        <v>696785</v>
       </c>
       <c r="R18" t="n">
-        <v>6643630</v>
+        <v>6643731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2628,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,66 +2639,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821435</v>
+        <v>132830977</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>58332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696687</v>
+        <v>696664</v>
       </c>
       <c r="R19" t="n">
-        <v>6643684</v>
+        <v>6643658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2734,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2744,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2759,19 +2754,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821661</v>
+        <v>132825468</v>
       </c>
       <c r="B20" t="n">
         <v>99130</v>
@@ -2799,7 +2794,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -2811,10 +2810,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696690</v>
+        <v>696704</v>
       </c>
       <c r="R20" t="n">
-        <v>6643717</v>
+        <v>6643630</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,7 +2855,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,50 +2882,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830947</v>
+        <v>132821435</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696785</v>
+        <v>696687</v>
       </c>
       <c r="R21" t="n">
-        <v>6643731</v>
+        <v>6643684</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2968,7 +2971,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2983,65 +2986,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830977</v>
+        <v>132821661</v>
       </c>
       <c r="B22" t="n">
-        <v>58332</v>
+        <v>99130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696664</v>
+        <v>696690</v>
       </c>
       <c r="R22" t="n">
-        <v>6643658</v>
+        <v>6643717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,66 +3098,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132830942</v>
+        <v>132830980</v>
       </c>
       <c r="B23" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696776</v>
+        <v>696668</v>
       </c>
       <c r="R23" t="n">
-        <v>6643778</v>
+        <v>6643646</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3189,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3199,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3226,7 +3217,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132823051</v>
+        <v>132822772</v>
       </c>
       <c r="B24" t="n">
         <v>99130</v>
@@ -3256,7 +3247,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3270,10 +3261,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696853</v>
+        <v>696813</v>
       </c>
       <c r="R24" t="n">
-        <v>6643821</v>
+        <v>6643818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3315,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,52 +3326,61 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830980</v>
+        <v>132830942</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696668</v>
+        <v>696776</v>
       </c>
       <c r="R25" t="n">
-        <v>6643646</v>
+        <v>6643778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,45 +3449,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830962</v>
+        <v>132821594</v>
       </c>
       <c r="B26" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696727</v>
+        <v>696683</v>
       </c>
       <c r="R26" t="n">
-        <v>6643708</v>
+        <v>6643725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,57 +3553,66 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830932</v>
+        <v>132823051</v>
       </c>
       <c r="B27" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696970</v>
+        <v>696853</v>
       </c>
       <c r="R27" t="n">
-        <v>6643862</v>
+        <v>6643821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3626,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3636,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,19 +3669,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830940</v>
+        <v>132830962</v>
       </c>
       <c r="B28" t="n">
         <v>101338</v>
@@ -3698,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696814</v>
+        <v>696727</v>
       </c>
       <c r="R28" t="n">
-        <v>6643811</v>
+        <v>6643708</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3733,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3743,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3770,7 +3788,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830941</v>
+        <v>132830932</v>
       </c>
       <c r="B29" t="n">
         <v>101338</v>
@@ -3801,14 +3819,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696790</v>
+        <v>696970</v>
       </c>
       <c r="R29" t="n">
-        <v>6643780</v>
+        <v>6643862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3840,7 +3858,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3868,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,54 +3895,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132822772</v>
+        <v>132830940</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696813</v>
+        <v>696814</v>
       </c>
       <c r="R30" t="n">
-        <v>6643818</v>
+        <v>6643811</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3966,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3981,66 +3990,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132821594</v>
+        <v>132830941</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696683</v>
+        <v>696790</v>
       </c>
       <c r="R31" t="n">
-        <v>6643725</v>
+        <v>6643780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,57 +4097,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132830937</v>
+        <v>132826336</v>
       </c>
       <c r="B32" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696837</v>
+        <v>696492</v>
       </c>
       <c r="R32" t="n">
-        <v>6643803</v>
+        <v>6643764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,19 +4209,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830929</v>
+        <v>132830937</v>
       </c>
       <c r="B33" t="n">
         <v>101338</v>
@@ -4247,14 +4252,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697012</v>
+        <v>696837</v>
       </c>
       <c r="R33" t="n">
-        <v>6643911</v>
+        <v>6643803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,7 +4291,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4301,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,7 +4328,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830957</v>
+        <v>132830929</v>
       </c>
       <c r="B34" t="n">
         <v>101338</v>
@@ -4354,14 +4359,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696757</v>
+        <v>697012</v>
       </c>
       <c r="R34" t="n">
-        <v>6643672</v>
+        <v>6643911</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,50 +4435,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132826336</v>
+        <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696492</v>
+        <v>696757</v>
       </c>
       <c r="R35" t="n">
-        <v>6643764</v>
+        <v>6643672</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5443,45 +5443,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132821927</v>
+        <v>132830956</v>
       </c>
       <c r="B44" t="n">
-        <v>106258</v>
+        <v>99130</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696722</v>
+        <v>696730</v>
       </c>
       <c r="R44" t="n">
-        <v>6643677</v>
+        <v>6643665</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5538,57 +5547,66 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830934</v>
+        <v>132821365</v>
       </c>
       <c r="B45" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696926</v>
+        <v>696684</v>
       </c>
       <c r="R45" t="n">
-        <v>6643877</v>
+        <v>6643670</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5620,7 +5638,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5630,7 +5648,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5645,66 +5663,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830956</v>
+        <v>132821927</v>
       </c>
       <c r="B46" t="n">
-        <v>99130</v>
+        <v>106258</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696730</v>
+        <v>696722</v>
       </c>
       <c r="R46" t="n">
-        <v>6643665</v>
+        <v>6643677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5761,66 +5770,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821365</v>
+        <v>132830934</v>
       </c>
       <c r="B47" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696684</v>
+        <v>696926</v>
       </c>
       <c r="R47" t="n">
-        <v>6643670</v>
+        <v>6643877</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,12 +5877,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6331,45 +6331,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830930</v>
+        <v>132830927</v>
       </c>
       <c r="B52" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697027</v>
+        <v>696972</v>
       </c>
       <c r="R52" t="n">
-        <v>6643874</v>
+        <v>6643904</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6401,7 +6410,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6411,7 +6420,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6438,50 +6447,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830911</v>
+        <v>132822683</v>
       </c>
       <c r="B53" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696479</v>
+        <v>696803</v>
       </c>
       <c r="R53" t="n">
-        <v>6643760</v>
+        <v>6643814</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6523,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6538,66 +6551,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830927</v>
+        <v>132830930</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696972</v>
+        <v>697027</v>
       </c>
       <c r="R54" t="n">
-        <v>6643904</v>
+        <v>6643874</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6633,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6643,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6666,54 +6670,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132822683</v>
+        <v>132830911</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696803</v>
+        <v>696479</v>
       </c>
       <c r="R55" t="n">
-        <v>6643814</v>
+        <v>6643760</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,46 +6770,42 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132830935</v>
+        <v>132830931</v>
       </c>
       <c r="B56" t="n">
-        <v>101338</v>
+        <v>91938</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6817,10 +6813,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696897</v>
+        <v>697026</v>
       </c>
       <c r="R56" t="n">
-        <v>6643810</v>
+        <v>6643874</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6852,7 +6848,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6862,7 +6858,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6889,41 +6885,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830931</v>
+        <v>132821892</v>
       </c>
       <c r="B57" t="n">
-        <v>91938</v>
+        <v>99130</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697026</v>
+        <v>696722</v>
       </c>
       <c r="R57" t="n">
-        <v>6643874</v>
+        <v>6643684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6955,7 +6964,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6965,7 +6974,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6980,66 +6989,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132821892</v>
+        <v>132830935</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696722</v>
+        <v>696897</v>
       </c>
       <c r="R58" t="n">
-        <v>6643684</v>
+        <v>6643810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7340,50 +7340,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132830971</v>
+        <v>132821719</v>
       </c>
       <c r="B61" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696622</v>
+        <v>696709</v>
       </c>
       <c r="R61" t="n">
-        <v>6643679</v>
+        <v>6643709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7415,7 +7419,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7425,7 +7429,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7440,12 +7444,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7559,54 +7563,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132821719</v>
+        <v>132830971</v>
       </c>
       <c r="B63" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696709</v>
+        <v>696622</v>
       </c>
       <c r="R63" t="n">
-        <v>6643709</v>
+        <v>6643679</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B68" t="n">
-        <v>58502</v>
+        <v>58641</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R68" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,53 +8259,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B69" t="n">
-        <v>58641</v>
+        <v>99130</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R69" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8338,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8348,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8362,66 +8363,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132825569</v>
+        <v>132830978</v>
       </c>
       <c r="B70" t="n">
-        <v>99130</v>
+        <v>58502</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696671</v>
+        <v>696664</v>
       </c>
       <c r="R70" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8722,45 +8722,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132830976</v>
+        <v>132821474</v>
       </c>
       <c r="B73" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696677</v>
+        <v>696684</v>
       </c>
       <c r="R73" t="n">
-        <v>6643661</v>
+        <v>6643683</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8817,57 +8826,66 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830949</v>
+        <v>132830974</v>
       </c>
       <c r="B74" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696758</v>
+        <v>696678</v>
       </c>
       <c r="R74" t="n">
-        <v>6643677</v>
+        <v>6643668</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8899,7 +8917,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8909,7 +8927,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8936,54 +8959,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132821474</v>
+        <v>132830976</v>
       </c>
       <c r="B75" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696684</v>
+        <v>696677</v>
       </c>
       <c r="R75" t="n">
-        <v>6643683</v>
+        <v>6643661</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9040,66 +9054,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830974</v>
+        <v>132830949</v>
       </c>
       <c r="B76" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696678</v>
+        <v>696758</v>
       </c>
       <c r="R76" t="n">
-        <v>6643668</v>
+        <v>6643677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9131,7 +9136,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9141,12 +9146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9391,45 +9391,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132830960</v>
+        <v>132823493</v>
       </c>
       <c r="B79" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696741</v>
+        <v>696964</v>
       </c>
       <c r="R79" t="n">
-        <v>6643703</v>
+        <v>6643823</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9461,7 +9470,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9471,7 +9480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9486,66 +9495,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B80" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R80" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -4109,50 +4109,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132826336</v>
+        <v>132830937</v>
       </c>
       <c r="B32" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696492</v>
+        <v>696837</v>
       </c>
       <c r="R32" t="n">
-        <v>6643764</v>
+        <v>6643803</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4184,7 +4179,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4194,7 +4189,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,19 +4204,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830937</v>
+        <v>132830929</v>
       </c>
       <c r="B33" t="n">
         <v>101338</v>
@@ -4252,14 +4247,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696837</v>
+        <v>697012</v>
       </c>
       <c r="R33" t="n">
-        <v>6643803</v>
+        <v>6643911</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4301,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,7 +4323,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830929</v>
+        <v>132830957</v>
       </c>
       <c r="B34" t="n">
         <v>101338</v>
@@ -4359,14 +4354,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697012</v>
+        <v>696757</v>
       </c>
       <c r="R34" t="n">
-        <v>6643911</v>
+        <v>6643672</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4398,7 +4393,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,45 +4430,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132830957</v>
+        <v>132826336</v>
       </c>
       <c r="B35" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696757</v>
+        <v>696492</v>
       </c>
       <c r="R35" t="n">
-        <v>6643672</v>
+        <v>6643764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,12 +4530,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5443,42 +5443,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830956</v>
+        <v>132830963</v>
       </c>
       <c r="B44" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5487,10 +5483,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696730</v>
+        <v>696701</v>
       </c>
       <c r="R44" t="n">
-        <v>6643665</v>
+        <v>6643708</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5522,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5532,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5559,7 +5555,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132821365</v>
+        <v>132830956</v>
       </c>
       <c r="B45" t="n">
         <v>99130</v>
@@ -5589,7 +5585,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5599,14 +5595,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696684</v>
+        <v>696730</v>
       </c>
       <c r="R45" t="n">
-        <v>6643670</v>
+        <v>6643665</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5638,7 +5634,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5648,7 +5644,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5663,57 +5659,66 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132821927</v>
+        <v>132821365</v>
       </c>
       <c r="B46" t="n">
-        <v>106258</v>
+        <v>99130</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696722</v>
+        <v>696684</v>
       </c>
       <c r="R46" t="n">
-        <v>6643677</v>
+        <v>6643670</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5745,7 +5750,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5755,7 +5760,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5782,10 +5787,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830934</v>
+        <v>132821927</v>
       </c>
       <c r="B47" t="n">
-        <v>101338</v>
+        <v>106258</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5793,34 +5798,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696926</v>
+        <v>696722</v>
       </c>
       <c r="R47" t="n">
-        <v>6643877</v>
+        <v>6643677</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5852,7 +5857,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5862,7 +5867,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,44 +5882,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830936</v>
+        <v>132830934</v>
       </c>
       <c r="B48" t="n">
-        <v>91939</v>
+        <v>101338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5924,10 +5929,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696871</v>
+        <v>696926</v>
       </c>
       <c r="R48" t="n">
-        <v>6643836</v>
+        <v>6643877</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5959,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5969,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5996,10 +6001,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830963</v>
+        <v>132830936</v>
       </c>
       <c r="B49" t="n">
-        <v>57955</v>
+        <v>91939</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6007,39 +6012,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696701</v>
+        <v>696871</v>
       </c>
       <c r="R49" t="n">
-        <v>6643708</v>
+        <v>6643836</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6782,41 +6782,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132830931</v>
+        <v>132821892</v>
       </c>
       <c r="B56" t="n">
-        <v>91938</v>
+        <v>99130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697026</v>
+        <v>696722</v>
       </c>
       <c r="R56" t="n">
-        <v>6643874</v>
+        <v>6643684</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6848,7 +6861,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6858,7 +6871,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6873,66 +6886,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132821892</v>
+        <v>132830935</v>
       </c>
       <c r="B57" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696722</v>
+        <v>696897</v>
       </c>
       <c r="R57" t="n">
-        <v>6643684</v>
+        <v>6643810</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6964,7 +6968,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6974,7 +6978,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6989,46 +6993,42 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830935</v>
+        <v>132830931</v>
       </c>
       <c r="B58" t="n">
-        <v>101338</v>
+        <v>91938</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696897</v>
+        <v>697026</v>
       </c>
       <c r="R58" t="n">
-        <v>6643810</v>
+        <v>6643874</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830964</v>
+        <v>132830978</v>
       </c>
       <c r="B68" t="n">
-        <v>58641</v>
+        <v>58502</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696700</v>
+        <v>696664</v>
       </c>
       <c r="R68" t="n">
-        <v>6643694</v>
+        <v>6643658</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,54 +8259,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132825569</v>
+        <v>132830964</v>
       </c>
       <c r="B69" t="n">
-        <v>99130</v>
+        <v>58641</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696671</v>
+        <v>696700</v>
       </c>
       <c r="R69" t="n">
-        <v>6643630</v>
+        <v>6643694</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8363,65 +8362,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830978</v>
+        <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>58502</v>
+        <v>99130</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696664</v>
+        <v>696671</v>
       </c>
       <c r="R70" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2432,45 +2432,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830954</v>
+        <v>132830947</v>
       </c>
       <c r="B17" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696732</v>
+        <v>696785</v>
       </c>
       <c r="R17" t="n">
-        <v>6643642</v>
+        <v>6643731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2502,7 +2507,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2512,7 +2517,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,27 +2544,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830947</v>
+        <v>132830977</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>58332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2568,21 +2573,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696785</v>
+        <v>696664</v>
       </c>
       <c r="R18" t="n">
-        <v>6643731</v>
+        <v>6643658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132830977</v>
+        <v>132830954</v>
       </c>
       <c r="B19" t="n">
-        <v>58332</v>
+        <v>101338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,42 +2670,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696664</v>
+        <v>696732</v>
       </c>
       <c r="R19" t="n">
-        <v>6643658</v>
+        <v>6643642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3217,54 +3217,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132822772</v>
+        <v>132830962</v>
       </c>
       <c r="B24" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696813</v>
+        <v>696727</v>
       </c>
       <c r="R24" t="n">
-        <v>6643818</v>
+        <v>6643708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3287,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3297,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,66 +3312,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830942</v>
+        <v>132830932</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696776</v>
+        <v>696970</v>
       </c>
       <c r="R25" t="n">
-        <v>6643778</v>
+        <v>6643862</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,54 +3431,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132821594</v>
+        <v>132830940</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696683</v>
+        <v>696814</v>
       </c>
       <c r="R26" t="n">
-        <v>6643725</v>
+        <v>6643811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3528,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3538,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,66 +3526,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132823051</v>
+        <v>132830941</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696853</v>
+        <v>696790</v>
       </c>
       <c r="R27" t="n">
-        <v>6643821</v>
+        <v>6643780</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3608,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3618,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,57 +3633,66 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132830962</v>
+        <v>132822772</v>
       </c>
       <c r="B28" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696727</v>
+        <v>696813</v>
       </c>
       <c r="R28" t="n">
-        <v>6643708</v>
+        <v>6643818</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,7 +3724,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3734,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3776,57 +3749,66 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830932</v>
+        <v>132830942</v>
       </c>
       <c r="B29" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696970</v>
+        <v>696776</v>
       </c>
       <c r="R29" t="n">
-        <v>6643862</v>
+        <v>6643778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,7 +3840,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3868,7 +3850,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,45 +3877,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132830940</v>
+        <v>132821594</v>
       </c>
       <c r="B30" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696814</v>
+        <v>696683</v>
       </c>
       <c r="R30" t="n">
-        <v>6643811</v>
+        <v>6643725</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,7 +3956,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3966,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,57 +3981,66 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132830941</v>
+        <v>132823051</v>
       </c>
       <c r="B31" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696790</v>
+        <v>696853</v>
       </c>
       <c r="R31" t="n">
-        <v>6643780</v>
+        <v>6643821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,57 +4097,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132830937</v>
+        <v>132826336</v>
       </c>
       <c r="B32" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696837</v>
+        <v>696492</v>
       </c>
       <c r="R32" t="n">
-        <v>6643803</v>
+        <v>6643764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,19 +4209,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830929</v>
+        <v>132830937</v>
       </c>
       <c r="B33" t="n">
         <v>101338</v>
@@ -4247,14 +4252,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697012</v>
+        <v>696837</v>
       </c>
       <c r="R33" t="n">
-        <v>6643911</v>
+        <v>6643803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,7 +4291,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4301,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,7 +4328,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830957</v>
+        <v>132830929</v>
       </c>
       <c r="B34" t="n">
         <v>101338</v>
@@ -4354,14 +4359,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696757</v>
+        <v>697012</v>
       </c>
       <c r="R34" t="n">
-        <v>6643672</v>
+        <v>6643911</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4403,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,50 +4435,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132826336</v>
+        <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696492</v>
+        <v>696757</v>
       </c>
       <c r="R35" t="n">
-        <v>6643764</v>
+        <v>6643672</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4530,22 +4530,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132830923</v>
+        <v>132830961</v>
       </c>
       <c r="B36" t="n">
-        <v>101338</v>
+        <v>99165</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,34 +4553,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697051</v>
+        <v>696729</v>
       </c>
       <c r="R36" t="n">
-        <v>6643938</v>
+        <v>6643708</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132830961</v>
+        <v>132830923</v>
       </c>
       <c r="B37" t="n">
-        <v>99165</v>
+        <v>101338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,34 +4660,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696729</v>
+        <v>697051</v>
       </c>
       <c r="R37" t="n">
-        <v>6643708</v>
+        <v>6643938</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5104,54 +5104,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132823172</v>
+        <v>132830925</v>
       </c>
       <c r="B41" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696885</v>
+        <v>697028</v>
       </c>
       <c r="R41" t="n">
-        <v>6643816</v>
+        <v>6643921</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5183,7 +5174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5193,7 +5184,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5208,19 +5199,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132830915</v>
+        <v>132823172</v>
       </c>
       <c r="B42" t="n">
         <v>99130</v>
@@ -5250,7 +5241,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5260,14 +5251,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696686</v>
+        <v>696885</v>
       </c>
       <c r="R42" t="n">
-        <v>6643680</v>
+        <v>6643816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5299,7 +5290,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5309,7 +5300,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5324,57 +5315,66 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132830925</v>
+        <v>132830915</v>
       </c>
       <c r="B43" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697028</v>
+        <v>696686</v>
       </c>
       <c r="R43" t="n">
-        <v>6643921</v>
+        <v>6643680</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5671,54 +5671,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132821365</v>
+        <v>132821927</v>
       </c>
       <c r="B46" t="n">
-        <v>99130</v>
+        <v>106258</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696684</v>
+        <v>696722</v>
       </c>
       <c r="R46" t="n">
-        <v>6643670</v>
+        <v>6643677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5750,7 +5741,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5760,7 +5751,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5787,45 +5778,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821927</v>
+        <v>132821365</v>
       </c>
       <c r="B47" t="n">
-        <v>106258</v>
+        <v>99130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696722</v>
+        <v>696684</v>
       </c>
       <c r="R47" t="n">
-        <v>6643677</v>
+        <v>6643670</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5894,32 +5894,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830934</v>
+        <v>132830936</v>
       </c>
       <c r="B48" t="n">
-        <v>101338</v>
+        <v>91939</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696926</v>
+        <v>696871</v>
       </c>
       <c r="R48" t="n">
-        <v>6643877</v>
+        <v>6643836</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,32 +6001,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830936</v>
+        <v>132830934</v>
       </c>
       <c r="B49" t="n">
-        <v>91939</v>
+        <v>101338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696871</v>
+        <v>696926</v>
       </c>
       <c r="R49" t="n">
-        <v>6643836</v>
+        <v>6643877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6108,54 +6108,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132830979</v>
+        <v>132830943</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696663</v>
+        <v>696778</v>
       </c>
       <c r="R50" t="n">
-        <v>6643658</v>
+        <v>6643770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6187,7 +6178,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6197,7 +6188,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6224,45 +6215,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132830943</v>
+        <v>132830979</v>
       </c>
       <c r="B51" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696778</v>
+        <v>696663</v>
       </c>
       <c r="R51" t="n">
-        <v>6643770</v>
+        <v>6643658</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6331,54 +6331,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830927</v>
+        <v>132830911</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696972</v>
+        <v>696479</v>
       </c>
       <c r="R52" t="n">
-        <v>6643904</v>
+        <v>6643760</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6410,7 +6406,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6420,7 +6416,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6447,54 +6443,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132822683</v>
+        <v>132830930</v>
       </c>
       <c r="B53" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696803</v>
+        <v>697027</v>
       </c>
       <c r="R53" t="n">
-        <v>6643814</v>
+        <v>6643874</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6526,7 +6513,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6523,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6551,57 +6538,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830930</v>
+        <v>132830927</v>
       </c>
       <c r="B54" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697027</v>
+        <v>696972</v>
       </c>
       <c r="R54" t="n">
-        <v>6643874</v>
+        <v>6643904</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6633,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6643,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,50 +6666,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132830911</v>
+        <v>132822683</v>
       </c>
       <c r="B55" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696479</v>
+        <v>696803</v>
       </c>
       <c r="R55" t="n">
-        <v>6643760</v>
+        <v>6643814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,12 +6770,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6898,34 +6898,30 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830935</v>
+        <v>132830931</v>
       </c>
       <c r="B57" t="n">
-        <v>101338</v>
+        <v>91938</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6933,10 +6929,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696897</v>
+        <v>697026</v>
       </c>
       <c r="R57" t="n">
-        <v>6643810</v>
+        <v>6643874</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6968,7 +6964,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6978,7 +6974,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7005,30 +7001,34 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830931</v>
+        <v>132830935</v>
       </c>
       <c r="B58" t="n">
-        <v>91938</v>
+        <v>101338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>697026</v>
+        <v>696897</v>
       </c>
       <c r="R58" t="n">
-        <v>6643874</v>
+        <v>6643810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7340,54 +7340,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132821719</v>
+        <v>132830970</v>
       </c>
       <c r="B61" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696709</v>
+        <v>696614</v>
       </c>
       <c r="R61" t="n">
-        <v>6643709</v>
+        <v>6643745</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7419,7 +7410,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7429,7 +7420,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7444,57 +7435,66 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B62" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R62" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7551,12 +7551,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8722,54 +8722,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132821474</v>
+        <v>132830976</v>
       </c>
       <c r="B73" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696684</v>
+        <v>696677</v>
       </c>
       <c r="R73" t="n">
-        <v>6643683</v>
+        <v>6643661</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8826,66 +8817,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830974</v>
+        <v>132830949</v>
       </c>
       <c r="B74" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696678</v>
+        <v>696758</v>
       </c>
       <c r="R74" t="n">
-        <v>6643668</v>
+        <v>6643677</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8917,7 +8899,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8927,12 +8909,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8959,45 +8936,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132830976</v>
+        <v>132821474</v>
       </c>
       <c r="B75" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696677</v>
+        <v>696684</v>
       </c>
       <c r="R75" t="n">
-        <v>6643661</v>
+        <v>6643683</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9054,57 +9040,66 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830949</v>
+        <v>132830974</v>
       </c>
       <c r="B76" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696758</v>
+        <v>696678</v>
       </c>
       <c r="R76" t="n">
-        <v>6643677</v>
+        <v>6643668</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9136,7 +9131,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9146,7 +9141,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -5443,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830963</v>
+        <v>132830936</v>
       </c>
       <c r="B44" t="n">
-        <v>57955</v>
+        <v>91939</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5454,39 +5454,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696701</v>
+        <v>696871</v>
       </c>
       <c r="R44" t="n">
-        <v>6643708</v>
+        <v>6643836</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5518,7 +5513,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,7 +5523,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5555,42 +5550,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830956</v>
+        <v>132830963</v>
       </c>
       <c r="B45" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5599,10 +5590,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696730</v>
+        <v>696701</v>
       </c>
       <c r="R45" t="n">
-        <v>6643665</v>
+        <v>6643708</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5634,7 +5625,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5644,7 +5635,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5671,10 +5662,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132821927</v>
+        <v>132830934</v>
       </c>
       <c r="B46" t="n">
-        <v>106258</v>
+        <v>101338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5682,34 +5673,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696722</v>
+        <v>696926</v>
       </c>
       <c r="R46" t="n">
-        <v>6643677</v>
+        <v>6643877</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5741,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5751,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5766,19 +5757,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821365</v>
+        <v>132830956</v>
       </c>
       <c r="B47" t="n">
         <v>99130</v>
@@ -5808,7 +5799,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5818,14 +5809,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696684</v>
+        <v>696730</v>
       </c>
       <c r="R47" t="n">
-        <v>6643670</v>
+        <v>6643665</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5857,7 +5848,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5867,7 +5858,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5882,57 +5873,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830936</v>
+        <v>132821927</v>
       </c>
       <c r="B48" t="n">
-        <v>91939</v>
+        <v>106258</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696871</v>
+        <v>696722</v>
       </c>
       <c r="R48" t="n">
-        <v>6643836</v>
+        <v>6643677</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5955,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5965,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5989,57 +5980,66 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830934</v>
+        <v>132821365</v>
       </c>
       <c r="B49" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696926</v>
+        <v>696684</v>
       </c>
       <c r="R49" t="n">
-        <v>6643877</v>
+        <v>6643670</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,12 +6096,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -7447,54 +7447,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132821719</v>
+        <v>132830971</v>
       </c>
       <c r="B62" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696709</v>
+        <v>696622</v>
       </c>
       <c r="R62" t="n">
-        <v>6643709</v>
+        <v>6643679</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7526,7 +7522,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7536,7 +7532,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7551,62 +7547,66 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830971</v>
+        <v>132821719</v>
       </c>
       <c r="B63" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696622</v>
+        <v>696709</v>
       </c>
       <c r="R63" t="n">
-        <v>6643679</v>
+        <v>6643709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B68" t="n">
-        <v>58502</v>
+        <v>58641</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R68" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,53 +8259,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B69" t="n">
-        <v>58641</v>
+        <v>99130</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R69" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8338,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8348,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8362,66 +8363,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132825569</v>
+        <v>132830978</v>
       </c>
       <c r="B70" t="n">
-        <v>99130</v>
+        <v>58502</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696671</v>
+        <v>696664</v>
       </c>
       <c r="R70" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9391,54 +9391,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132823493</v>
+        <v>132830960</v>
       </c>
       <c r="B79" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696964</v>
+        <v>696741</v>
       </c>
       <c r="R79" t="n">
-        <v>6643823</v>
+        <v>6643703</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9470,7 +9461,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9480,7 +9471,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9495,57 +9486,66 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132830960</v>
+        <v>132823493</v>
       </c>
       <c r="B80" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696741</v>
+        <v>696964</v>
       </c>
       <c r="R80" t="n">
-        <v>6643703</v>
+        <v>6643823</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -5443,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830936</v>
+        <v>132830963</v>
       </c>
       <c r="B44" t="n">
-        <v>91939</v>
+        <v>57955</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5454,34 +5454,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696871</v>
+        <v>696701</v>
       </c>
       <c r="R44" t="n">
-        <v>6643836</v>
+        <v>6643708</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5513,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5523,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5550,38 +5555,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830963</v>
+        <v>132830956</v>
       </c>
       <c r="B45" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5590,10 +5599,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696701</v>
+        <v>696730</v>
       </c>
       <c r="R45" t="n">
-        <v>6643708</v>
+        <v>6643665</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,7 +5634,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5635,7 +5644,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5662,10 +5671,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830934</v>
+        <v>132821927</v>
       </c>
       <c r="B46" t="n">
-        <v>101338</v>
+        <v>106258</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5673,34 +5682,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696926</v>
+        <v>696722</v>
       </c>
       <c r="R46" t="n">
-        <v>6643877</v>
+        <v>6643677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,7 +5741,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5751,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5757,19 +5766,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830956</v>
+        <v>132821365</v>
       </c>
       <c r="B47" t="n">
         <v>99130</v>
@@ -5799,7 +5808,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5809,14 +5818,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696730</v>
+        <v>696684</v>
       </c>
       <c r="R47" t="n">
-        <v>6643665</v>
+        <v>6643670</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5848,7 +5857,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5858,7 +5867,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5873,57 +5882,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821927</v>
+        <v>132830936</v>
       </c>
       <c r="B48" t="n">
-        <v>106258</v>
+        <v>91939</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696722</v>
+        <v>696871</v>
       </c>
       <c r="R48" t="n">
-        <v>6643677</v>
+        <v>6643836</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5955,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5965,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,66 +5989,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132821365</v>
+        <v>132830934</v>
       </c>
       <c r="B49" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696684</v>
+        <v>696926</v>
       </c>
       <c r="R49" t="n">
-        <v>6643670</v>
+        <v>6643877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,12 +6096,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830964</v>
+        <v>132830978</v>
       </c>
       <c r="B68" t="n">
-        <v>58641</v>
+        <v>58502</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696700</v>
+        <v>696664</v>
       </c>
       <c r="R68" t="n">
-        <v>6643694</v>
+        <v>6643658</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,54 +8259,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132825569</v>
+        <v>132830964</v>
       </c>
       <c r="B69" t="n">
-        <v>99130</v>
+        <v>58641</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696671</v>
+        <v>696700</v>
       </c>
       <c r="R69" t="n">
-        <v>6643630</v>
+        <v>6643694</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8363,65 +8362,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830978</v>
+        <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>58502</v>
+        <v>99130</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696664</v>
+        <v>696671</v>
       </c>
       <c r="R70" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830978</v>
+        <v>132830964</v>
       </c>
       <c r="B68" t="n">
-        <v>58502</v>
+        <v>58641</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696664</v>
+        <v>696700</v>
       </c>
       <c r="R68" t="n">
-        <v>6643658</v>
+        <v>6643694</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,53 +8259,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B69" t="n">
-        <v>58641</v>
+        <v>99130</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R69" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8338,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8348,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8362,66 +8363,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132825569</v>
+        <v>132830978</v>
       </c>
       <c r="B70" t="n">
-        <v>99130</v>
+        <v>58502</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696671</v>
+        <v>696664</v>
       </c>
       <c r="R70" t="n">
-        <v>6643630</v>
+        <v>6643658</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -5443,10 +5443,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830963</v>
+        <v>132830936</v>
       </c>
       <c r="B44" t="n">
-        <v>57955</v>
+        <v>91939</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5454,39 +5454,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696701</v>
+        <v>696871</v>
       </c>
       <c r="R44" t="n">
-        <v>6643708</v>
+        <v>6643836</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5518,7 +5513,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,7 +5523,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5555,42 +5550,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830956</v>
+        <v>132830963</v>
       </c>
       <c r="B45" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5599,10 +5590,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696730</v>
+        <v>696701</v>
       </c>
       <c r="R45" t="n">
-        <v>6643665</v>
+        <v>6643708</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5634,7 +5625,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5644,7 +5635,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5671,10 +5662,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132821927</v>
+        <v>132830934</v>
       </c>
       <c r="B46" t="n">
-        <v>106258</v>
+        <v>101338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5682,34 +5673,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696722</v>
+        <v>696926</v>
       </c>
       <c r="R46" t="n">
-        <v>6643677</v>
+        <v>6643877</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5741,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5751,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5766,19 +5757,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821365</v>
+        <v>132830956</v>
       </c>
       <c r="B47" t="n">
         <v>99130</v>
@@ -5808,7 +5799,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5818,14 +5809,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696684</v>
+        <v>696730</v>
       </c>
       <c r="R47" t="n">
-        <v>6643670</v>
+        <v>6643665</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5857,7 +5848,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5867,7 +5858,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5882,57 +5873,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830936</v>
+        <v>132821927</v>
       </c>
       <c r="B48" t="n">
-        <v>91939</v>
+        <v>106258</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696871</v>
+        <v>696722</v>
       </c>
       <c r="R48" t="n">
-        <v>6643836</v>
+        <v>6643677</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5964,7 +5955,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5974,7 +5965,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5989,57 +5980,66 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132830934</v>
+        <v>132821365</v>
       </c>
       <c r="B49" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696926</v>
+        <v>696684</v>
       </c>
       <c r="R49" t="n">
-        <v>6643877</v>
+        <v>6643670</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6096,12 +6096,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6782,54 +6782,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132821892</v>
+        <v>132830931</v>
       </c>
       <c r="B56" t="n">
-        <v>99130</v>
+        <v>91938</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696722</v>
+        <v>697026</v>
       </c>
       <c r="R56" t="n">
-        <v>6643684</v>
+        <v>6643874</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6861,7 +6848,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6871,7 +6858,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6886,42 +6873,46 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830931</v>
+        <v>132830935</v>
       </c>
       <c r="B57" t="n">
-        <v>91938</v>
+        <v>101338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6929,10 +6920,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697026</v>
+        <v>696897</v>
       </c>
       <c r="R57" t="n">
-        <v>6643874</v>
+        <v>6643810</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6964,7 +6955,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6974,7 +6965,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7001,45 +6992,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B58" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R58" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7447,50 +7447,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830971</v>
+        <v>132821719</v>
       </c>
       <c r="B62" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696622</v>
+        <v>696709</v>
       </c>
       <c r="R62" t="n">
-        <v>6643679</v>
+        <v>6643709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7522,7 +7526,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7532,7 +7536,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7547,66 +7551,62 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132821719</v>
+        <v>132830971</v>
       </c>
       <c r="B63" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696709</v>
+        <v>696622</v>
       </c>
       <c r="R63" t="n">
-        <v>6643709</v>
+        <v>6643679</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,12 +7663,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830964</v>
+        <v>132830978</v>
       </c>
       <c r="B68" t="n">
-        <v>58641</v>
+        <v>58502</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696700</v>
+        <v>696664</v>
       </c>
       <c r="R68" t="n">
-        <v>6643694</v>
+        <v>6643658</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8259,54 +8259,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132825569</v>
+        <v>132830964</v>
       </c>
       <c r="B69" t="n">
-        <v>99130</v>
+        <v>58641</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696671</v>
+        <v>696700</v>
       </c>
       <c r="R69" t="n">
-        <v>6643630</v>
+        <v>6643694</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8363,65 +8362,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132830978</v>
+        <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>58502</v>
+        <v>99130</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696664</v>
+        <v>696671</v>
       </c>
       <c r="R70" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8478,12 +8478,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2659,45 +2659,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132830954</v>
+        <v>132825468</v>
       </c>
       <c r="B19" t="n">
-        <v>101338</v>
+        <v>99132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696732</v>
+        <v>696704</v>
       </c>
       <c r="R19" t="n">
-        <v>6643642</v>
+        <v>6643630</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2748,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,22 +2763,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132825468</v>
+        <v>132821435</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,7 +2805,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2810,10 +2819,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696704</v>
+        <v>696687</v>
       </c>
       <c r="R20" t="n">
-        <v>6643630</v>
+        <v>6643684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,7 +2854,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,7 +2864,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,54 +2891,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132821435</v>
+        <v>132830954</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>101340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696687</v>
+        <v>696732</v>
       </c>
       <c r="R21" t="n">
-        <v>6643684</v>
+        <v>6643642</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,12 +2986,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3001,7 +3001,7 @@
         <v>132821661</v>
       </c>
       <c r="B22" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132830980</v>
+        <v>132830962</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>101340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696668</v>
+        <v>696727</v>
       </c>
       <c r="R23" t="n">
-        <v>6643646</v>
+        <v>6643708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3217,45 +3217,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132830962</v>
+        <v>132822772</v>
       </c>
       <c r="B24" t="n">
-        <v>101338</v>
+        <v>99132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696727</v>
+        <v>696813</v>
       </c>
       <c r="R24" t="n">
-        <v>6643708</v>
+        <v>6643818</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3297,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,57 +3321,66 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830932</v>
+        <v>132830942</v>
       </c>
       <c r="B25" t="n">
-        <v>101338</v>
+        <v>99132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696970</v>
+        <v>696776</v>
       </c>
       <c r="R25" t="n">
-        <v>6643862</v>
+        <v>6643778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3422,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,10 +3449,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830940</v>
+        <v>132830932</v>
       </c>
       <c r="B26" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3462,14 +3480,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696814</v>
+        <v>696970</v>
       </c>
       <c r="R26" t="n">
-        <v>6643811</v>
+        <v>6643862</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830941</v>
+        <v>132830940</v>
       </c>
       <c r="B27" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,10 +3591,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696790</v>
+        <v>696814</v>
       </c>
       <c r="R27" t="n">
-        <v>6643780</v>
+        <v>6643811</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3608,7 +3626,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3618,7 +3636,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,10 +3663,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132822772</v>
+        <v>132821594</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3675,7 +3693,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3689,10 +3707,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696813</v>
+        <v>696683</v>
       </c>
       <c r="R28" t="n">
-        <v>6643818</v>
+        <v>6643725</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,7 +3742,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3734,7 +3752,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3754,17 +3772,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132830942</v>
+        <v>132823051</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3791,7 +3809,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3801,14 +3819,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696776</v>
+        <v>696853</v>
       </c>
       <c r="R29" t="n">
-        <v>6643778</v>
+        <v>6643821</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3840,7 +3858,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3850,7 +3868,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3865,66 +3883,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132821594</v>
+        <v>132830941</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>101340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696683</v>
+        <v>696790</v>
       </c>
       <c r="R30" t="n">
-        <v>6643725</v>
+        <v>6643780</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3966,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3981,66 +3990,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132823051</v>
+        <v>132830980</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>91920</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696853</v>
+        <v>696668</v>
       </c>
       <c r="R31" t="n">
-        <v>6643821</v>
+        <v>6643646</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,12 +4097,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4224,7 +4224,7 @@
         <v>132830937</v>
       </c>
       <c r="B33" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>132830929</v>
       </c>
       <c r="B34" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>132830957</v>
       </c>
       <c r="B35" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>132830961</v>
       </c>
       <c r="B36" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>132830923</v>
       </c>
       <c r="B37" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>132823255</v>
       </c>
       <c r="B38" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>132822951</v>
       </c>
       <c r="B39" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>132822662</v>
       </c>
       <c r="B40" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5104,45 +5104,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132830925</v>
+        <v>132823172</v>
       </c>
       <c r="B41" t="n">
-        <v>101338</v>
+        <v>99132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>697028</v>
+        <v>696885</v>
       </c>
       <c r="R41" t="n">
-        <v>6643921</v>
+        <v>6643816</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5174,7 +5183,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5184,7 +5193,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,66 +5208,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132823172</v>
+        <v>132830925</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>101340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696885</v>
+        <v>697028</v>
       </c>
       <c r="R42" t="n">
-        <v>6643816</v>
+        <v>6643921</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,12 +5315,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5330,7 +5330,7 @@
         <v>132830915</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>132830936</v>
       </c>
       <c r="B44" t="n">
-        <v>91939</v>
+        <v>91941</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5662,45 +5662,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830934</v>
+        <v>132830956</v>
       </c>
       <c r="B46" t="n">
-        <v>101338</v>
+        <v>99132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696926</v>
+        <v>696730</v>
       </c>
       <c r="R46" t="n">
-        <v>6643877</v>
+        <v>6643665</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,7 +5741,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5751,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5769,54 +5778,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132830956</v>
+        <v>132821927</v>
       </c>
       <c r="B47" t="n">
-        <v>99130</v>
+        <v>106260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696730</v>
+        <v>696722</v>
       </c>
       <c r="R47" t="n">
-        <v>6643665</v>
+        <v>6643677</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5873,22 +5873,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132821927</v>
+        <v>132830934</v>
       </c>
       <c r="B48" t="n">
-        <v>106258</v>
+        <v>101340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5896,34 +5896,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696722</v>
+        <v>696926</v>
       </c>
       <c r="R48" t="n">
-        <v>6643677</v>
+        <v>6643877</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,12 +5980,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5995,7 +5995,7 @@
         <v>132821365</v>
       </c>
       <c r="B49" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>132830943</v>
       </c>
       <c r="B50" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>132830979</v>
       </c>
       <c r="B51" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6443,45 +6443,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830930</v>
+        <v>132830927</v>
       </c>
       <c r="B53" t="n">
-        <v>101338</v>
+        <v>99132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697027</v>
+        <v>696972</v>
       </c>
       <c r="R53" t="n">
-        <v>6643874</v>
+        <v>6643904</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6513,7 +6522,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6523,7 +6532,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6550,54 +6559,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830927</v>
+        <v>132830930</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>101340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696972</v>
+        <v>697027</v>
       </c>
       <c r="R54" t="n">
-        <v>6643904</v>
+        <v>6643874</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6669,7 +6669,7 @@
         <v>132822683</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>132830931</v>
       </c>
       <c r="B56" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6885,45 +6885,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132830935</v>
+        <v>132821892</v>
       </c>
       <c r="B57" t="n">
-        <v>101338</v>
+        <v>99132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696897</v>
+        <v>696722</v>
       </c>
       <c r="R57" t="n">
-        <v>6643810</v>
+        <v>6643684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6955,7 +6964,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6965,7 +6974,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6980,66 +6989,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132821892</v>
+        <v>132830935</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>101340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696722</v>
+        <v>696897</v>
       </c>
       <c r="R58" t="n">
-        <v>6643684</v>
+        <v>6643810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,12 +7096,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7111,7 +7111,7 @@
         <v>132822271</v>
       </c>
       <c r="B59" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>132821521</v>
       </c>
       <c r="B60" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,45 +7340,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132830970</v>
+        <v>132821719</v>
       </c>
       <c r="B61" t="n">
-        <v>101338</v>
+        <v>99132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696614</v>
+        <v>696709</v>
       </c>
       <c r="R61" t="n">
-        <v>6643745</v>
+        <v>6643709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7410,7 +7419,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7420,7 +7429,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7435,66 +7444,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132821719</v>
+        <v>132830970</v>
       </c>
       <c r="B62" t="n">
-        <v>99130</v>
+        <v>101340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696709</v>
+        <v>696614</v>
       </c>
       <c r="R62" t="n">
-        <v>6643709</v>
+        <v>6643745</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7551,12 +7551,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7678,7 +7678,7 @@
         <v>132830933</v>
       </c>
       <c r="B64" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>132826107</v>
       </c>
       <c r="B65" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>132830913</v>
       </c>
       <c r="B66" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>132830985</v>
       </c>
       <c r="B67" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>132825569</v>
       </c>
       <c r="B70" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>132830946</v>
       </c>
       <c r="B71" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>132822866</v>
       </c>
       <c r="B72" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>132830976</v>
       </c>
       <c r="B73" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8829,45 +8829,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132830949</v>
+        <v>132821474</v>
       </c>
       <c r="B74" t="n">
-        <v>101338</v>
+        <v>99132</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696758</v>
+        <v>696684</v>
       </c>
       <c r="R74" t="n">
-        <v>6643677</v>
+        <v>6643683</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8899,7 +8908,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8909,7 +8918,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8924,22 +8933,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132821474</v>
+        <v>132830974</v>
       </c>
       <c r="B75" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8966,7 +8975,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8976,14 +8985,14 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696684</v>
+        <v>696678</v>
       </c>
       <c r="R75" t="n">
-        <v>6643683</v>
+        <v>6643668</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9028,6 +9037,11 @@
           <t>08:54</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9040,66 +9054,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830974</v>
+        <v>132830949</v>
       </c>
       <c r="B76" t="n">
-        <v>99130</v>
+        <v>101340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696678</v>
+        <v>696758</v>
       </c>
       <c r="R76" t="n">
-        <v>6643668</v>
+        <v>6643677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9131,7 +9136,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9141,12 +9146,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9176,7 +9176,7 @@
         <v>132830928</v>
       </c>
       <c r="B77" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>132830960</v>
       </c>
       <c r="B79" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>132823493</v>
       </c>
       <c r="B80" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>133089120</v>
       </c>
       <c r="B81" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -9617,7 +9617,7 @@
         <v>133089120</v>
       </c>
       <c r="B81" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55545397</v>
+        <v>55544916</v>
       </c>
       <c r="B2" t="n">
-        <v>88969</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>937</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Ekllund, SV om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696480.2157174445</v>
+        <v>696728</v>
       </c>
       <c r="R2" t="n">
-        <v>6643786.046914498</v>
+        <v>6643586</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,24 +753,9 @@
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal rötskadad asp. Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,41 +783,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55545434</v>
+        <v>55545340</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696972.9238630194</v>
+        <v>696475</v>
       </c>
       <c r="R3" t="n">
-        <v>6643917.84020714</v>
+        <v>6643810</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,24 +861,14 @@
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
+          <t>På östra sidan av gammal asp ca 1,8m över mark. Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +877,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,67 +895,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122318880</v>
+        <v>55545397</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>937</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696790</v>
+        <v>696480</v>
       </c>
       <c r="R4" t="n">
-        <v>6643862</v>
+        <v>6643786</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,12 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal rötskadad asp. Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,82 +981,64 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122318667</v>
+        <v>122318473</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696760</v>
+        <v>696752</v>
       </c>
       <c r="R5" t="n">
-        <v>6643790</v>
+        <v>6643853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,15 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122318473</v>
+        <v>132830980</v>
       </c>
       <c r="B6" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,14 +1128,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696752</v>
+        <v>696668</v>
       </c>
       <c r="R6" t="n">
-        <v>6643853</v>
+        <v>6643646</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,12 +1162,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,67 +1204,58 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319573</v>
+        <v>55545420</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Eklund, Eklund, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696744</v>
+        <v>696409</v>
       </c>
       <c r="R7" t="n">
-        <v>6643779</v>
+        <v>6643780</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,22 +1279,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En stor fruktkropp vid basen av en gammal asp. Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,85 +1298,70 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122318816</v>
+        <v>55545596</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696780</v>
+        <v>697019</v>
       </c>
       <c r="R8" t="n">
-        <v>6643852</v>
+        <v>6643848</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,12 +1385,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På block och gammal asp. Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,79 +1410,63 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122318564</v>
+        <v>55545424</v>
       </c>
       <c r="B9" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2779</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696737</v>
+        <v>696409</v>
       </c>
       <c r="R9" t="n">
-        <v>6643788</v>
+        <v>6643780</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,12 +1490,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal asp. Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,79 +1515,63 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122319284</v>
+        <v>55545225</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696914</v>
+        <v>696585</v>
       </c>
       <c r="R10" t="n">
-        <v>6643869</v>
+        <v>6643837</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,12 +1595,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,76 +1620,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122318788</v>
+        <v>132830968</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696781</v>
+        <v>696615</v>
       </c>
       <c r="R11" t="n">
-        <v>6643831</v>
+        <v>6643750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,12 +1697,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,67 +1739,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122318416</v>
+        <v>55545208</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696765</v>
+        <v>696737</v>
       </c>
       <c r="R12" t="n">
-        <v>6643857</v>
+        <v>6643878</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1923,12 +1806,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På asplåga. Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,87 +1825,69 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122318689</v>
+        <v>55545398</v>
       </c>
       <c r="B13" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696765</v>
+        <v>696438</v>
       </c>
       <c r="R13" t="n">
-        <v>6643808</v>
+        <v>6643716</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2041,12 +1911,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,79 +1937,70 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122318555</v>
+        <v>55545399</v>
       </c>
       <c r="B14" t="n">
-        <v>105350</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696752</v>
+        <v>696470</v>
       </c>
       <c r="R14" t="n">
-        <v>6643853</v>
+        <v>6643661</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2158,12 +2024,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,85 +2043,69 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122318601</v>
+        <v>55545434</v>
       </c>
       <c r="B15" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696750</v>
+        <v>696973</v>
       </c>
       <c r="R15" t="n">
-        <v>6643770</v>
+        <v>6643918</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2274,12 +2129,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,82 +2148,64 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122347695</v>
+        <v>132830936</v>
       </c>
       <c r="B16" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Eklund, Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696895</v>
+        <v>696871</v>
       </c>
       <c r="R16" t="n">
-        <v>6643837</v>
+        <v>6643836</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,22 +2232,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,22 +2262,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132830947</v>
+        <v>55545592</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>93233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,42 +2285,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696785</v>
+        <v>697043</v>
       </c>
       <c r="R17" t="n">
-        <v>6643731</v>
+        <v>6643847</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2502,22 +2341,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,74 +2360,69 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132830977</v>
+        <v>55545594</v>
       </c>
       <c r="B18" t="n">
-        <v>58332</v>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696664</v>
+        <v>697030</v>
       </c>
       <c r="R18" t="n">
-        <v>6643658</v>
+        <v>6643834</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2617,22 +2446,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>08:51</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>08:51</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,75 +2465,69 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132825468</v>
+        <v>55545704</v>
       </c>
       <c r="B19" t="n">
-        <v>99132</v>
+        <v>93233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696704</v>
+        <v>696975</v>
       </c>
       <c r="R19" t="n">
-        <v>6643630</v>
+        <v>6643792</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2733,22 +2551,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,60 +2570,57 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821435</v>
+        <v>132826336</v>
       </c>
       <c r="B20" t="n">
-        <v>99132</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2819,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696687</v>
+        <v>696492</v>
       </c>
       <c r="R20" t="n">
-        <v>6643684</v>
+        <v>6643764</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2854,7 +2664,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2864,7 +2674,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830954</v>
+        <v>132830911</v>
       </c>
       <c r="B21" t="n">
-        <v>101340</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,34 +2712,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696732</v>
+        <v>696479</v>
       </c>
       <c r="R21" t="n">
-        <v>6643642</v>
+        <v>6643760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2998,50 +2813,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132821661</v>
+        <v>132830947</v>
       </c>
       <c r="B22" t="n">
-        <v>99132</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696690</v>
+        <v>696785</v>
       </c>
       <c r="R22" t="n">
-        <v>6643717</v>
+        <v>6643731</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,7 +2888,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +2898,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,22 +2913,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132830962</v>
+        <v>132830963</v>
       </c>
       <c r="B23" t="n">
-        <v>101340</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3121,31 +2936,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696727</v>
+        <v>696701</v>
       </c>
       <c r="R23" t="n">
         <v>6643708</v>
@@ -3180,7 +3000,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3010,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3217,54 +3037,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132822772</v>
+        <v>132830971</v>
       </c>
       <c r="B24" t="n">
-        <v>99132</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696813</v>
+        <v>696622</v>
       </c>
       <c r="R24" t="n">
-        <v>6643818</v>
+        <v>6643679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3112,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3122,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,66 +3137,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132830942</v>
+        <v>132830978</v>
       </c>
       <c r="B25" t="n">
-        <v>99132</v>
+        <v>58519</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696776</v>
+        <v>696664</v>
       </c>
       <c r="R25" t="n">
-        <v>6643778</v>
+        <v>6643658</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3227,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3237,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,10 +3264,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132830932</v>
+        <v>132830945</v>
       </c>
       <c r="B26" t="n">
-        <v>101340</v>
+        <v>58349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3460,34 +3275,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696970</v>
+        <v>696784</v>
       </c>
       <c r="R26" t="n">
-        <v>6643862</v>
+        <v>6643729</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,7 +3342,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3352,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,10 +3379,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132830940</v>
+        <v>132830977</v>
       </c>
       <c r="B27" t="n">
-        <v>101340</v>
+        <v>58349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,34 +3390,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696814</v>
+        <v>696664</v>
       </c>
       <c r="R27" t="n">
-        <v>6643811</v>
+        <v>6643658</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3626,7 +3457,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3636,7 +3467,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3663,42 +3494,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132821594</v>
+        <v>132826159</v>
       </c>
       <c r="B28" t="n">
-        <v>99132</v>
+        <v>58131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3707,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696683</v>
+        <v>696520</v>
       </c>
       <c r="R28" t="n">
-        <v>6643725</v>
+        <v>6643691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3742,7 +3569,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3752,7 +3579,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3779,54 +3606,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132823051</v>
+        <v>132830912</v>
       </c>
       <c r="B29" t="n">
-        <v>99132</v>
+        <v>58131</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696853</v>
+        <v>696459</v>
       </c>
       <c r="R29" t="n">
-        <v>6643821</v>
+        <v>6643757</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3868,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3883,22 +3709,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132830941</v>
+        <v>132830972</v>
       </c>
       <c r="B30" t="n">
-        <v>101340</v>
+        <v>58131</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3906,34 +3732,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>103023</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696790</v>
+        <v>696637</v>
       </c>
       <c r="R30" t="n">
-        <v>6643780</v>
+        <v>6643668</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,7 +3799,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3809,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4002,45 +3836,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132830980</v>
+        <v>132830964</v>
       </c>
       <c r="B31" t="n">
-        <v>91920</v>
+        <v>58658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>103044</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696668</v>
+        <v>696700</v>
       </c>
       <c r="R31" t="n">
-        <v>6643646</v>
+        <v>6643694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +3914,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +3924,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,50 +3951,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132826336</v>
+        <v>132830961</v>
       </c>
       <c r="B32" t="n">
-        <v>57955</v>
+        <v>99230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696492</v>
+        <v>696729</v>
       </c>
       <c r="R32" t="n">
-        <v>6643764</v>
+        <v>6643708</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4184,7 +4021,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4194,7 +4031,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,57 +4046,73 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132830937</v>
+        <v>122318142</v>
       </c>
       <c r="B33" t="n">
-        <v>101340</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Barrnaturskog NV Eklund , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696837</v>
+        <v>696790</v>
       </c>
       <c r="R33" t="n">
-        <v>6643803</v>
+        <v>6643908</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4286,22 +4139,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:49</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:49</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4310,6 +4153,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4328,45 +4172,59 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132830929</v>
+        <v>122318416</v>
       </c>
       <c r="B34" t="n">
-        <v>101340</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697012</v>
+        <v>696765</v>
       </c>
       <c r="R34" t="n">
-        <v>6643911</v>
+        <v>6643857</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4393,22 +4251,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:11</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:11</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,45 +4283,59 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132830957</v>
+        <v>122318564</v>
       </c>
       <c r="B35" t="n">
-        <v>101340</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696757</v>
+        <v>696737</v>
       </c>
       <c r="R35" t="n">
-        <v>6643672</v>
+        <v>6643788</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4500,22 +4362,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4542,45 +4394,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132830961</v>
+        <v>122318601</v>
       </c>
       <c r="B36" t="n">
-        <v>99167</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696729</v>
+        <v>696750</v>
       </c>
       <c r="R36" t="n">
-        <v>6643708</v>
+        <v>6643770</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4607,22 +4473,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,45 +4505,59 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132830923</v>
+        <v>122318667</v>
       </c>
       <c r="B37" t="n">
-        <v>101340</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697051</v>
+        <v>696760</v>
       </c>
       <c r="R37" t="n">
-        <v>6643938</v>
+        <v>6643790</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4714,22 +4584,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4756,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132823255</v>
+        <v>122318689</v>
       </c>
       <c r="B38" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4786,7 +4646,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4794,16 +4654,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696904</v>
+        <v>696765</v>
       </c>
       <c r="R38" t="n">
-        <v>6643781</v>
+        <v>6643808</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4830,22 +4697,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4854,28 +4711,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132822951</v>
+        <v>122318788</v>
       </c>
       <c r="B39" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4902,7 +4760,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4910,16 +4768,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696846</v>
+        <v>696781</v>
       </c>
       <c r="R39" t="n">
-        <v>6643821</v>
+        <v>6643831</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4946,22 +4809,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4976,22 +4829,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132822662</v>
+        <v>122318816</v>
       </c>
       <c r="B40" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5018,7 +4871,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5026,16 +4879,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696811</v>
+        <v>696780</v>
       </c>
       <c r="R40" t="n">
-        <v>6643816</v>
+        <v>6643852</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5062,22 +4920,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:49</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:49</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,22 +4940,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132823172</v>
+        <v>122318880</v>
       </c>
       <c r="B41" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5134,7 +4982,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5142,16 +4990,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696885</v>
+        <v>696790</v>
       </c>
       <c r="R41" t="n">
-        <v>6643816</v>
+        <v>6643862</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5178,22 +5031,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5208,57 +5051,73 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132830925</v>
+        <v>122318944</v>
       </c>
       <c r="B42" t="n">
-        <v>101340</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>697028</v>
+        <v>696821</v>
       </c>
       <c r="R42" t="n">
-        <v>6643921</v>
+        <v>6643861</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5285,22 +5144,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5309,6 +5158,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5327,10 +5177,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132830915</v>
+        <v>122319229</v>
       </c>
       <c r="B43" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5357,7 +5207,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5365,16 +5215,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Eklund, Eklund, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696686</v>
+        <v>696950</v>
       </c>
       <c r="R43" t="n">
-        <v>6643680</v>
+        <v>6643906</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5401,22 +5256,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5431,57 +5286,71 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830936</v>
+        <v>122319238</v>
       </c>
       <c r="B44" t="n">
-        <v>91941</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Barrnaturskog NV Eklund , Dammviken, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696871</v>
+        <v>696896</v>
       </c>
       <c r="R44" t="n">
-        <v>6643836</v>
+        <v>6643891</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5508,22 +5377,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5550,50 +5409,59 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830963</v>
+        <v>122319284</v>
       </c>
       <c r="B45" t="n">
-        <v>57955</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696701</v>
+        <v>696914</v>
       </c>
       <c r="R45" t="n">
-        <v>6643708</v>
+        <v>6643869</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5620,22 +5488,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5662,10 +5520,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132830956</v>
+        <v>122319349</v>
       </c>
       <c r="B46" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5700,16 +5558,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696730</v>
+        <v>696877</v>
       </c>
       <c r="R46" t="n">
-        <v>6643665</v>
+        <v>6643851</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5736,22 +5599,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:23</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:23</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,45 +5631,59 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132821927</v>
+        <v>122319414</v>
       </c>
       <c r="B47" t="n">
-        <v>106260</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Eklund, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>696722</v>
+        <v>696867</v>
       </c>
       <c r="R47" t="n">
-        <v>6643677</v>
+        <v>6643836</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5843,22 +5710,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5878,52 +5745,66 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830934</v>
+        <v>122319573</v>
       </c>
       <c r="B48" t="n">
-        <v>101340</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Eklund, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696926</v>
+        <v>696744</v>
       </c>
       <c r="R48" t="n">
-        <v>6643877</v>
+        <v>6643779</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5950,22 +5831,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,22 +5861,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132821365</v>
+        <v>122347695</v>
       </c>
       <c r="B49" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6022,7 +5903,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6030,16 +5911,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Eklund, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696684</v>
+        <v>696895</v>
       </c>
       <c r="R49" t="n">
-        <v>6643670</v>
+        <v>6643837</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6066,22 +5952,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6101,52 +5987,61 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132830943</v>
+        <v>132821365</v>
       </c>
       <c r="B50" t="n">
-        <v>101340</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696778</v>
+        <v>696684</v>
       </c>
       <c r="R50" t="n">
-        <v>6643770</v>
+        <v>6643670</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,7 +6073,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6188,7 +6083,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6203,22 +6098,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132830979</v>
+        <v>132821435</v>
       </c>
       <c r="B51" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6245,7 +6140,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6255,14 +6150,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696663</v>
+        <v>696687</v>
       </c>
       <c r="R51" t="n">
-        <v>6643658</v>
+        <v>6643684</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6294,7 +6189,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6304,7 +6199,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6319,62 +6214,66 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132830911</v>
+        <v>132821474</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696479</v>
+        <v>696684</v>
       </c>
       <c r="R52" t="n">
-        <v>6643760</v>
+        <v>6643683</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6406,7 +6305,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6416,7 +6315,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6431,22 +6330,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132830927</v>
+        <v>132821521</v>
       </c>
       <c r="B53" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6473,7 +6372,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6483,14 +6382,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696972</v>
+        <v>696690</v>
       </c>
       <c r="R53" t="n">
-        <v>6643904</v>
+        <v>6643690</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6522,7 +6421,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6532,7 +6431,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6547,57 +6446,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132830930</v>
+        <v>132821594</v>
       </c>
       <c r="B54" t="n">
-        <v>101340</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697027</v>
+        <v>696683</v>
       </c>
       <c r="R54" t="n">
-        <v>6643874</v>
+        <v>6643725</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6629,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6654,22 +6562,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132822683</v>
+        <v>132821661</v>
       </c>
       <c r="B55" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6694,11 +6602,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -6710,10 +6614,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696803</v>
+        <v>696690</v>
       </c>
       <c r="R55" t="n">
-        <v>6643814</v>
+        <v>6643717</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,7 +6649,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6659,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6775,48 +6679,61 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132830931</v>
+        <v>132821719</v>
       </c>
       <c r="B56" t="n">
-        <v>91940</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697026</v>
+        <v>696709</v>
       </c>
       <c r="R56" t="n">
-        <v>6643874</v>
+        <v>6643709</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6848,7 +6765,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6858,7 +6775,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6873,12 +6790,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6888,7 +6805,7 @@
         <v>132821892</v>
       </c>
       <c r="B57" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7001,45 +6918,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132830935</v>
+        <v>132822271</v>
       </c>
       <c r="B58" t="n">
-        <v>101340</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696897</v>
+        <v>696774</v>
       </c>
       <c r="R58" t="n">
-        <v>6643810</v>
+        <v>6643715</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7071,7 +6997,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7081,7 +7007,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7096,22 +7022,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132822271</v>
+        <v>132822662</v>
       </c>
       <c r="B59" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7138,7 +7064,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7152,10 +7078,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696774</v>
+        <v>696811</v>
       </c>
       <c r="R59" t="n">
-        <v>6643715</v>
+        <v>6643816</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7187,7 +7113,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7197,7 +7123,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7224,10 +7150,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132821521</v>
+        <v>132822683</v>
       </c>
       <c r="B60" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7254,7 +7180,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7268,10 +7194,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696690</v>
+        <v>696803</v>
       </c>
       <c r="R60" t="n">
-        <v>6643690</v>
+        <v>6643814</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7303,7 +7229,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7313,7 +7239,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7340,10 +7266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132821719</v>
+        <v>132822772</v>
       </c>
       <c r="B61" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7370,7 +7296,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7384,10 +7310,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696709</v>
+        <v>696813</v>
       </c>
       <c r="R61" t="n">
-        <v>6643709</v>
+        <v>6643818</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7419,7 +7345,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7429,7 +7355,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7449,52 +7375,61 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132830970</v>
+        <v>132822866</v>
       </c>
       <c r="B62" t="n">
-        <v>101340</v>
+        <v>99195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696614</v>
+        <v>696815</v>
       </c>
       <c r="R62" t="n">
-        <v>6643745</v>
+        <v>6643822</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7526,7 +7461,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7536,7 +7471,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7551,62 +7486,66 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132830971</v>
+        <v>132822951</v>
       </c>
       <c r="B63" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696622</v>
+        <v>696846</v>
       </c>
       <c r="R63" t="n">
-        <v>6643679</v>
+        <v>6643821</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7638,7 +7577,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7648,7 +7587,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,22 +7602,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132830933</v>
+        <v>132823051</v>
       </c>
       <c r="B64" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7705,7 +7644,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7715,14 +7654,14 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696939</v>
+        <v>696853</v>
       </c>
       <c r="R64" t="n">
-        <v>6643882</v>
+        <v>6643821</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7754,7 +7693,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7764,7 +7703,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7779,22 +7718,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132826107</v>
+        <v>132823172</v>
       </c>
       <c r="B65" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7821,7 +7760,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7835,10 +7774,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696530</v>
+        <v>696885</v>
       </c>
       <c r="R65" t="n">
-        <v>6643699</v>
+        <v>6643816</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7870,7 +7809,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7880,7 +7819,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7907,10 +7846,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132830913</v>
+        <v>132823255</v>
       </c>
       <c r="B66" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7937,7 +7876,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7947,14 +7886,14 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696702</v>
+        <v>696904</v>
       </c>
       <c r="R66" t="n">
-        <v>6643704</v>
+        <v>6643781</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7986,7 +7925,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7996,7 +7935,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8011,22 +7950,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132830985</v>
+        <v>132823493</v>
       </c>
       <c r="B67" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8053,7 +7992,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8063,14 +8002,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696679</v>
+        <v>696964</v>
       </c>
       <c r="R67" t="n">
-        <v>6643623</v>
+        <v>6643823</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8102,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8112,12 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8132,65 +8066,66 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132830978</v>
+        <v>132825468</v>
       </c>
       <c r="B68" t="n">
-        <v>58502</v>
+        <v>99195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696664</v>
+        <v>696704</v>
       </c>
       <c r="R68" t="n">
-        <v>6643658</v>
+        <v>6643630</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8222,7 +8157,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8232,7 +8167,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8247,65 +8182,66 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132830964</v>
+        <v>132825569</v>
       </c>
       <c r="B69" t="n">
-        <v>58641</v>
+        <v>99195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696700</v>
+        <v>696671</v>
       </c>
       <c r="R69" t="n">
-        <v>6643694</v>
+        <v>6643630</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8337,7 +8273,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8347,7 +8283,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8362,22 +8298,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132825569</v>
+        <v>132826107</v>
       </c>
       <c r="B70" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8404,7 +8340,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8418,10 +8354,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696671</v>
+        <v>696530</v>
       </c>
       <c r="R70" t="n">
-        <v>6643630</v>
+        <v>6643699</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,7 +8389,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8463,7 +8399,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8490,10 +8426,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132830946</v>
+        <v>132830913</v>
       </c>
       <c r="B71" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8520,7 +8456,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8534,10 +8470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696782</v>
+        <v>696702</v>
       </c>
       <c r="R71" t="n">
-        <v>6643729</v>
+        <v>6643704</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8569,7 +8505,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8579,7 +8515,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8606,10 +8542,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132822866</v>
+        <v>132830915</v>
       </c>
       <c r="B72" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8636,7 +8572,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8646,14 +8582,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696815</v>
+        <v>696686</v>
       </c>
       <c r="R72" t="n">
-        <v>6643822</v>
+        <v>6643680</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8685,7 +8621,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8695,7 +8631,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8710,57 +8646,66 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132830976</v>
+        <v>132830927</v>
       </c>
       <c r="B73" t="n">
-        <v>101340</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696677</v>
+        <v>696972</v>
       </c>
       <c r="R73" t="n">
-        <v>6643661</v>
+        <v>6643904</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8792,7 +8737,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8802,7 +8747,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8829,10 +8774,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132821474</v>
+        <v>132830933</v>
       </c>
       <c r="B74" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8859,7 +8804,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8869,14 +8814,14 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696684</v>
+        <v>696939</v>
       </c>
       <c r="R74" t="n">
-        <v>6643683</v>
+        <v>6643882</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8908,7 +8853,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8918,7 +8863,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8933,22 +8878,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132830974</v>
+        <v>132830942</v>
       </c>
       <c r="B75" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8975,7 +8920,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8989,10 +8934,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696678</v>
+        <v>696776</v>
       </c>
       <c r="R75" t="n">
-        <v>6643668</v>
+        <v>6643778</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9024,7 +8969,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9034,12 +8979,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9066,45 +9006,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132830949</v>
+        <v>132830946</v>
       </c>
       <c r="B76" t="n">
-        <v>101340</v>
+        <v>99195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696758</v>
+        <v>696782</v>
       </c>
       <c r="R76" t="n">
-        <v>6643677</v>
+        <v>6643729</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9136,7 +9085,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9146,7 +9095,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9173,41 +9122,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132830928</v>
+        <v>132830956</v>
       </c>
       <c r="B77" t="n">
-        <v>91940</v>
+        <v>99195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696996</v>
+        <v>696730</v>
       </c>
       <c r="R77" t="n">
-        <v>6643908</v>
+        <v>6643665</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9239,7 +9201,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9249,7 +9211,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9276,53 +9238,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132830945</v>
+        <v>132830974</v>
       </c>
       <c r="B78" t="n">
-        <v>58332</v>
+        <v>99195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696784</v>
+        <v>696678</v>
       </c>
       <c r="R78" t="n">
-        <v>6643729</v>
+        <v>6643668</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9354,7 +9317,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9364,7 +9327,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9391,45 +9359,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132830960</v>
+        <v>132830979</v>
       </c>
       <c r="B79" t="n">
-        <v>101340</v>
+        <v>99195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696741</v>
+        <v>696663</v>
       </c>
       <c r="R79" t="n">
-        <v>6643703</v>
+        <v>6643658</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9461,7 +9438,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9471,7 +9448,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9498,10 +9475,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132823493</v>
+        <v>132830985</v>
       </c>
       <c r="B80" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9528,7 +9505,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9538,14 +9515,14 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696964</v>
+        <v>696679</v>
       </c>
       <c r="R80" t="n">
-        <v>6643823</v>
+        <v>6643623</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9577,7 +9554,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9587,7 +9564,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9602,12 +9584,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9617,7 +9599,7 @@
         <v>133089120</v>
       </c>
       <c r="B81" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9726,14 +9708,2470 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122318555</v>
+      </c>
+      <c r="B82" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>696752</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6643853</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>132821927</v>
+      </c>
+      <c r="B83" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>696722</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6643677</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>55544918</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Ekllund, SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>696728</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6643586</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132830923</v>
+      </c>
+      <c r="B85" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>697051</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6643938</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>132830925</v>
+      </c>
+      <c r="B86" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>697028</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6643921</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>132830929</v>
+      </c>
+      <c r="B87" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>697012</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6643911</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>132830930</v>
+      </c>
+      <c r="B88" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>697027</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6643874</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>132830932</v>
+      </c>
+      <c r="B89" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>696970</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6643862</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>132830934</v>
+      </c>
+      <c r="B90" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>696926</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6643877</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132830935</v>
+      </c>
+      <c r="B91" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>696897</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6643810</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>132830937</v>
+      </c>
+      <c r="B92" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>696837</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6643803</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>132830940</v>
+      </c>
+      <c r="B93" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>696814</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6643811</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>132830941</v>
+      </c>
+      <c r="B94" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>696790</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6643780</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>132830943</v>
+      </c>
+      <c r="B95" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>696778</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6643770</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>132830949</v>
+      </c>
+      <c r="B96" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>696758</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6643677</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>132830954</v>
+      </c>
+      <c r="B97" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>696732</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6643642</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>132830957</v>
+      </c>
+      <c r="B98" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>696757</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6643672</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>132830960</v>
+      </c>
+      <c r="B99" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>696741</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6643703</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>132830962</v>
+      </c>
+      <c r="B100" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>696727</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6643708</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>132830970</v>
+      </c>
+      <c r="B101" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>696614</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6643745</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>132830976</v>
+      </c>
+      <c r="B102" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>696677</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6643661</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>132830922</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>697038</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6643950</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>55545583</v>
+      </c>
+      <c r="B104" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Eklund, NO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>697082</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6643889</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>En frisk alm ca 70 år gammal. Gammal barrblandskog på delvis kalkhaltig mark.</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55544916</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545340</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545397</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318473</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830980</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545420</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545596</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545424</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545225</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830968</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1841,6 +1896,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545208</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545398</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2059,6 +2124,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545399</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,6 +2234,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545434</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2271,6 +2346,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830936</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2376,6 +2456,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545592</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2481,6 +2566,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545594</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2586,6 +2676,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545704</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2698,6 +2793,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132826336</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2810,6 +2910,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830911</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2922,6 +3027,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830947</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3034,6 +3144,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830963</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3146,6 +3261,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830971</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3261,6 +3381,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830978</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3376,6 +3501,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830945</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3491,6 +3621,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830977</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3603,6 +3738,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132826159</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3718,6 +3858,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830912</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3833,6 +3978,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830972</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3948,6 +4098,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830964</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4055,6 +4210,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830961</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4169,6 +4329,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318142</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4280,6 +4445,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318416</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4391,6 +4561,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318564</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4502,6 +4677,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318601</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4613,6 +4793,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318667</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4727,6 +4912,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318689</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4838,6 +5028,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318788</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4949,6 +5144,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318816</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5060,6 +5260,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318880</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5174,6 +5379,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318944</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5295,6 +5505,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319229</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5406,6 +5621,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319238</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5517,6 +5737,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319284</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5628,6 +5853,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319349</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5749,6 +5979,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319414</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5870,6 +6105,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122319573</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5991,6 +6231,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122347695</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6107,6 +6352,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821365</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6223,6 +6473,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821435</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6339,6 +6594,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821474</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6455,6 +6715,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821521</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6571,6 +6836,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821594</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6683,6 +6953,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821661</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6799,6 +7074,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821719</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6915,6 +7195,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821892</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7031,6 +7316,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132822271</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7147,6 +7437,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132822662</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7263,6 +7558,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132822683</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7379,6 +7679,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132822772</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7495,6 +7800,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132822866</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7611,6 +7921,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132822951</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7727,6 +8042,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132823051</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7843,6 +8163,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132823172</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7959,6 +8284,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132823255</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8075,6 +8405,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132823493</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8191,6 +8526,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132825468</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8307,6 +8647,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132825569</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8423,6 +8768,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132826107</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8539,6 +8889,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830913</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8655,6 +9010,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830915</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8771,6 +9131,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830927</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8887,6 +9252,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830933</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9003,6 +9373,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830942</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9119,6 +9494,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830946</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9235,6 +9615,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830956</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9356,6 +9741,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830974</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9472,6 +9862,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830979</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9593,6 +9988,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830985</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9716,6 +10116,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133089120</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9827,6 +10232,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122318555</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9934,6 +10344,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821927</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10034,6 +10449,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55544918</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10141,6 +10561,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830923</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10248,6 +10673,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830925</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10355,6 +10785,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830929</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10462,6 +10897,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830930</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10569,6 +11009,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830932</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10676,6 +11121,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830934</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10783,6 +11233,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830935</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10890,6 +11345,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830937</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10997,6 +11457,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830940</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11104,6 +11569,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830941</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11211,6 +11681,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830943</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11318,6 +11793,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830949</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11425,6 +11905,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830954</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11532,6 +12017,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830957</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11639,6 +12129,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830960</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11746,6 +12241,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830962</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11853,6 +12353,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830970</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11960,6 +12465,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830976</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12067,6 +12577,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830922</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12172,8 +12687,118 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545583</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>